--- a/hojas_de_datos/ResultadosBenchMarking.xlsx
+++ b/hojas_de_datos/ResultadosBenchMarking.xlsx
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3021204929.824976</v>
+        <v>3024150467.102217</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -21525,7 +21525,7 @@
         <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>5267.777345711154</v>
+        <v>4241.99641231951</v>
       </c>
       <c r="F2" t="n">
         <v>7423.166440000001</v>
@@ -21552,7 +21552,7 @@
         <v>250.3942113358145</v>
       </c>
       <c r="N2" t="n">
-        <v>3125.114982518239</v>
+        <v>125.1149825182401</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
@@ -21561,7 +21561,7 @@
         <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3025.780933391645</v>
+        <v>5000</v>
       </c>
       <c r="R2" t="n">
         <v>-0</v>
@@ -21582,7 +21582,7 @@
         <v>-0</v>
       </c>
       <c r="X2" t="n">
-        <v>1517.8</v>
+        <v>2543.580933391645</v>
       </c>
     </row>
     <row r="3">
@@ -21673,7 +21673,7 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>4823.670183758341</v>
+        <v>4823.670183758342</v>
       </c>
       <c r="F4" t="n">
         <v>8079.23839</v>
@@ -21700,7 +21700,7 @@
         <v>377.8739993830025</v>
       </c>
       <c r="N4" t="n">
-        <v>2261.002937383469</v>
+        <v>3500</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -21709,7 +21709,7 @@
         <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4070.125919927039</v>
+        <v>-0</v>
       </c>
       <c r="R4" t="n">
         <v>-0</v>
@@ -21774,7 +21774,7 @@
         <v>425.4709999691429</v>
       </c>
       <c r="N5" t="n">
-        <v>692.9358767268823</v>
+        <v>1463.773371293509</v>
       </c>
       <c r="O5" t="n">
         <v>-0</v>
@@ -21783,7 +21783,7 @@
         <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5000</v>
+        <v>4229.162505433371</v>
       </c>
       <c r="R5" t="n">
         <v>-0</v>
@@ -21821,7 +21821,7 @@
         <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>4567.120777586878</v>
+        <v>4567.120777586879</v>
       </c>
       <c r="F6" t="n">
         <v>8682.460069999999</v>
@@ -21848,7 +21848,7 @@
         <v>459.4462723611891</v>
       </c>
       <c r="N6" t="n">
-        <v>2326.815179972386</v>
+        <v>3316.98062278923</v>
       </c>
       <c r="O6" t="n">
         <v>-0</v>
@@ -21857,7 +21857,7 @@
         <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>990.1654428168404</v>
+        <v>-0</v>
       </c>
       <c r="R6" t="n">
         <v>-0</v>
@@ -22043,7 +22043,7 @@
         <v>-0</v>
       </c>
       <c r="E9" t="n">
-        <v>7255.303644380245</v>
+        <v>7255.303644380246</v>
       </c>
       <c r="F9" t="n">
         <v>6619.036059999999</v>
@@ -22079,7 +22079,7 @@
         <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>2443.579497611642</v>
       </c>
       <c r="R9" t="n">
         <v>-0</v>
@@ -22153,7 +22153,7 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1816.679034094517</v>
+        <v>-0</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
@@ -22227,7 +22227,7 @@
         <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>2204.228393793392</v>
       </c>
       <c r="R11" t="n">
         <v>-0</v>
@@ -22262,10 +22262,10 @@
         <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>3237.020229057701</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
-        <v>1996.808339506161</v>
+        <v>4579.808339506161</v>
       </c>
       <c r="F12" t="n">
         <v>12534.34</v>
@@ -22336,10 +22336,10 @@
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0</v>
+        <v>6469.418523057303</v>
       </c>
       <c r="E13" t="n">
-        <v>-0</v>
+        <v>2435.774892253643</v>
       </c>
       <c r="F13" t="n">
         <v>15517.42701</v>
@@ -22413,7 +22413,7 @@
         <v>10423.35</v>
       </c>
       <c r="E14" t="n">
-        <v>-0</v>
+        <v>533.7846095046607</v>
       </c>
       <c r="F14" t="n">
         <v>17274.06641</v>
@@ -22561,7 +22561,7 @@
         <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0</v>
+        <v>257.5180622626422</v>
       </c>
       <c r="F16" t="n">
         <v>16964.3992</v>
@@ -22632,10 +22632,10 @@
         <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>10423.35</v>
+        <v>-0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0</v>
+        <v>1380.874141979453</v>
       </c>
       <c r="F17" t="n">
         <v>15285.94784</v>
@@ -22774,7 +22774,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4210.832768889447</v>
+        <v>-0</v>
       </c>
       <c r="C19" t="n">
         <v>4173.96286192</v>
@@ -22810,7 +22810,7 @@
         <v>155.274640416711</v>
       </c>
       <c r="N19" t="n">
-        <v>1638.89473300505</v>
+        <v>3500</v>
       </c>
       <c r="O19" t="n">
         <v>-0</v>
@@ -22884,7 +22884,7 @@
         <v>646.0270932079262</v>
       </c>
       <c r="N20" t="n">
-        <v>1582.508377436786</v>
+        <v>410.0732189624996</v>
       </c>
       <c r="O20" t="n">
         <v>-0</v>
@@ -22958,7 +22958,7 @@
         <v>445.1091389484712</v>
       </c>
       <c r="N21" t="n">
-        <v>573.0308691752589</v>
+        <v>3500</v>
       </c>
       <c r="O21" t="n">
         <v>-0</v>
@@ -22996,7 +22996,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>3475.962545707418</v>
+        <v>-0</v>
       </c>
       <c r="C22" t="n">
         <v>13603.98</v>
@@ -23070,7 +23070,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>-0</v>
+        <v>5310.87403031968</v>
       </c>
       <c r="C23" t="n">
         <v>7526.67448962</v>
@@ -23106,7 +23106,7 @@
         <v>217.7519741569288</v>
       </c>
       <c r="N23" t="n">
-        <v>3500</v>
+        <v>1389.213171302919</v>
       </c>
       <c r="O23" t="n">
         <v>-0</v>
@@ -23180,7 +23180,7 @@
         <v>202.9204721831211</v>
       </c>
       <c r="N24" t="n">
-        <v>3500</v>
+        <v>2662.989214442389</v>
       </c>
       <c r="O24" t="n">
         <v>-0</v>
@@ -23254,7 +23254,7 @@
         <v>252.2638997094605</v>
       </c>
       <c r="N25" t="n">
-        <v>3500</v>
+        <v>2056.337111728451</v>
       </c>
       <c r="O25" t="n">
         <v>-0</v>
@@ -23328,7 +23328,7 @@
         <v>300.9090666450953</v>
       </c>
       <c r="N26" t="n">
-        <v>2249.670652153991</v>
+        <v>3106.55460852242</v>
       </c>
       <c r="O26" t="n">
         <v>-0</v>
@@ -23366,7 +23366,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>-0</v>
+        <v>23.8054476937541</v>
       </c>
       <c r="C27" t="n">
         <v>3156.57</v>
@@ -23402,7 +23402,7 @@
         <v>354.0019194051488</v>
       </c>
       <c r="N27" t="n">
-        <v>2754.334061549865</v>
+        <v>2730.52861385611</v>
       </c>
       <c r="O27" t="n">
         <v>-0</v>
@@ -23588,7 +23588,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>-0</v>
+        <v>2466.58847162861</v>
       </c>
       <c r="C30" t="n">
         <v>3156.57</v>
@@ -23624,7 +23624,7 @@
         <v>514.5686936446501</v>
       </c>
       <c r="N30" t="n">
-        <v>3500</v>
+        <v>3494.54778406888</v>
       </c>
       <c r="O30" t="n">
         <v>-0</v>
@@ -23662,7 +23662,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>5629.644180326301</v>
+        <v>-0</v>
       </c>
       <c r="C31" t="n">
         <v>3156.57</v>
@@ -23698,7 +23698,7 @@
         <v>664.0886432481268</v>
       </c>
       <c r="N31" t="n">
-        <v>3301.3411070476</v>
+        <v>3500</v>
       </c>
       <c r="O31" t="n">
         <v>-0</v>
@@ -23736,7 +23736,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>870.7889000688356</v>
+        <v>-0</v>
       </c>
       <c r="C32" t="n">
         <v>3156.57</v>
@@ -23810,7 +23810,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>-0</v>
+        <v>7393.036246000001</v>
       </c>
       <c r="C33" t="n">
         <v>13603.98</v>
@@ -23846,7 +23846,7 @@
         <v>859.2264623578617</v>
       </c>
       <c r="N33" t="n">
-        <v>3500</v>
+        <v>2242.46027683484</v>
       </c>
       <c r="O33" t="n">
         <v>-0</v>
@@ -23958,7 +23958,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>6023.302495179312</v>
+        <v>5016.226694529273</v>
       </c>
       <c r="C35" t="n">
         <v>6048.51138724</v>
@@ -23994,7 +23994,7 @@
         <v>482.0255205753758</v>
       </c>
       <c r="N35" t="n">
-        <v>1368.55535428164</v>
+        <v>2375.631154931679</v>
       </c>
       <c r="O35" t="n">
         <v>-0</v>
@@ -24550,7 +24550,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>-0</v>
+        <v>5678.694498267134</v>
       </c>
       <c r="C43" t="n">
         <v>13603.98</v>
@@ -24624,7 +24624,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>-0</v>
+        <v>7393.036246000001</v>
       </c>
       <c r="C44" t="n">
         <v>13603.98</v>
@@ -24698,7 +24698,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>-0</v>
+        <v>7393.036246000001</v>
       </c>
       <c r="C45" t="n">
         <v>13603.98</v>
@@ -24734,7 +24734,7 @@
         <v>375.8500554982932</v>
       </c>
       <c r="N45" t="n">
-        <v>3500</v>
+        <v>1954.31420541114</v>
       </c>
       <c r="O45" t="n">
         <v>-0</v>
@@ -24772,7 +24772,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>2988.116679440191</v>
+        <v>5672.763736898643</v>
       </c>
       <c r="C46" t="n">
         <v>12247.86732114</v>
@@ -24808,7 +24808,7 @@
         <v>223.2967422021102</v>
       </c>
       <c r="N46" t="n">
-        <v>1898.568401195447</v>
+        <v>1399.514941515678</v>
       </c>
       <c r="O46" t="n">
         <v>-0</v>
@@ -24920,7 +24920,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>4922.372209184004</v>
+        <v>-0</v>
       </c>
       <c r="C48" t="n">
         <v>8383.780536509999</v>
@@ -24956,7 +24956,7 @@
         <v>74.36594025393924</v>
       </c>
       <c r="N48" t="n">
-        <v>1725.854771302921</v>
+        <v>2629.574948541416</v>
       </c>
       <c r="O48" t="n">
         <v>-0</v>
@@ -25030,7 +25030,7 @@
         <v>123.0736335392933</v>
       </c>
       <c r="N49" t="n">
-        <v>2265.032290451849</v>
+        <v>2394.394383038531</v>
       </c>
       <c r="O49" t="n">
         <v>-0</v>
@@ -25290,7 +25290,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>387.6601500911988</v>
+        <v>-0</v>
       </c>
       <c r="C53" t="n">
         <v>3156.57</v>
@@ -25364,7 +25364,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>2319.547015732088</v>
+        <v>-0</v>
       </c>
       <c r="C54" t="n">
         <v>3156.57</v>
@@ -25512,7 +25512,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>-0</v>
+        <v>3009.297076312449</v>
       </c>
       <c r="C56" t="n">
         <v>12383.26318294</v>
@@ -25586,7 +25586,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>7393.036246000001</v>
+        <v>-0</v>
       </c>
       <c r="C57" t="n">
         <v>4645.79724674</v>
@@ -25660,7 +25660,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>7393.036246000001</v>
+        <v>-0</v>
       </c>
       <c r="C58" t="n">
         <v>13603.98</v>
@@ -25734,7 +25734,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>3743.059257030732</v>
+        <v>-0</v>
       </c>
       <c r="C59" t="n">
         <v>9081.98225082</v>
@@ -25770,7 +25770,7 @@
         <v>373.9400218428702</v>
       </c>
       <c r="N59" t="n">
-        <v>2488.343015556547</v>
+        <v>3500</v>
       </c>
       <c r="O59" t="n">
         <v>-0</v>
@@ -25853,7 +25853,7 @@
         <v>-0</v>
       </c>
       <c r="Q60" t="n">
-        <v>504.2686572403109</v>
+        <v>3371.196503475658</v>
       </c>
       <c r="R60" t="n">
         <v>-0</v>
@@ -25918,7 +25918,7 @@
         <v>-0</v>
       </c>
       <c r="N61" t="n">
-        <v>761.3884989625003</v>
+        <v>1576.119398339636</v>
       </c>
       <c r="O61" t="n">
         <v>570.2927766128739</v>
@@ -26001,7 +26001,7 @@
         <v>-0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2866.927846235347</v>
+        <v>-0</v>
       </c>
       <c r="R62" t="n">
         <v>650.2977500531507</v>
@@ -26066,7 +26066,7 @@
         <v>-0</v>
       </c>
       <c r="N63" t="n">
-        <v>3237.454840892816</v>
+        <v>3500</v>
       </c>
       <c r="O63" t="n">
         <v>1439.812776618374</v>
@@ -26140,7 +26140,7 @@
         <v>-0</v>
       </c>
       <c r="N64" t="n">
-        <v>3500</v>
+        <v>2422.72394151568</v>
       </c>
       <c r="O64" t="n">
         <v>1213.628076613874</v>
@@ -26344,7 +26344,7 @@
         <v>-0</v>
       </c>
       <c r="H67" t="n">
-        <v>1533.83664</v>
+        <v>-0</v>
       </c>
       <c r="I67" t="n">
         <v>4613</v>
@@ -26362,7 +26362,7 @@
         <v>90.6519233861261</v>
       </c>
       <c r="N67" t="n">
-        <v>1834.40497300505</v>
+        <v>425.6595999382535</v>
       </c>
       <c r="O67" t="n">
         <v>-0</v>
@@ -26418,7 +26418,7 @@
         <v>-0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0</v>
+        <v>1533.83664</v>
       </c>
       <c r="I68" t="n">
         <v>4613</v>
@@ -26436,7 +26436,7 @@
         <v>587.3497764800568</v>
       </c>
       <c r="N68" t="n">
-        <v>2223.447626622067</v>
+        <v>757.2842666220668</v>
       </c>
       <c r="O68" t="n">
         <v>-0</v>
@@ -26492,7 +26492,7 @@
         <v>-0</v>
       </c>
       <c r="H69" t="n">
-        <v>1142.132674460203</v>
+        <v>1533.83664</v>
       </c>
       <c r="I69" t="n">
         <v>4613</v>
@@ -26566,7 +26566,7 @@
         <v>-0</v>
       </c>
       <c r="H70" t="n">
-        <v>1533.83664</v>
+        <v>-0</v>
       </c>
       <c r="I70" t="n">
         <v>4613</v>
@@ -26584,7 +26584,7 @@
         <v>262.4008026846213</v>
       </c>
       <c r="N70" t="n">
-        <v>1187.23018151568</v>
+        <v>2653.39354151568</v>
       </c>
       <c r="O70" t="n">
         <v>-0</v>
@@ -26714,7 +26714,7 @@
         <v>-0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0</v>
+        <v>1533.83664</v>
       </c>
       <c r="I72" t="n">
         <v>4613</v>
@@ -26732,7 +26732,7 @@
         <v>249.1245674377418</v>
       </c>
       <c r="N72" t="n">
-        <v>842.2081814933574</v>
+        <v>2250.953554560153</v>
       </c>
       <c r="O72" t="n">
         <v>-0</v>
@@ -27380,7 +27380,7 @@
         <v>-0</v>
       </c>
       <c r="H81" t="n">
-        <v>1533.83664</v>
+        <v>-0</v>
       </c>
       <c r="I81" t="n">
         <v>4613</v>
@@ -27528,7 +27528,7 @@
         <v>-0</v>
       </c>
       <c r="H83" t="n">
-        <v>-0</v>
+        <v>1142.132674460202</v>
       </c>
       <c r="I83" t="n">
         <v>4613</v>
@@ -28102,7 +28102,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>5076.18095732357</v>
+        <v>-0</v>
       </c>
       <c r="C91" t="n">
         <v>3156.57</v>
@@ -28176,7 +28176,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>-0</v>
+        <v>3813.457247456812</v>
       </c>
       <c r="C92" t="n">
         <v>3156.57</v>
@@ -28212,7 +28212,7 @@
         <v>-0</v>
       </c>
       <c r="N92" t="n">
-        <v>1880.624809552654</v>
+        <v>3143.348519419411</v>
       </c>
       <c r="O92" t="n">
         <v>893.531891337853</v>
@@ -28398,7 +28398,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>-0</v>
+        <v>1262.723709866756</v>
       </c>
       <c r="C95" t="n">
         <v>4163.44244778</v>
@@ -28434,7 +28434,7 @@
         <v>-0</v>
       </c>
       <c r="N95" t="n">
-        <v>2805.51390021009</v>
+        <v>1542.790190343334</v>
       </c>
       <c r="O95" t="n">
         <v>2059.25739013362</v>
@@ -29372,7 +29372,7 @@
         <v>6555.553197338784</v>
       </c>
       <c r="F108" t="n">
-        <v>10823.10621794033</v>
+        <v>12111.69536306516</v>
       </c>
       <c r="G108" t="n">
         <v>-0</v>
@@ -29387,7 +29387,7 @@
         <v>-0</v>
       </c>
       <c r="K108" t="n">
-        <v>2987.55441025</v>
+        <v>1698.965265125164</v>
       </c>
       <c r="L108" t="n">
         <v>2154.67024346759</v>
@@ -29399,7 +29399,7 @@
         <v>-0</v>
       </c>
       <c r="O108" t="n">
-        <v>1288.589145124836</v>
+        <v>-0</v>
       </c>
       <c r="P108" t="n">
         <v>5000</v>
@@ -29446,7 +29446,7 @@
         <v>15500</v>
       </c>
       <c r="F109" t="n">
-        <v>3110.368677645951</v>
+        <v>2256.539532521115</v>
       </c>
       <c r="G109" t="n">
         <v>2563.800547794086</v>
@@ -29461,7 +29461,7 @@
         <v>-0</v>
       </c>
       <c r="K109" t="n">
-        <v>1698.965265125164</v>
+        <v>2552.79441025</v>
       </c>
       <c r="L109" t="n">
         <v>-0</v>
@@ -29473,7 +29473,7 @@
         <v>-0</v>
       </c>
       <c r="O109" t="n">
-        <v>-0</v>
+        <v>853.829145124836</v>
       </c>
       <c r="P109" t="n">
         <v>5000</v>
@@ -29742,7 +29742,7 @@
         <v>15500</v>
       </c>
       <c r="F113" t="n">
-        <v>3088.371560403943</v>
+        <v>2813.618395278108</v>
       </c>
       <c r="G113" t="n">
         <v>5137.797260397982</v>
@@ -29757,7 +29757,7 @@
         <v>-0</v>
       </c>
       <c r="K113" t="n">
-        <v>1647.409224874164</v>
+        <v>1922.16239</v>
       </c>
       <c r="L113" t="n">
         <v>215.0546444638221</v>
@@ -29769,7 +29769,7 @@
         <v>-0</v>
       </c>
       <c r="O113" t="n">
-        <v>-0</v>
+        <v>274.7531651258359</v>
       </c>
       <c r="P113" t="n">
         <v>5000</v>
@@ -29816,7 +29816,7 @@
         <v>11227.84991862234</v>
       </c>
       <c r="F114" t="n">
-        <v>7370.046641781602</v>
+        <v>6660.533476655766</v>
       </c>
       <c r="G114" t="n">
         <v>961.3168953001709</v>
@@ -29831,7 +29831,7 @@
         <v>-0</v>
       </c>
       <c r="K114" t="n">
-        <v>1647.409224874164</v>
+        <v>2356.92239</v>
       </c>
       <c r="L114" t="n">
         <v>1438.990254105891</v>
@@ -29843,7 +29843,7 @@
         <v>-0</v>
       </c>
       <c r="O114" t="n">
-        <v>-0</v>
+        <v>709.5131651258362</v>
       </c>
       <c r="P114" t="n">
         <v>5000</v>
@@ -30331,7 +30331,7 @@
         <v>-0</v>
       </c>
       <c r="E121" t="n">
-        <v>1597.875262769742</v>
+        <v>1597.875262769741</v>
       </c>
       <c r="F121" t="n">
         <v>12916.3413</v>
@@ -30399,13 +30399,13 @@
         <v>-0</v>
       </c>
       <c r="C122" t="n">
-        <v>-0</v>
+        <v>2117.321068075324</v>
       </c>
       <c r="D122" t="n">
-        <v>465.6789319246764</v>
+        <v>-0</v>
       </c>
       <c r="E122" t="n">
-        <v>2112.097722135176</v>
+        <v>4695.097722135176</v>
       </c>
       <c r="F122" t="n">
         <v>13301.63984</v>
@@ -30476,10 +30476,10 @@
         <v>-0</v>
       </c>
       <c r="D123" t="n">
-        <v>2156.698431070829</v>
+        <v>-0</v>
       </c>
       <c r="E123" t="n">
-        <v>3073.694623581701</v>
+        <v>5230.39305465253</v>
       </c>
       <c r="F123" t="n">
         <v>13324.29168</v>
@@ -31068,10 +31068,10 @@
         <v>-0</v>
       </c>
       <c r="D131" t="n">
-        <v>5563.69374831</v>
+        <v>4848.950616217697</v>
       </c>
       <c r="E131" t="n">
-        <v>3584.517266087354</v>
+        <v>4299.260398179658</v>
       </c>
       <c r="F131" t="n">
         <v>14969.39079</v>
@@ -31219,10 +31219,10 @@
         <v>13320.75</v>
       </c>
       <c r="E133" t="n">
-        <v>15500</v>
+        <v>9506.882641300894</v>
       </c>
       <c r="F133" t="n">
-        <v>3168.552275056932</v>
+        <v>9161.669633756039</v>
       </c>
       <c r="G133" t="n">
         <v>-0</v>
@@ -31293,10 +31293,10 @@
         <v>13320.75</v>
       </c>
       <c r="E134" t="n">
-        <v>6888.940936501251</v>
+        <v>15500</v>
       </c>
       <c r="F134" t="n">
-        <v>11739.36733782</v>
+        <v>3128.308274321251</v>
       </c>
       <c r="G134" t="n">
         <v>1745.975476635593</v>
@@ -31441,10 +31441,10 @@
         <v>13320.75</v>
       </c>
       <c r="E136" t="n">
-        <v>9697.867878253328</v>
+        <v>8657.092114796933</v>
       </c>
       <c r="F136" t="n">
-        <v>8788.639426123606</v>
+        <v>9829.415189580001</v>
       </c>
       <c r="G136" t="n">
         <v>214.8692673201458</v>
@@ -31515,7 +31515,7 @@
         <v>13320.75</v>
       </c>
       <c r="E137" t="n">
-        <v>9482.37113144945</v>
+        <v>8911.168160777828</v>
       </c>
       <c r="F137" t="n">
         <v>9128.514142870001</v>
@@ -31533,7 +31533,7 @@
         <v>-0</v>
       </c>
       <c r="K137" t="n">
-        <v>1601.956469328378</v>
+        <v>2173.15944</v>
       </c>
       <c r="L137" t="n">
         <v>-0</v>
@@ -31545,7 +31545,7 @@
         <v>-0</v>
       </c>
       <c r="O137" t="n">
-        <v>-0</v>
+        <v>571.2029706716219</v>
       </c>
       <c r="P137" t="n">
         <v>5000</v>
@@ -31589,7 +31589,7 @@
         <v>13320.75</v>
       </c>
       <c r="E138" t="n">
-        <v>4681.473066959451</v>
+        <v>3675.510096287829</v>
       </c>
       <c r="F138" t="n">
         <v>13929.70820736</v>
@@ -31607,7 +31607,7 @@
         <v>-0</v>
       </c>
       <c r="K138" t="n">
-        <v>1601.956469328378</v>
+        <v>2607.91944</v>
       </c>
       <c r="L138" t="n">
         <v>-0</v>
@@ -31619,7 +31619,7 @@
         <v>-0</v>
       </c>
       <c r="O138" t="n">
-        <v>-0</v>
+        <v>1005.962970671622</v>
       </c>
       <c r="P138" t="n">
         <v>5000</v>
@@ -31731,10 +31731,10 @@
         <v>-0</v>
       </c>
       <c r="C140" t="n">
-        <v>-0</v>
+        <v>10447.41</v>
       </c>
       <c r="D140" t="n">
-        <v>2897.4</v>
+        <v>-0</v>
       </c>
       <c r="E140" t="n">
         <v>5500.388122006305</v>
@@ -31885,7 +31885,7 @@
         <v>-0</v>
       </c>
       <c r="E142" t="n">
-        <v>3082.72596720654</v>
+        <v>5665.72596720654</v>
       </c>
       <c r="F142" t="n">
         <v>11159.98377</v>
@@ -32027,13 +32027,13 @@
         <v>-0</v>
       </c>
       <c r="C144" t="n">
-        <v>5005.802096916634</v>
+        <v>1649.325494279837</v>
       </c>
       <c r="D144" t="n">
         <v>-0</v>
       </c>
       <c r="E144" t="n">
-        <v>398.1043244648981</v>
+        <v>2981.104324464898</v>
       </c>
       <c r="F144" t="n">
         <v>12369.58734</v>
@@ -32101,13 +32101,13 @@
         <v>-0</v>
       </c>
       <c r="C145" t="n">
-        <v>467.4866285078569</v>
+        <v>-0</v>
       </c>
       <c r="D145" t="n">
-        <v>-0</v>
+        <v>2897.4</v>
       </c>
       <c r="E145" t="n">
-        <v>2533.695937394116</v>
+        <v>-0</v>
       </c>
       <c r="F145" t="n">
         <v>13116.01247</v>
@@ -32119,7 +32119,7 @@
         <v>-0</v>
       </c>
       <c r="I145" t="n">
-        <v>3821.18803715</v>
+        <v>2565.74494346759</v>
       </c>
       <c r="J145" t="n">
         <v>-0</v>
@@ -32255,7 +32255,7 @@
         <v>13320.75</v>
       </c>
       <c r="E147" t="n">
-        <v>-0</v>
+        <v>1459.176594667197</v>
       </c>
       <c r="F147" t="n">
         <v>15217.86381</v>
@@ -32270,7 +32270,7 @@
         <v>-0</v>
       </c>
       <c r="J147" t="n">
-        <v>795.9433896049917</v>
+        <v>-0</v>
       </c>
       <c r="K147" t="n">
         <v>3139.68378372</v>
@@ -32326,7 +32326,7 @@
         <v>-0</v>
       </c>
       <c r="D148" t="n">
-        <v>10788.78388841773</v>
+        <v>13320.75</v>
       </c>
       <c r="E148" t="n">
         <v>-0</v>
@@ -32344,7 +32344,7 @@
         <v>-0</v>
       </c>
       <c r="J148" t="n">
-        <v>-0</v>
+        <v>2470.59299257951</v>
       </c>
       <c r="K148" t="n">
         <v>2704.92378372</v>
@@ -32418,7 +32418,7 @@
         <v>-0</v>
       </c>
       <c r="J149" t="n">
-        <v>2286.319388447299</v>
+        <v>-0</v>
       </c>
       <c r="K149" t="n">
         <v>2270.16378372</v>
@@ -32480,7 +32480,7 @@
         <v>9714.666993919622</v>
       </c>
       <c r="F150" t="n">
-        <v>8973.558292888461</v>
+        <v>8593.553412218949</v>
       </c>
       <c r="G150" t="n">
         <v>-0</v>
@@ -32495,7 +32495,7 @@
         <v>2843.15284789867</v>
       </c>
       <c r="K150" t="n">
-        <v>1455.398903050488</v>
+        <v>1835.40378372</v>
       </c>
       <c r="L150" t="n">
         <v>-0</v>
@@ -32507,7 +32507,7 @@
         <v>-0</v>
       </c>
       <c r="O150" t="n">
-        <v>-0</v>
+        <v>380.004880669512</v>
       </c>
       <c r="P150" t="n">
         <v>5000</v>
@@ -32551,10 +32551,10 @@
         <v>13320.75</v>
       </c>
       <c r="E151" t="n">
-        <v>3111.419174029921</v>
+        <v>5110.643549993593</v>
       </c>
       <c r="F151" t="n">
-        <v>15783.07311424002</v>
+        <v>13783.84873827635</v>
       </c>
       <c r="G151" t="n">
         <v>-0</v>
@@ -32566,7 +32566,7 @@
         <v>-0</v>
       </c>
       <c r="J151" t="n">
-        <v>2358.578311851559</v>
+        <v>-0</v>
       </c>
       <c r="K151" t="n">
         <v>1455.39890305</v>
@@ -32640,7 +32640,7 @@
         <v>-0</v>
       </c>
       <c r="J152" t="n">
-        <v>2244.796503340918</v>
+        <v>1490.192510148008</v>
       </c>
       <c r="K152" t="n">
         <v>1455.39890305</v>
@@ -32699,10 +32699,10 @@
         <v>13320.75</v>
       </c>
       <c r="E153" t="n">
-        <v>2854.398294233615</v>
+        <v>855.173918269943</v>
       </c>
       <c r="F153" t="n">
-        <v>16096.86299403633</v>
+        <v>18096.08737</v>
       </c>
       <c r="G153" t="n">
         <v>-0</v>
@@ -32714,7 +32714,7 @@
         <v>-0</v>
       </c>
       <c r="J153" t="n">
-        <v>-0</v>
+        <v>2469.408996834839</v>
       </c>
       <c r="K153" t="n">
         <v>1455.39890305</v>
@@ -32998,7 +32998,7 @@
         <v>10807.72393832665</v>
       </c>
       <c r="F157" t="n">
-        <v>7883.3343506724</v>
+        <v>7883.334350678489</v>
       </c>
       <c r="G157" t="n">
         <v>-0</v>
@@ -33013,7 +33013,7 @@
         <v>-0</v>
       </c>
       <c r="K157" t="n">
-        <v>1639.11874025</v>
+        <v>1639.11874024391</v>
       </c>
       <c r="L157" t="n">
         <v>-0</v>
@@ -33025,7 +33025,7 @@
         <v>-0</v>
       </c>
       <c r="O157" t="n">
-        <v>6.089976523071527e-09</v>
+        <v>-0</v>
       </c>
       <c r="P157" t="n">
         <v>5000</v>
@@ -33072,7 +33072,7 @@
         <v>13300.48802651136</v>
       </c>
       <c r="F158" t="n">
-        <v>5348.967261752002</v>
+        <v>5348.967261758092</v>
       </c>
       <c r="G158" t="n">
         <v>413.9205382782171</v>
@@ -33087,7 +33087,7 @@
         <v>-0</v>
       </c>
       <c r="K158" t="n">
-        <v>1639.11874025</v>
+        <v>1639.11874024391</v>
       </c>
       <c r="L158" t="n">
         <v>-0</v>
@@ -33099,7 +33099,7 @@
         <v>-0</v>
       </c>
       <c r="O158" t="n">
-        <v>6.089976523071527e-09</v>
+        <v>-0</v>
       </c>
       <c r="P158" t="n">
         <v>5000</v>
@@ -33291,10 +33291,10 @@
         <v>13320.75</v>
       </c>
       <c r="E161" t="n">
-        <v>15500</v>
+        <v>11876.72772881388</v>
       </c>
       <c r="F161" t="n">
-        <v>3134.091288269944</v>
+        <v>6757.36355945606</v>
       </c>
       <c r="G161" t="n">
         <v>2292.428999402101</v>
@@ -33439,10 +33439,10 @@
         <v>2897.4</v>
       </c>
       <c r="E163" t="n">
-        <v>11876.72772881389</v>
+        <v>15500</v>
       </c>
       <c r="F163" t="n">
-        <v>6737.839559456059</v>
+        <v>3114.567288269944</v>
       </c>
       <c r="G163" t="n">
         <v>-0</v>
@@ -33833,13 +33833,13 @@
         <v>-0</v>
       </c>
       <c r="M168" t="n">
-        <v>-0</v>
+        <v>4.87943907501176e-10</v>
       </c>
       <c r="N168" t="n">
         <v>-0</v>
       </c>
       <c r="O168" t="n">
-        <v>-4.87943907501176e-10</v>
+        <v>-0</v>
       </c>
       <c r="P168" t="n">
         <v>5000</v>
@@ -34088,7 +34088,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-5267.777345711154</v>
+        <v>-4241.99641231951</v>
       </c>
       <c r="F2" t="n">
         <v>-7423.166440000001</v>
@@ -34115,7 +34115,7 @@
         <v>-250.3942113358145</v>
       </c>
       <c r="N2" t="n">
-        <v>-3125.114982518239</v>
+        <v>-125.1149825182401</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -34124,7 +34124,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3025.780933391645</v>
+        <v>-5000</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34145,7 +34145,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1517.8</v>
+        <v>-2543.580933391645</v>
       </c>
     </row>
     <row r="3">
@@ -34236,7 +34236,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-4823.670183758341</v>
+        <v>-4823.670183758342</v>
       </c>
       <c r="F4" t="n">
         <v>-8079.23839</v>
@@ -34263,7 +34263,7 @@
         <v>-377.8739993830025</v>
       </c>
       <c r="N4" t="n">
-        <v>-2261.002937383469</v>
+        <v>-3500</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -34272,7 +34272,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4070.125919927039</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -34337,7 +34337,7 @@
         <v>-425.4709999691429</v>
       </c>
       <c r="N5" t="n">
-        <v>-692.9358767268823</v>
+        <v>-1463.773371293509</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -34346,7 +34346,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5000</v>
+        <v>-4229.162505433371</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -34384,7 +34384,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-4567.120777586878</v>
+        <v>-4567.120777586879</v>
       </c>
       <c r="F6" t="n">
         <v>-8682.460069999999</v>
@@ -34411,7 +34411,7 @@
         <v>-459.4462723611891</v>
       </c>
       <c r="N6" t="n">
-        <v>-2326.815179972386</v>
+        <v>-3316.98062278923</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -34420,7 +34420,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-990.1654428168404</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -34606,7 +34606,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-7255.303644380245</v>
+        <v>-7255.303644380246</v>
       </c>
       <c r="F9" t="n">
         <v>-6619.036059999999</v>
@@ -34642,7 +34642,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2443.579497611642</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -34716,7 +34716,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1816.679034094517</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -34790,7 +34790,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2204.228393793392</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -34825,10 +34825,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-3237.020229057701</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-1996.808339506161</v>
+        <v>-4579.808339506161</v>
       </c>
       <c r="F12" t="n">
         <v>-12534.34</v>
@@ -34899,10 +34899,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-6469.418523057303</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-2435.774892253643</v>
       </c>
       <c r="F13" t="n">
         <v>-15517.42701</v>
@@ -34976,7 +34976,7 @@
         <v>-10423.35</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-533.7846095046607</v>
       </c>
       <c r="F14" t="n">
         <v>-17274.06641</v>
@@ -35124,7 +35124,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-257.5180622626422</v>
       </c>
       <c r="F16" t="n">
         <v>-16964.3992</v>
@@ -35195,10 +35195,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-10423.35</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-1380.874141979453</v>
       </c>
       <c r="F17" t="n">
         <v>-15285.94784</v>
@@ -35337,7 +35337,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-4210.832768889447</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>-4173.96286192</v>
@@ -35373,7 +35373,7 @@
         <v>-155.274640416711</v>
       </c>
       <c r="N19" t="n">
-        <v>-1638.89473300505</v>
+        <v>-3500</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -35447,7 +35447,7 @@
         <v>-646.0270932079262</v>
       </c>
       <c r="N20" t="n">
-        <v>-1582.508377436786</v>
+        <v>-410.0732189624996</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -35521,7 +35521,7 @@
         <v>-445.1091389484712</v>
       </c>
       <c r="N21" t="n">
-        <v>-573.0308691752589</v>
+        <v>-3500</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -35559,7 +35559,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-3475.962545707418</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>-13603.98</v>
@@ -35633,7 +35633,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>-5310.87403031968</v>
       </c>
       <c r="C23" t="n">
         <v>-7526.67448962</v>
@@ -35669,7 +35669,7 @@
         <v>-217.7519741569288</v>
       </c>
       <c r="N23" t="n">
-        <v>-3500</v>
+        <v>-1389.213171302919</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -35743,7 +35743,7 @@
         <v>-202.9204721831211</v>
       </c>
       <c r="N24" t="n">
-        <v>-3500</v>
+        <v>-2662.989214442389</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -35817,7 +35817,7 @@
         <v>-252.2638997094605</v>
       </c>
       <c r="N25" t="n">
-        <v>-3500</v>
+        <v>-2056.337111728451</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -35891,7 +35891,7 @@
         <v>-300.9090666450953</v>
       </c>
       <c r="N26" t="n">
-        <v>-2249.670652153991</v>
+        <v>-3106.55460852242</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -35929,7 +35929,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>-23.8054476937541</v>
       </c>
       <c r="C27" t="n">
         <v>-3156.57</v>
@@ -35965,7 +35965,7 @@
         <v>-354.0019194051488</v>
       </c>
       <c r="N27" t="n">
-        <v>-2754.334061549865</v>
+        <v>-2730.52861385611</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -36151,7 +36151,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-2466.58847162861</v>
       </c>
       <c r="C30" t="n">
         <v>-3156.57</v>
@@ -36187,7 +36187,7 @@
         <v>-514.5686936446501</v>
       </c>
       <c r="N30" t="n">
-        <v>-3500</v>
+        <v>-3494.54778406888</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -36225,7 +36225,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>-5629.644180326301</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>-3156.57</v>
@@ -36261,7 +36261,7 @@
         <v>-664.0886432481268</v>
       </c>
       <c r="N31" t="n">
-        <v>-3301.3411070476</v>
+        <v>-3500</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -36299,7 +36299,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>-870.7889000688356</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>-3156.57</v>
@@ -36373,7 +36373,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>-7393.036246000001</v>
       </c>
       <c r="C33" t="n">
         <v>-13603.98</v>
@@ -36409,7 +36409,7 @@
         <v>-859.2264623578617</v>
       </c>
       <c r="N33" t="n">
-        <v>-3500</v>
+        <v>-2242.46027683484</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -36521,7 +36521,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>-6023.302495179312</v>
+        <v>-5016.226694529273</v>
       </c>
       <c r="C35" t="n">
         <v>-6048.51138724</v>
@@ -36557,7 +36557,7 @@
         <v>-482.0255205753758</v>
       </c>
       <c r="N35" t="n">
-        <v>-1368.55535428164</v>
+        <v>-2375.631154931679</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -37113,7 +37113,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>-5678.694498267134</v>
       </c>
       <c r="C43" t="n">
         <v>-13603.98</v>
@@ -37187,7 +37187,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>-7393.036246000001</v>
       </c>
       <c r="C44" t="n">
         <v>-13603.98</v>
@@ -37261,7 +37261,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>-7393.036246000001</v>
       </c>
       <c r="C45" t="n">
         <v>-13603.98</v>
@@ -37297,7 +37297,7 @@
         <v>-375.8500554982932</v>
       </c>
       <c r="N45" t="n">
-        <v>-3500</v>
+        <v>-1954.31420541114</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -37335,7 +37335,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>-2988.116679440191</v>
+        <v>-5672.763736898643</v>
       </c>
       <c r="C46" t="n">
         <v>-12247.86732114</v>
@@ -37371,7 +37371,7 @@
         <v>-223.2967422021102</v>
       </c>
       <c r="N46" t="n">
-        <v>-1898.568401195447</v>
+        <v>-1399.514941515678</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -37483,7 +37483,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>-4922.372209184004</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>-8383.780536509999</v>
@@ -37519,7 +37519,7 @@
         <v>-74.36594025393924</v>
       </c>
       <c r="N48" t="n">
-        <v>-1725.854771302921</v>
+        <v>-2629.574948541416</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -37593,7 +37593,7 @@
         <v>-123.0736335392933</v>
       </c>
       <c r="N49" t="n">
-        <v>-2265.032290451849</v>
+        <v>-2394.394383038531</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -37853,7 +37853,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>-387.6601500911988</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
         <v>-3156.57</v>
@@ -37927,7 +37927,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>-2319.547015732088</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
         <v>-3156.57</v>
@@ -38075,7 +38075,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>-3009.297076312449</v>
       </c>
       <c r="C56" t="n">
         <v>-12383.26318294</v>
@@ -38149,7 +38149,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>-7393.036246000001</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
         <v>-4645.79724674</v>
@@ -38223,7 +38223,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>-7393.036246000001</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
         <v>-13603.98</v>
@@ -38297,7 +38297,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>-3743.059257030732</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
         <v>-9081.98225082</v>
@@ -38333,7 +38333,7 @@
         <v>-373.9400218428702</v>
       </c>
       <c r="N59" t="n">
-        <v>-2488.343015556547</v>
+        <v>-3500</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -38416,7 +38416,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>-504.2686572403109</v>
+        <v>-3371.196503475658</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -38481,7 +38481,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>-761.3884989625003</v>
+        <v>-1576.119398339636</v>
       </c>
       <c r="O61" t="n">
         <v>-570.2927766128739</v>
@@ -38564,7 +38564,7 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>-2866.927846235347</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>-650.2977500531507</v>
@@ -38629,7 +38629,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>-3237.454840892816</v>
+        <v>-3500</v>
       </c>
       <c r="O63" t="n">
         <v>-1439.812776618374</v>
@@ -38703,7 +38703,7 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>-3500</v>
+        <v>-2422.72394151568</v>
       </c>
       <c r="O64" t="n">
         <v>-1213.628076613874</v>
@@ -38907,7 +38907,7 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1533.83664</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>-4613</v>
@@ -38925,7 +38925,7 @@
         <v>-90.6519233861261</v>
       </c>
       <c r="N67" t="n">
-        <v>-1834.40497300505</v>
+        <v>-425.6595999382535</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -38981,7 +38981,7 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>-1533.83664</v>
       </c>
       <c r="I68" t="n">
         <v>-4613</v>
@@ -38999,7 +38999,7 @@
         <v>-587.3497764800568</v>
       </c>
       <c r="N68" t="n">
-        <v>-2223.447626622067</v>
+        <v>-757.2842666220668</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -39055,7 +39055,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1142.132674460203</v>
+        <v>-1533.83664</v>
       </c>
       <c r="I69" t="n">
         <v>-4613</v>
@@ -39129,7 +39129,7 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1533.83664</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>-4613</v>
@@ -39147,7 +39147,7 @@
         <v>-262.4008026846213</v>
       </c>
       <c r="N70" t="n">
-        <v>-1187.23018151568</v>
+        <v>-2653.39354151568</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -39277,7 +39277,7 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>-1533.83664</v>
       </c>
       <c r="I72" t="n">
         <v>-4613</v>
@@ -39295,7 +39295,7 @@
         <v>-249.1245674377418</v>
       </c>
       <c r="N72" t="n">
-        <v>-842.2081814933574</v>
+        <v>-2250.953554560153</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -39943,7 +39943,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-1533.83664</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>-4613</v>
@@ -40091,7 +40091,7 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>-1142.132674460202</v>
       </c>
       <c r="I83" t="n">
         <v>-4613</v>
@@ -40665,7 +40665,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>-5076.18095732357</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
         <v>-3156.57</v>
@@ -40739,7 +40739,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>-3813.457247456812</v>
       </c>
       <c r="C92" t="n">
         <v>-3156.57</v>
@@ -40775,7 +40775,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>-1880.624809552654</v>
+        <v>-3143.348519419411</v>
       </c>
       <c r="O92" t="n">
         <v>-893.531891337853</v>
@@ -40961,7 +40961,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>-1262.723709866756</v>
       </c>
       <c r="C95" t="n">
         <v>-4163.44244778</v>
@@ -40997,7 +40997,7 @@
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>-2805.51390021009</v>
+        <v>-1542.790190343334</v>
       </c>
       <c r="O95" t="n">
         <v>-2059.25739013362</v>
@@ -41935,7 +41935,7 @@
         <v>-6555.553197338784</v>
       </c>
       <c r="F108" t="n">
-        <v>-10823.10621794033</v>
+        <v>-12111.69536306516</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -41950,7 +41950,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>-2987.55441025</v>
+        <v>-1698.965265125164</v>
       </c>
       <c r="L108" t="n">
         <v>-2154.67024346759</v>
@@ -41962,7 +41962,7 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>-1288.589145124836</v>
+        <v>0</v>
       </c>
       <c r="P108" t="n">
         <v>-5000</v>
@@ -42009,7 +42009,7 @@
         <v>-15500</v>
       </c>
       <c r="F109" t="n">
-        <v>-3110.368677645951</v>
+        <v>-2256.539532521115</v>
       </c>
       <c r="G109" t="n">
         <v>-2563.800547794086</v>
@@ -42024,7 +42024,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>-1698.965265125164</v>
+        <v>-2552.79441025</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -42036,7 +42036,7 @@
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>-853.829145124836</v>
       </c>
       <c r="P109" t="n">
         <v>-5000</v>
@@ -42305,7 +42305,7 @@
         <v>-15500</v>
       </c>
       <c r="F113" t="n">
-        <v>-3088.371560403943</v>
+        <v>-2813.618395278108</v>
       </c>
       <c r="G113" t="n">
         <v>-5137.797260397982</v>
@@ -42320,7 +42320,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>-1647.409224874164</v>
+        <v>-1922.16239</v>
       </c>
       <c r="L113" t="n">
         <v>-215.0546444638221</v>
@@ -42332,7 +42332,7 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>-274.7531651258359</v>
       </c>
       <c r="P113" t="n">
         <v>-5000</v>
@@ -42379,7 +42379,7 @@
         <v>-11227.84991862234</v>
       </c>
       <c r="F114" t="n">
-        <v>-7370.046641781602</v>
+        <v>-6660.533476655766</v>
       </c>
       <c r="G114" t="n">
         <v>-961.3168953001709</v>
@@ -42394,7 +42394,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>-1647.409224874164</v>
+        <v>-2356.92239</v>
       </c>
       <c r="L114" t="n">
         <v>-1438.990254105891</v>
@@ -42406,7 +42406,7 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>-709.5131651258362</v>
       </c>
       <c r="P114" t="n">
         <v>-5000</v>
@@ -42894,7 +42894,7 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>-1597.875262769742</v>
+        <v>-1597.875262769741</v>
       </c>
       <c r="F121" t="n">
         <v>-12916.3413</v>
@@ -42962,13 +42962,13 @@
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>-2117.321068075324</v>
       </c>
       <c r="D122" t="n">
-        <v>-465.6789319246764</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>-2112.097722135176</v>
+        <v>-4695.097722135176</v>
       </c>
       <c r="F122" t="n">
         <v>-13301.63984</v>
@@ -43039,10 +43039,10 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>-2156.698431070829</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>-3073.694623581701</v>
+        <v>-5230.39305465253</v>
       </c>
       <c r="F123" t="n">
         <v>-13324.29168</v>
@@ -43631,10 +43631,10 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>-5563.69374831</v>
+        <v>-4848.950616217697</v>
       </c>
       <c r="E131" t="n">
-        <v>-3584.517266087354</v>
+        <v>-4299.260398179658</v>
       </c>
       <c r="F131" t="n">
         <v>-14969.39079</v>
@@ -43782,10 +43782,10 @@
         <v>-13320.75</v>
       </c>
       <c r="E133" t="n">
-        <v>-15500</v>
+        <v>-9506.882641300894</v>
       </c>
       <c r="F133" t="n">
-        <v>-3168.552275056932</v>
+        <v>-9161.669633756039</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -43856,10 +43856,10 @@
         <v>-13320.75</v>
       </c>
       <c r="E134" t="n">
-        <v>-6888.940936501251</v>
+        <v>-15500</v>
       </c>
       <c r="F134" t="n">
-        <v>-11739.36733782</v>
+        <v>-3128.308274321251</v>
       </c>
       <c r="G134" t="n">
         <v>-1745.975476635593</v>
@@ -44004,10 +44004,10 @@
         <v>-13320.75</v>
       </c>
       <c r="E136" t="n">
-        <v>-9697.867878253328</v>
+        <v>-8657.092114796933</v>
       </c>
       <c r="F136" t="n">
-        <v>-8788.639426123606</v>
+        <v>-9829.415189580001</v>
       </c>
       <c r="G136" t="n">
         <v>-214.8692673201458</v>
@@ -44078,7 +44078,7 @@
         <v>-13320.75</v>
       </c>
       <c r="E137" t="n">
-        <v>-9482.37113144945</v>
+        <v>-8911.168160777828</v>
       </c>
       <c r="F137" t="n">
         <v>-9128.514142870001</v>
@@ -44096,7 +44096,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>-1601.956469328378</v>
+        <v>-2173.15944</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -44108,7 +44108,7 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>-571.2029706716219</v>
       </c>
       <c r="P137" t="n">
         <v>-5000</v>
@@ -44152,7 +44152,7 @@
         <v>-13320.75</v>
       </c>
       <c r="E138" t="n">
-        <v>-4681.473066959451</v>
+        <v>-3675.510096287829</v>
       </c>
       <c r="F138" t="n">
         <v>-13929.70820736</v>
@@ -44170,7 +44170,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>-1601.956469328378</v>
+        <v>-2607.91944</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -44182,7 +44182,7 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>-1005.962970671622</v>
       </c>
       <c r="P138" t="n">
         <v>-5000</v>
@@ -44294,10 +44294,10 @@
         <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>-10447.41</v>
       </c>
       <c r="D140" t="n">
-        <v>-2897.4</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
         <v>-5500.388122006305</v>
@@ -44448,7 +44448,7 @@
         <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>-3082.72596720654</v>
+        <v>-5665.72596720654</v>
       </c>
       <c r="F142" t="n">
         <v>-11159.98377</v>
@@ -44590,13 +44590,13 @@
         <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>-5005.802096916634</v>
+        <v>-1649.325494279837</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>-398.1043244648981</v>
+        <v>-2981.104324464898</v>
       </c>
       <c r="F144" t="n">
         <v>-12369.58734</v>
@@ -44664,13 +44664,13 @@
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>-467.4866285078569</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>-2897.4</v>
       </c>
       <c r="E145" t="n">
-        <v>-2533.695937394116</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
         <v>-13116.01247</v>
@@ -44682,7 +44682,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>-3821.18803715</v>
+        <v>-2565.74494346759</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -44818,7 +44818,7 @@
         <v>-13320.75</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>-1459.176594667197</v>
       </c>
       <c r="F147" t="n">
         <v>-15217.86381</v>
@@ -44833,7 +44833,7 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>-795.9433896049917</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
         <v>-3139.68378372</v>
@@ -44889,7 +44889,7 @@
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>-10788.78388841773</v>
+        <v>-13320.75</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -44907,7 +44907,7 @@
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>-2470.59299257951</v>
       </c>
       <c r="K148" t="n">
         <v>-2704.92378372</v>
@@ -44981,7 +44981,7 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>-2286.319388447299</v>
+        <v>0</v>
       </c>
       <c r="K149" t="n">
         <v>-2270.16378372</v>
@@ -45043,7 +45043,7 @@
         <v>-9714.666993919622</v>
       </c>
       <c r="F150" t="n">
-        <v>-8973.558292888461</v>
+        <v>-8593.553412218949</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -45058,7 +45058,7 @@
         <v>-2843.15284789867</v>
       </c>
       <c r="K150" t="n">
-        <v>-1455.398903050488</v>
+        <v>-1835.40378372</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -45070,7 +45070,7 @@
         <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>0</v>
+        <v>-380.004880669512</v>
       </c>
       <c r="P150" t="n">
         <v>-5000</v>
@@ -45114,10 +45114,10 @@
         <v>-13320.75</v>
       </c>
       <c r="E151" t="n">
-        <v>-3111.419174029921</v>
+        <v>-5110.643549993593</v>
       </c>
       <c r="F151" t="n">
-        <v>-15783.07311424002</v>
+        <v>-13783.84873827635</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -45129,7 +45129,7 @@
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>-2358.578311851559</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
         <v>-1455.39890305</v>
@@ -45203,7 +45203,7 @@
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>-2244.796503340918</v>
+        <v>-1490.192510148008</v>
       </c>
       <c r="K152" t="n">
         <v>-1455.39890305</v>
@@ -45262,10 +45262,10 @@
         <v>-13320.75</v>
       </c>
       <c r="E153" t="n">
-        <v>-2854.398294233615</v>
+        <v>-855.173918269943</v>
       </c>
       <c r="F153" t="n">
-        <v>-16096.86299403633</v>
+        <v>-18096.08737</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -45277,7 +45277,7 @@
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>-2469.408996834839</v>
       </c>
       <c r="K153" t="n">
         <v>-1455.39890305</v>
@@ -45561,7 +45561,7 @@
         <v>-10807.72393832665</v>
       </c>
       <c r="F157" t="n">
-        <v>-7883.3343506724</v>
+        <v>-7883.334350678489</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -45576,7 +45576,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>-1639.11874025</v>
+        <v>-1639.11874024391</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -45588,7 +45588,7 @@
         <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>-6.089976523071527e-09</v>
+        <v>0</v>
       </c>
       <c r="P157" t="n">
         <v>-5000</v>
@@ -45635,7 +45635,7 @@
         <v>-13300.48802651136</v>
       </c>
       <c r="F158" t="n">
-        <v>-5348.967261752002</v>
+        <v>-5348.967261758092</v>
       </c>
       <c r="G158" t="n">
         <v>-413.9205382782171</v>
@@ -45650,7 +45650,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>-1639.11874025</v>
+        <v>-1639.11874024391</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -45662,7 +45662,7 @@
         <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>-6.089976523071527e-09</v>
+        <v>0</v>
       </c>
       <c r="P158" t="n">
         <v>-5000</v>
@@ -45854,10 +45854,10 @@
         <v>-13320.75</v>
       </c>
       <c r="E161" t="n">
-        <v>-15500</v>
+        <v>-11876.72772881388</v>
       </c>
       <c r="F161" t="n">
-        <v>-3134.091288269944</v>
+        <v>-6757.36355945606</v>
       </c>
       <c r="G161" t="n">
         <v>-2292.428999402101</v>
@@ -46002,10 +46002,10 @@
         <v>-2897.4</v>
       </c>
       <c r="E163" t="n">
-        <v>-11876.72772881389</v>
+        <v>-15500</v>
       </c>
       <c r="F163" t="n">
-        <v>-6737.839559456059</v>
+        <v>-3114.567288269944</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -46396,13 +46396,13 @@
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>-4.87943907501176e-10</v>
       </c>
       <c r="N168" t="n">
         <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>4.87943907501176e-10</v>
+        <v>0</v>
       </c>
       <c r="P168" t="n">
         <v>-5000</v>
@@ -47056,7 +47056,7 @@
         <v>944.3353171983975</v>
       </c>
       <c r="U2" t="n">
-        <v>3025.780933391645</v>
+        <v>5000</v>
       </c>
       <c r="V2" t="n">
         <v>1223.6722856992</v>
@@ -47068,7 +47068,7 @@
         <v>1517.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>1025.780933391645</v>
       </c>
       <c r="Z2" t="n">
         <v>1240</v>
@@ -47222,7 +47222,7 @@
         <v>816.8555291512096</v>
       </c>
       <c r="U4" t="n">
-        <v>4070.125919927039</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
         <v>1223.6722856992</v>
@@ -47305,7 +47305,7 @@
         <v>769.2585285650691</v>
       </c>
       <c r="U5" t="n">
-        <v>5000</v>
+        <v>4229.162505433371</v>
       </c>
       <c r="V5" t="n">
         <v>1223.6722856992</v>
@@ -47388,7 +47388,7 @@
         <v>735.2832561730229</v>
       </c>
       <c r="U6" t="n">
-        <v>990.1654428168404</v>
+        <v>-0</v>
       </c>
       <c r="V6" t="n">
         <v>1223.6722856992</v>
@@ -47637,7 +47637,7 @@
         <v>695.9012281866748</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>2443.579497611642</v>
       </c>
       <c r="V9" t="n">
         <v>1223.6722856992</v>
@@ -47720,7 +47720,7 @@
         <v>695.4925897388337</v>
       </c>
       <c r="U10" t="n">
-        <v>1816.679034094517</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>1223.6722856992</v>
@@ -47803,7 +47803,7 @@
         <v>1149.565603887817</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>2204.228393793392</v>
       </c>
       <c r="V11" t="n">
         <v>1223.6722856992</v>
@@ -48117,7 +48117,7 @@
         <v>51.68</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>3.830241336949257</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
@@ -48283,7 +48283,7 @@
         <v>65.246</v>
       </c>
       <c r="O17" t="n">
-        <v>25.58011753077176</v>
+        <v>21.74987619382068</v>
       </c>
       <c r="P17" t="n">
         <v>-0</v>
@@ -48422,7 +48422,7 @@
         <v>1049.093</v>
       </c>
       <c r="F19" t="n">
-        <v>4210.832768889447</v>
+        <v>-0</v>
       </c>
       <c r="G19" t="n">
         <v>794.8797756535125</v>
@@ -48671,7 +48671,7 @@
         <v>1049.093</v>
       </c>
       <c r="F22" t="n">
-        <v>3475.962545707418</v>
+        <v>-0</v>
       </c>
       <c r="G22" t="n">
         <v>794.8797756535125</v>
@@ -48754,7 +48754,7 @@
         <v>1004.765</v>
       </c>
       <c r="F23" t="n">
-        <v>-0</v>
+        <v>5310.87403031968</v>
       </c>
       <c r="G23" t="n">
         <v>794.8797756535125</v>
@@ -49086,7 +49086,7 @@
         <v>953.049</v>
       </c>
       <c r="F27" t="n">
-        <v>-0</v>
+        <v>23.8054476937541</v>
       </c>
       <c r="G27" t="n">
         <v>794.8797756535125</v>
@@ -49335,7 +49335,7 @@
         <v>953.049</v>
       </c>
       <c r="F30" t="n">
-        <v>-0</v>
+        <v>2466.58847162861</v>
       </c>
       <c r="G30" t="n">
         <v>794.8797756535125</v>
@@ -49418,7 +49418,7 @@
         <v>953.049</v>
       </c>
       <c r="F31" t="n">
-        <v>5629.644180326301</v>
+        <v>-0</v>
       </c>
       <c r="G31" t="n">
         <v>794.8797756535125</v>
@@ -49501,7 +49501,7 @@
         <v>962.9</v>
       </c>
       <c r="F32" t="n">
-        <v>870.7889000688356</v>
+        <v>-0</v>
       </c>
       <c r="G32" t="n">
         <v>794.8797756535125</v>
@@ -49584,7 +49584,7 @@
         <v>1036.78</v>
       </c>
       <c r="F33" t="n">
-        <v>-0</v>
+        <v>7393.036246000001</v>
       </c>
       <c r="G33" t="n">
         <v>794.8797756535125</v>
@@ -49750,7 +49750,7 @@
         <v>1081.108</v>
       </c>
       <c r="F35" t="n">
-        <v>6023.302495179312</v>
+        <v>5016.226694529273</v>
       </c>
       <c r="G35" t="n">
         <v>794.8797756535125</v>
@@ -49869,7 +49869,7 @@
         <v>366.1717586600685</v>
       </c>
       <c r="R36" t="n">
-        <v>2591</v>
+        <v>446.3431664435411</v>
       </c>
       <c r="S36" t="n">
         <v>499.1065893617001</v>
@@ -49922,7 +49922,7 @@
         <v>794.8797756535125</v>
       </c>
       <c r="H37" t="n">
-        <v>-0</v>
+        <v>7872.999999999999</v>
       </c>
       <c r="I37" t="n">
         <v>4498.05924845574</v>
@@ -49952,7 +49952,7 @@
         <v>366.1717586600685</v>
       </c>
       <c r="R37" t="n">
-        <v>-0</v>
+        <v>1119.82040920801</v>
       </c>
       <c r="S37" t="n">
         <v>1533.19207234043</v>
@@ -50088,7 +50088,7 @@
         <v>794.8797756535125</v>
       </c>
       <c r="H39" t="n">
-        <v>7872.999999999999</v>
+        <v>-0</v>
       </c>
       <c r="I39" t="n">
         <v>7432.931580118211</v>
@@ -50171,7 +50171,7 @@
         <v>794.8797756535125</v>
       </c>
       <c r="H40" t="n">
-        <v>-0</v>
+        <v>7594.253243008296</v>
       </c>
       <c r="I40" t="n">
         <v>8449.30537281143</v>
@@ -50254,7 +50254,7 @@
         <v>794.8797756535125</v>
       </c>
       <c r="H41" t="n">
-        <v>7594.253243008296</v>
+        <v>-0</v>
       </c>
       <c r="I41" t="n">
         <v>5495.44045506996</v>
@@ -50284,7 +50284,7 @@
         <v>366.1717586600685</v>
       </c>
       <c r="R41" t="n">
-        <v>460.0234595446764</v>
+        <v>1484.859883893123</v>
       </c>
       <c r="S41" t="n">
         <v>1753.40815744681</v>
@@ -50414,7 +50414,7 @@
         <v>1058.944</v>
       </c>
       <c r="F43" t="n">
-        <v>-0</v>
+        <v>5678.694498267134</v>
       </c>
       <c r="G43" t="n">
         <v>794.8797756535125</v>
@@ -50497,7 +50497,7 @@
         <v>1073.72</v>
       </c>
       <c r="F44" t="n">
-        <v>-0</v>
+        <v>7393.036246000001</v>
       </c>
       <c r="G44" t="n">
         <v>794.8797756535125</v>
@@ -50580,7 +50580,7 @@
         <v>1090.958</v>
       </c>
       <c r="F45" t="n">
-        <v>-0</v>
+        <v>7393.036246000001</v>
       </c>
       <c r="G45" t="n">
         <v>794.8797756535125</v>
@@ -50663,7 +50663,7 @@
         <v>1113.122</v>
       </c>
       <c r="F46" t="n">
-        <v>2988.116679440191</v>
+        <v>5672.763736898643</v>
       </c>
       <c r="G46" t="n">
         <v>794.8797756535125</v>
@@ -50829,7 +50829,7 @@
         <v>1098.346</v>
       </c>
       <c r="F48" t="n">
-        <v>4922.372209184004</v>
+        <v>-0</v>
       </c>
       <c r="G48" t="n">
         <v>794.8797756535125</v>
@@ -51244,7 +51244,7 @@
         <v>1026.929</v>
       </c>
       <c r="F53" t="n">
-        <v>387.6601500911988</v>
+        <v>-0</v>
       </c>
       <c r="G53" t="n">
         <v>794.8797756535125</v>
@@ -51327,7 +51327,7 @@
         <v>1022.004</v>
       </c>
       <c r="F54" t="n">
-        <v>2319.547015732088</v>
+        <v>-0</v>
       </c>
       <c r="G54" t="n">
         <v>794.8797756535125</v>
@@ -51493,7 +51493,7 @@
         <v>1031.855</v>
       </c>
       <c r="F56" t="n">
-        <v>-0</v>
+        <v>3009.297076312449</v>
       </c>
       <c r="G56" t="n">
         <v>794.8797756535125</v>
@@ -51576,7 +51576,7 @@
         <v>1039.243</v>
       </c>
       <c r="F57" t="n">
-        <v>7393.036246000001</v>
+        <v>-0</v>
       </c>
       <c r="G57" t="n">
         <v>794.8797756535125</v>
@@ -51659,7 +51659,7 @@
         <v>1063.869</v>
       </c>
       <c r="F58" t="n">
-        <v>7393.036246000001</v>
+        <v>-0</v>
       </c>
       <c r="G58" t="n">
         <v>794.8797756535125</v>
@@ -51742,7 +51742,7 @@
         <v>1090.958</v>
       </c>
       <c r="F59" t="n">
-        <v>3743.059257030732</v>
+        <v>-0</v>
       </c>
       <c r="G59" t="n">
         <v>794.8797756535125</v>
@@ -51870,7 +51870,7 @@
         <v>1809.13124025</v>
       </c>
       <c r="U60" t="n">
-        <v>504.2686572403109</v>
+        <v>3371.196503475658</v>
       </c>
       <c r="V60" t="n">
         <v>1223.6722856992</v>
@@ -52036,7 +52036,7 @@
         <v>2627.0952</v>
       </c>
       <c r="U62" t="n">
-        <v>2866.927846235347</v>
+        <v>-0</v>
       </c>
       <c r="V62" t="n">
         <v>903.3745419468493</v>
@@ -52436,7 +52436,7 @@
         <v>963.3790000000001</v>
       </c>
       <c r="P67" t="n">
-        <v>1533.83664</v>
+        <v>-0</v>
       </c>
       <c r="Q67" t="n">
         <v>643.5368138561096</v>
@@ -52519,7 +52519,7 @@
         <v>971.005</v>
       </c>
       <c r="P68" t="n">
-        <v>-0</v>
+        <v>1533.83664</v>
       </c>
       <c r="Q68" t="n">
         <v>643.5368138561096</v>
@@ -52602,7 +52602,7 @@
         <v>969.5950000000001</v>
       </c>
       <c r="P69" t="n">
-        <v>1142.132674460203</v>
+        <v>1533.83664</v>
       </c>
       <c r="Q69" t="n">
         <v>643.5368138561096</v>
@@ -52685,7 +52685,7 @@
         <v>968.6360000000001</v>
       </c>
       <c r="P70" t="n">
-        <v>1533.83664</v>
+        <v>-0</v>
       </c>
       <c r="Q70" t="n">
         <v>643.5368138561096</v>
@@ -52851,7 +52851,7 @@
         <v>951.1529999999999</v>
       </c>
       <c r="P72" t="n">
-        <v>-0</v>
+        <v>1533.83664</v>
       </c>
       <c r="Q72" t="n">
         <v>643.5368138561096</v>
@@ -53598,7 +53598,7 @@
         <v>923.837</v>
       </c>
       <c r="P81" t="n">
-        <v>1533.83664</v>
+        <v>-0</v>
       </c>
       <c r="Q81" t="n">
         <v>643.5368138561096</v>
@@ -53764,7 +53764,7 @@
         <v>962.725</v>
       </c>
       <c r="P83" t="n">
-        <v>-0</v>
+        <v>1142.132674460202</v>
       </c>
       <c r="Q83" t="n">
         <v>643.5368138561096</v>
@@ -54398,7 +54398,7 @@
         <v>1105.734</v>
       </c>
       <c r="F91" t="n">
-        <v>5076.18095732357</v>
+        <v>-0</v>
       </c>
       <c r="G91" t="n">
         <v>794.8797756535125</v>
@@ -54481,7 +54481,7 @@
         <v>1120.51</v>
       </c>
       <c r="F92" t="n">
-        <v>-0</v>
+        <v>3813.457247456812</v>
       </c>
       <c r="G92" t="n">
         <v>794.8797756535125</v>
@@ -54730,7 +54730,7 @@
         <v>1150.062</v>
       </c>
       <c r="F95" t="n">
-        <v>-0</v>
+        <v>1262.723709866756</v>
       </c>
       <c r="G95" t="n">
         <v>794.8797756535125</v>
@@ -55824,7 +55824,7 @@
         <v>-0</v>
       </c>
       <c r="K108" t="n">
-        <v>10823.10621794033</v>
+        <v>12111.69536306516</v>
       </c>
       <c r="L108" t="n">
         <v>2803.749</v>
@@ -55851,7 +55851,7 @@
         <v>344.5481893617</v>
       </c>
       <c r="T108" t="n">
-        <v>2987.55441025</v>
+        <v>1698.965265125164</v>
       </c>
       <c r="U108" t="n">
         <v>-0</v>
@@ -55907,7 +55907,7 @@
         <v>2563.800547794086</v>
       </c>
       <c r="K109" t="n">
-        <v>3110.368677645951</v>
+        <v>2256.539532521115</v>
       </c>
       <c r="L109" t="n">
         <v>4989.2354</v>
@@ -55934,7 +55934,7 @@
         <v>1320.67427234043</v>
       </c>
       <c r="T109" t="n">
-        <v>1698.965265125164</v>
+        <v>2552.79441025</v>
       </c>
       <c r="U109" t="n">
         <v>-0</v>
@@ -56239,7 +56239,7 @@
         <v>5137.797260397982</v>
       </c>
       <c r="K113" t="n">
-        <v>3088.371560403943</v>
+        <v>2813.618395278108</v>
       </c>
       <c r="L113" t="n">
         <v>5564.3634</v>
@@ -56266,7 +56266,7 @@
         <v>1318.71265744681</v>
       </c>
       <c r="T113" t="n">
-        <v>1647.409224874164</v>
+        <v>1922.16239</v>
       </c>
       <c r="U113" t="n">
         <v>-0</v>
@@ -56322,7 +56322,7 @@
         <v>961.3168953001709</v>
       </c>
       <c r="K114" t="n">
-        <v>7370.046641781602</v>
+        <v>6660.533476655766</v>
       </c>
       <c r="L114" t="n">
         <v>3695.1974</v>
@@ -56349,7 +56349,7 @@
         <v>-0</v>
       </c>
       <c r="T114" t="n">
-        <v>1647.409224874164</v>
+        <v>2356.92239</v>
       </c>
       <c r="U114" t="n">
         <v>-0</v>
@@ -56426,7 +56426,7 @@
         <v>555.1391739626951</v>
       </c>
       <c r="R115" t="n">
-        <v>-0</v>
+        <v>2397.893040930913</v>
       </c>
       <c r="S115" t="n">
         <v>-0</v>
@@ -56509,7 +56509,7 @@
         <v>643.5368138561096</v>
       </c>
       <c r="R116" t="n">
-        <v>2591</v>
+        <v>-0</v>
       </c>
       <c r="S116" t="n">
         <v>-0</v>
@@ -56592,7 +56592,7 @@
         <v>643.5368138561096</v>
       </c>
       <c r="R117" t="n">
-        <v>1875.484049973681</v>
+        <v>1951.151519043654</v>
       </c>
       <c r="S117" t="n">
         <v>-0</v>
@@ -56728,7 +56728,7 @@
         <v>794.8797756535125</v>
       </c>
       <c r="H119" t="n">
-        <v>-0</v>
+        <v>5392.575992633191</v>
       </c>
       <c r="I119" t="n">
         <v>-0</v>
@@ -56758,7 +56758,7 @@
         <v>643.5368138561096</v>
       </c>
       <c r="R119" t="n">
-        <v>2429.356529661145</v>
+        <v>-0</v>
       </c>
       <c r="S119" t="n">
         <v>-0</v>
@@ -56841,7 +56841,7 @@
         <v>643.5368138561096</v>
       </c>
       <c r="R120" t="n">
-        <v>-0</v>
+        <v>2546.796019660261</v>
       </c>
       <c r="S120" t="n">
         <v>-0</v>
@@ -56894,7 +56894,7 @@
         <v>794.8797756535125</v>
       </c>
       <c r="H121" t="n">
-        <v>5392.575992633183</v>
+        <v>-0</v>
       </c>
       <c r="I121" t="n">
         <v>-0</v>
@@ -56998,7 +56998,7 @@
         <v>115.634</v>
       </c>
       <c r="O122" t="n">
-        <v>875.718</v>
+        <v>417.6048413399217</v>
       </c>
       <c r="P122" t="n">
         <v>-0</v>
@@ -57081,7 +57081,7 @@
         <v>95.60799999999999</v>
       </c>
       <c r="O123" t="n">
-        <v>867.949</v>
+        <v>109.7386413399317</v>
       </c>
       <c r="P123" t="n">
         <v>-0</v>
@@ -57330,7 +57330,7 @@
         <v>69.122</v>
       </c>
       <c r="O126" t="n">
-        <v>868.884</v>
+        <v>-0</v>
       </c>
       <c r="P126" t="n">
         <v>-0</v>
@@ -57496,7 +57496,7 @@
         <v>71.706</v>
       </c>
       <c r="O128" t="n">
-        <v>414.7338246246118</v>
+        <v>889.2630000000001</v>
       </c>
       <c r="P128" t="n">
         <v>-0</v>
@@ -57662,7 +57662,7 @@
         <v>71.06</v>
       </c>
       <c r="O130" t="n">
-        <v>-0</v>
+        <v>945.163</v>
       </c>
       <c r="P130" t="n">
         <v>-0</v>
@@ -57745,7 +57745,7 @@
         <v>76.22799999999999</v>
       </c>
       <c r="O131" t="n">
-        <v>39.67224133993193</v>
+        <v>947.8340000000001</v>
       </c>
       <c r="P131" t="n">
         <v>-0</v>
@@ -57899,7 +57899,7 @@
         <v>-0</v>
       </c>
       <c r="K133" t="n">
-        <v>3168.552275056932</v>
+        <v>9161.669633756039</v>
       </c>
       <c r="L133" t="n">
         <v>5017.9918</v>
@@ -57911,7 +57911,7 @@
         <v>85.27200000000001</v>
       </c>
       <c r="O133" t="n">
-        <v>943.711</v>
+        <v>293.5377694262424</v>
       </c>
       <c r="P133" t="n">
         <v>-0</v>
@@ -57982,7 +57982,7 @@
         <v>1745.975476635593</v>
       </c>
       <c r="K134" t="n">
-        <v>11739.36733782</v>
+        <v>3128.308274321251</v>
       </c>
       <c r="L134" t="n">
         <v>5909.4402</v>
@@ -57994,7 +57994,7 @@
         <v>96.90000000000002</v>
       </c>
       <c r="O134" t="n">
-        <v>544.2961861415492</v>
+        <v>951.823</v>
       </c>
       <c r="P134" t="n">
         <v>-0</v>
@@ -58148,7 +58148,7 @@
         <v>214.8692673201458</v>
       </c>
       <c r="K136" t="n">
-        <v>8788.639426123606</v>
+        <v>9829.415189580001</v>
       </c>
       <c r="L136" t="n">
         <v>5046.7482</v>
@@ -58258,7 +58258,7 @@
         <v>-0</v>
       </c>
       <c r="T137" t="n">
-        <v>1601.956469328378</v>
+        <v>2173.15944</v>
       </c>
       <c r="U137" t="n">
         <v>-0</v>
@@ -58341,7 +58341,7 @@
         <v>-0</v>
       </c>
       <c r="T138" t="n">
-        <v>1601.956469328378</v>
+        <v>2607.91944</v>
       </c>
       <c r="U138" t="n">
         <v>-0</v>
@@ -59310,7 +59310,7 @@
         <v>-0</v>
       </c>
       <c r="K150" t="n">
-        <v>8973.558292888461</v>
+        <v>8593.553412218949</v>
       </c>
       <c r="L150" t="n">
         <v>-0</v>
@@ -59337,7 +59337,7 @@
         <v>-0</v>
       </c>
       <c r="T150" t="n">
-        <v>1455.398903050488</v>
+        <v>1835.40378372</v>
       </c>
       <c r="U150" t="n">
         <v>-0</v>
@@ -59393,7 +59393,7 @@
         <v>-0</v>
       </c>
       <c r="K151" t="n">
-        <v>15783.07311424002</v>
+        <v>13783.84873827635</v>
       </c>
       <c r="L151" t="n">
         <v>-0</v>
@@ -59559,7 +59559,7 @@
         <v>-0</v>
       </c>
       <c r="K153" t="n">
-        <v>16096.86299403633</v>
+        <v>18096.08737</v>
       </c>
       <c r="L153" t="n">
         <v>-0</v>
@@ -59891,7 +59891,7 @@
         <v>-0</v>
       </c>
       <c r="K157" t="n">
-        <v>7883.3343506724</v>
+        <v>7883.334350678489</v>
       </c>
       <c r="L157" t="n">
         <v>1294.038</v>
@@ -59918,7 +59918,7 @@
         <v>-0</v>
       </c>
       <c r="T157" t="n">
-        <v>1639.11874025</v>
+        <v>1639.11874024391</v>
       </c>
       <c r="U157" t="n">
         <v>-0</v>
@@ -59974,7 +59974,7 @@
         <v>413.9205382782171</v>
       </c>
       <c r="K158" t="n">
-        <v>5348.967261752002</v>
+        <v>5348.967261758092</v>
       </c>
       <c r="L158" t="n">
         <v>2185.4864</v>
@@ -60001,7 +60001,7 @@
         <v>-0</v>
       </c>
       <c r="T158" t="n">
-        <v>1639.11874025</v>
+        <v>1639.11874024391</v>
       </c>
       <c r="U158" t="n">
         <v>-0</v>
@@ -60223,7 +60223,7 @@
         <v>2292.428999402101</v>
       </c>
       <c r="K161" t="n">
-        <v>3134.091288269944</v>
+        <v>6757.36355945606</v>
       </c>
       <c r="L161" t="n">
         <v>3048.1784</v>
@@ -60389,7 +60389,7 @@
         <v>-0</v>
       </c>
       <c r="K163" t="n">
-        <v>6737.839559456059</v>
+        <v>3114.567288269944</v>
       </c>
       <c r="L163" t="n">
         <v>1308.4162</v>
@@ -61027,13 +61027,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.092726157978177e-12</v>
+        <v>-3.637978807091713e-12</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -61073,13 +61073,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-6.821210263296962e-12</v>
+        <v>-3.183231456205249e-12</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -61096,7 +61096,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="C5" t="n">
         <v>6.821210263296962e-13</v>
@@ -61119,10 +61119,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.364242052659392e-12</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.13686837721616e-12</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -61188,10 +61188,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>3.183231456205249e-12</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -61211,7 +61211,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.364242052659392e-12</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="C10" t="n">
         <v>-2.273736754432321e-13</v>
@@ -61234,7 +61234,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.364242052659392e-12</v>
+        <v>-2.273736754432321e-12</v>
       </c>
       <c r="C11" t="n">
         <v>-2.273736754432321e-13</v>
@@ -61332,7 +61332,7 @@
         <v>-1.13686837721616e-12</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -61349,7 +61349,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="C16" t="n">
         <v>-9.094947017729282e-13</v>
@@ -61441,7 +61441,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -61533,13 +61533,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -61677,7 +61677,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -61694,7 +61694,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>-4.547473508864641e-13</v>
@@ -61740,7 +61740,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="C33" t="n">
         <v>4.547473508864641e-13</v>
@@ -61838,7 +61838,7 @@
         <v>-9.094947017729282e-13</v>
       </c>
       <c r="D37" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -61878,7 +61878,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>2.728484105318785e-12</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -61924,7 +61924,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>5.456968210637569e-12</v>
+        <v>-3.637978807091713e-12</v>
       </c>
       <c r="C41" t="n">
         <v>-4.547473508864641e-13</v>
@@ -61993,7 +61993,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-5.456968210637569e-12</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -62039,7 +62039,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-2.728484105318785e-12</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -62085,7 +62085,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>2.728484105318785e-12</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="C48" t="n">
         <v>4.547473508864641e-13</v>
@@ -62292,7 +62292,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>-2.728484105318785e-12</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -62361,7 +62361,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>-3.183231456205249e-12</v>
+        <v>-4.092726157978177e-12</v>
       </c>
       <c r="C60" t="n">
         <v>6.821210263296962e-13</v>
@@ -62407,7 +62407,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>5.002220859751105e-12</v>
+        <v>3.183231456205249e-12</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -62430,7 +62430,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>2.273736754432321e-12</v>
       </c>
       <c r="C63" t="n">
         <v>-4.547473508864641e-13</v>
@@ -62453,7 +62453,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>4.092726157978177e-12</v>
+        <v>2.273736754432321e-12</v>
       </c>
       <c r="C64" t="n">
         <v>-4.547473508864641e-13</v>
@@ -62522,13 +62522,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="C67" t="n">
         <v>9.094947017729282e-13</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -62545,13 +62545,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>4.547473508864641e-12</v>
+        <v>2.728484105318785e-12</v>
       </c>
       <c r="C68" t="n">
         <v>4.547473508864641e-13</v>
       </c>
       <c r="D68" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -62574,7 +62574,7 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -62597,7 +62597,7 @@
         <v>4.547473508864641e-13</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -62637,13 +62637,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -62850,7 +62850,7 @@
         <v>-4.547473508864641e-13</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -63468,7 +63468,7 @@
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>1.13686837721616e-12</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="D108" t="n">
         <v>4.547473508864641e-13</v>
@@ -63718,7 +63718,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="C119" t="n">
         <v>9.094947017729282e-13</v>
@@ -63747,7 +63747,7 @@
         <v>2.273736754432321e-13</v>
       </c>
       <c r="D120" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -63764,10 +63764,10 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>-4.547473508864641e-12</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="C121" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="D121" t="n">
         <v>-9.094947017729282e-13</v>
@@ -63885,7 +63885,7 @@
         <v>6.821210263296962e-13</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -63931,7 +63931,7 @@
         <v>6.821210263296962e-13</v>
       </c>
       <c r="D128" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
@@ -63977,7 +63977,7 @@
         <v>6.821210263296962e-13</v>
       </c>
       <c r="D130" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -63994,7 +63994,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
         <v>6.821210263296962e-13</v>
@@ -64043,10 +64043,10 @@
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="D133" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -64063,13 +64063,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>-1.591615728102624e-12</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="C134" t="n">
         <v>6.821210263296962e-13</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -64112,7 +64112,7 @@
         <v>-1.790567694115452e-12</v>
       </c>
       <c r="C136" t="n">
-        <v>1.13686837721616e-12</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="D136" t="n">
         <v>1.023181539494544e-12</v>
@@ -64135,7 +64135,7 @@
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>6.821210263296962e-13</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="D137" t="n">
         <v>2.273736754432321e-13</v>
@@ -64158,7 +64158,7 @@
         <v>2.728484105318785e-12</v>
       </c>
       <c r="C138" t="n">
-        <v>6.821210263296962e-13</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="D138" t="n">
         <v>4.547473508864641e-13</v>
@@ -64201,7 +64201,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="C140" t="n">
         <v>-4.547473508864641e-13</v>
@@ -64316,7 +64316,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="C145" t="n">
         <v>6.821210263296962e-13</v>
@@ -64434,7 +64434,7 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>6.821210263296962e-13</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -64454,10 +64454,10 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="C151" t="n">
-        <v>-1.13686837721616e-12</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="D151" t="n">
         <v>-4.547473508864641e-13</v>
@@ -64500,10 +64500,10 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="C153" t="n">
-        <v>-1.13686837721616e-12</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="D153" t="n">
         <v>4.547473508864641e-13</v>
@@ -64684,10 +64684,10 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>-6.821210263296962e-12</v>
+        <v>-8.640199666842818e-12</v>
       </c>
       <c r="C161" t="n">
-        <v>-6.821210263296962e-13</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="D161" t="n">
         <v>-4.547473508864641e-13</v>
@@ -64733,7 +64733,7 @@
         <v>1.818989403545856e-12</v>
       </c>
       <c r="C163" t="n">
-        <v>6.821210263296962e-13</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="D163" t="n">
         <v>-9.094947017729282e-13</v>
@@ -64848,7 +64848,7 @@
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -64977,46 +64977,46 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.63</v>
+        <v>73.7</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>18.63</v>
+        <v>73.7</v>
       </c>
       <c r="E2" t="n">
-        <v>18.63</v>
+        <v>73.7</v>
       </c>
       <c r="F2" t="n">
-        <v>18.53</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>18.73</v>
+        <v>73.80000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>18.53</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>18.73</v>
+        <v>73.80000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>15.63</v>
+        <v>70.7</v>
       </c>
       <c r="L2" t="n">
-        <v>18.83</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>18.73</v>
+        <v>73.80000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>18.63</v>
+        <v>73.7</v>
       </c>
       <c r="O2" t="n">
-        <v>18.63</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="3">
@@ -65465,7 +65465,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
@@ -65559,7 +65559,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
@@ -65653,7 +65653,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -65700,7 +65700,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
@@ -71698,7 +71698,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
@@ -71707,7 +71707,7 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -71798,7 +71798,7 @@
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="E147" t="n">
         <v>0.9999999999999999</v>
@@ -71810,7 +71810,7 @@
         <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>0.9</v>
+        <v>0.8999999999999998</v>
       </c>
       <c r="I147" t="n">
         <v>1</v>
@@ -71828,10 +71828,10 @@
         <v>1.1</v>
       </c>
       <c r="N147" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="O147" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -71839,7 +71839,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
@@ -71848,7 +71848,7 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F148" t="n">
         <v>1</v>
@@ -72797,7 +72797,7 @@
         <v>1</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1243998646227791</v>
+        <v>0.3243998646227791</v>
       </c>
       <c r="I168" t="n">
         <v>2</v>
@@ -73009,7 +73009,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-3237.020229057701</v>
+        <v>-0</v>
       </c>
       <c r="C12" t="n">
         <v>4613</v>
@@ -73020,7 +73020,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-0</v>
+        <v>-6469.418523057303</v>
       </c>
       <c r="C13" t="n">
         <v>3484.00376827</v>
@@ -73064,7 +73064,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-10423.35</v>
+        <v>-0</v>
       </c>
       <c r="C17" t="n">
         <v>4613</v>
@@ -74219,7 +74219,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>-465.6789319246764</v>
+        <v>2117.321068075324</v>
       </c>
       <c r="C122" t="n">
         <v>4613</v>
@@ -74230,7 +74230,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>-2156.698431070829</v>
+        <v>-0</v>
       </c>
       <c r="C123" t="n">
         <v>4613</v>
@@ -74318,7 +74318,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>-5563.69374831</v>
+        <v>-4848.950616217697</v>
       </c>
       <c r="C131" t="n">
         <v>4613</v>
@@ -74417,7 +74417,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>-2897.4</v>
+        <v>10447.41</v>
       </c>
       <c r="C140" t="n">
         <v>4613</v>
@@ -74461,7 +74461,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>5005.802096916634</v>
+        <v>1649.325494279837</v>
       </c>
       <c r="C144" t="n">
         <v>4613</v>
@@ -74472,10 +74472,10 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>467.4866285078569</v>
+        <v>-2897.4</v>
       </c>
       <c r="C145" t="n">
-        <v>3821.18803715</v>
+        <v>2565.74494346759</v>
       </c>
     </row>
     <row r="146">
@@ -74497,7 +74497,7 @@
         <v>-13320.75</v>
       </c>
       <c r="C147" t="n">
-        <v>-795.9433896049917</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="148">
@@ -74505,10 +74505,10 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>-10788.78388841773</v>
+        <v>-13320.75</v>
       </c>
       <c r="C148" t="n">
-        <v>-0</v>
+        <v>-2470.59299257951</v>
       </c>
     </row>
     <row r="149">
@@ -74519,7 +74519,7 @@
         <v>-13320.75</v>
       </c>
       <c r="C149" t="n">
-        <v>-2286.319388447299</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="150">
@@ -74541,7 +74541,7 @@
         <v>-13320.75</v>
       </c>
       <c r="C151" t="n">
-        <v>-2358.578311851559</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="152">
@@ -74552,7 +74552,7 @@
         <v>-13320.75</v>
       </c>
       <c r="C152" t="n">
-        <v>-2244.796503340918</v>
+        <v>-1490.192510148008</v>
       </c>
     </row>
     <row r="153">
@@ -74563,7 +74563,7 @@
         <v>-13320.75</v>
       </c>
       <c r="C153" t="n">
-        <v>-0</v>
+        <v>-2469.408996834839</v>
       </c>
     </row>
     <row r="154">
@@ -74883,7 +74883,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18345161.42022905</v>
+        <v>18341924.4</v>
       </c>
       <c r="C12" t="n">
         <v>2926097</v>
@@ -74894,7 +74894,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18345161.42022905</v>
+        <v>18348393.81852306</v>
       </c>
       <c r="C13" t="n">
         <v>2922612.99623173</v>
@@ -74905,7 +74905,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>18355584.77022906</v>
+        <v>18358817.16852306</v>
       </c>
       <c r="C14" t="n">
         <v>2917999.99623173</v>
@@ -74916,7 +74916,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>18355584.77022906</v>
+        <v>18358817.16852306</v>
       </c>
       <c r="C15" t="n">
         <v>2913461.86873811</v>
@@ -74927,7 +74927,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>18355584.77022906</v>
+        <v>18358817.16852306</v>
       </c>
       <c r="C16" t="n">
         <v>2908983.38992443</v>
@@ -74938,7 +74938,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18366008.12022906</v>
+        <v>18358817.16852306</v>
       </c>
       <c r="C17" t="n">
         <v>2904370.38992443</v>
@@ -74949,7 +74949,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>18363631.09597213</v>
+        <v>18356440.14426613</v>
       </c>
       <c r="C18" t="n">
         <v>2899757.38992443</v>
@@ -74960,7 +74960,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>18359457.13311021</v>
+        <v>18352266.18140421</v>
       </c>
       <c r="C19" t="n">
         <v>2895144.38992443</v>
@@ -74971,7 +74971,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>18345853.15311021</v>
+        <v>18338662.20140421</v>
       </c>
       <c r="C20" t="n">
         <v>2890531.38992443</v>
@@ -74982,7 +74982,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18342696.58311021</v>
+        <v>18335505.63140421</v>
       </c>
       <c r="C21" t="n">
         <v>2885918.38992443</v>
@@ -74993,7 +74993,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>18329092.60311021</v>
+        <v>18321901.65140421</v>
       </c>
       <c r="C22" t="n">
         <v>2881305.38992443</v>
@@ -75004,7 +75004,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>18321565.92862058</v>
+        <v>18314374.97691458</v>
       </c>
       <c r="C23" t="n">
         <v>2876692.38992443</v>
@@ -75015,7 +75015,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>18316507.78421589</v>
+        <v>18309316.83250989</v>
       </c>
       <c r="C24" t="n">
         <v>2872079.38992443</v>
@@ -75026,7 +75026,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>18313351.21421589</v>
+        <v>18306160.26250989</v>
       </c>
       <c r="C25" t="n">
         <v>2867466.38992443</v>
@@ -75037,7 +75037,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>18310194.64421589</v>
+        <v>18303003.69250989</v>
       </c>
       <c r="C26" t="n">
         <v>2862853.38992443</v>
@@ -75048,7 +75048,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>18307038.07421589</v>
+        <v>18299847.12250989</v>
       </c>
       <c r="C27" t="n">
         <v>2858240.38992443</v>
@@ -75059,7 +75059,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>18303881.50421588</v>
+        <v>18296690.55250989</v>
       </c>
       <c r="C28" t="n">
         <v>2853627.38992443</v>
@@ -75070,7 +75070,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>18300724.93421588</v>
+        <v>18293533.98250988</v>
       </c>
       <c r="C29" t="n">
         <v>2849014.38992443</v>
@@ -75081,7 +75081,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>18297568.36421588</v>
+        <v>18290377.41250988</v>
       </c>
       <c r="C30" t="n">
         <v>2844401.38992443</v>
@@ -75092,7 +75092,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>18294411.79421588</v>
+        <v>18287220.84250988</v>
       </c>
       <c r="C31" t="n">
         <v>2839788.38992443</v>
@@ -75103,7 +75103,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>18291255.22421588</v>
+        <v>18284064.27250988</v>
       </c>
       <c r="C32" t="n">
         <v>2835175.38992443</v>
@@ -75114,7 +75114,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>18277651.24421588</v>
+        <v>18270460.29250988</v>
       </c>
       <c r="C33" t="n">
         <v>2830562.38992443</v>
@@ -75125,7 +75125,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>18264047.26421588</v>
+        <v>18256856.31250988</v>
       </c>
       <c r="C34" t="n">
         <v>2825949.38992443</v>
@@ -75136,7 +75136,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>18257998.75282864</v>
+        <v>18250807.80112264</v>
       </c>
       <c r="C35" t="n">
         <v>2821336.38992443</v>
@@ -75147,7 +75147,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>18254842.18282864</v>
+        <v>18247651.23112264</v>
       </c>
       <c r="C36" t="n">
         <v>2816723.38992443</v>
@@ -75158,7 +75158,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>18251685.61282864</v>
+        <v>18244494.66112264</v>
       </c>
       <c r="C37" t="n">
         <v>2812110.38992443</v>
@@ -75169,7 +75169,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>18248529.04282864</v>
+        <v>18241338.09112264</v>
       </c>
       <c r="C38" t="n">
         <v>2807497.38992443</v>
@@ -75180,7 +75180,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>18248529.04282864</v>
+        <v>18241338.09112264</v>
       </c>
       <c r="C39" t="n">
         <v>2802884.38992443</v>
@@ -75191,7 +75191,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>18245372.47282864</v>
+        <v>18238181.52112264</v>
       </c>
       <c r="C40" t="n">
         <v>2798271.38992443</v>
@@ -75202,7 +75202,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>18245372.47282864</v>
+        <v>18238181.52112264</v>
       </c>
       <c r="C41" t="n">
         <v>2793658.38992443</v>
@@ -75213,7 +75213,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>18242215.90282864</v>
+        <v>18235024.95112264</v>
       </c>
       <c r="C42" t="n">
         <v>2789045.38992443</v>
@@ -75224,7 +75224,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>18228611.92282864</v>
+        <v>18221420.97112264</v>
       </c>
       <c r="C43" t="n">
         <v>2784432.38992443</v>
@@ -75235,7 +75235,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>18215007.94282864</v>
+        <v>18207816.99112264</v>
       </c>
       <c r="C44" t="n">
         <v>2779819.38992443</v>
@@ -75246,7 +75246,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>18201403.96282864</v>
+        <v>18194213.01112264</v>
       </c>
       <c r="C45" t="n">
         <v>2775206.38992443</v>
@@ -75257,7 +75257,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>18189156.0955075</v>
+        <v>18181965.1438015</v>
       </c>
       <c r="C46" t="n">
         <v>2770593.38992443</v>
@@ -75268,7 +75268,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>18185999.5255075</v>
+        <v>18178808.5738015</v>
       </c>
       <c r="C47" t="n">
         <v>2765980.38992443</v>
@@ -75279,7 +75279,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>18177615.74497099</v>
+        <v>18170424.79326499</v>
       </c>
       <c r="C48" t="n">
         <v>2761367.38992443</v>
@@ -75290,7 +75290,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>18174459.17497099</v>
+        <v>18167268.22326499</v>
       </c>
       <c r="C49" t="n">
         <v>2756754.38992443</v>
@@ -75301,7 +75301,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>18171302.60497099</v>
+        <v>18164111.65326499</v>
       </c>
       <c r="C50" t="n">
         <v>2752141.38992443</v>
@@ -75312,7 +75312,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>18168146.03497099</v>
+        <v>18160955.08326499</v>
       </c>
       <c r="C51" t="n">
         <v>2747528.38992443</v>
@@ -75323,7 +75323,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>18164989.46497099</v>
+        <v>18157798.51326499</v>
       </c>
       <c r="C52" t="n">
         <v>2742915.38992443</v>
@@ -75334,7 +75334,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>18161832.89497099</v>
+        <v>18154641.94326499</v>
       </c>
       <c r="C53" t="n">
         <v>2738302.38992443</v>
@@ -75345,7 +75345,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>18158676.32497099</v>
+        <v>18151485.37326499</v>
       </c>
       <c r="C54" t="n">
         <v>2733689.38992443</v>
@@ -75356,7 +75356,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>18152672.21053415</v>
+        <v>18145481.25882815</v>
       </c>
       <c r="C55" t="n">
         <v>2729076.38992443</v>
@@ -75367,7 +75367,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>18140288.94735121</v>
+        <v>18133097.99564521</v>
       </c>
       <c r="C56" t="n">
         <v>2724463.38992443</v>
@@ -75378,7 +75378,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>18135643.15010447</v>
+        <v>18128452.19839847</v>
       </c>
       <c r="C57" t="n">
         <v>2719850.38992443</v>
@@ -75389,7 +75389,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>18122039.17010447</v>
+        <v>18114848.21839847</v>
       </c>
       <c r="C58" t="n">
         <v>2715237.38992443</v>
@@ -75400,7 +75400,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>18112957.18785365</v>
+        <v>18105766.23614765</v>
       </c>
       <c r="C59" t="n">
         <v>2710624.38992443</v>
@@ -75411,7 +75411,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>18109800.61785365</v>
+        <v>18102609.66614765</v>
       </c>
       <c r="C60" t="n">
         <v>2706011.38992443</v>
@@ -75422,7 +75422,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>18106644.04785364</v>
+        <v>18099453.09614765</v>
       </c>
       <c r="C61" t="n">
         <v>2701398.38992443</v>
@@ -75433,7 +75433,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>18103487.47785364</v>
+        <v>18096296.52614764</v>
       </c>
       <c r="C62" t="n">
         <v>2696785.38992443</v>
@@ -75444,7 +75444,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>18100330.90785364</v>
+        <v>18093139.95614764</v>
       </c>
       <c r="C63" t="n">
         <v>2692172.38992443</v>
@@ -75455,7 +75455,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>18097174.33785364</v>
+        <v>18089983.38614764</v>
       </c>
       <c r="C64" t="n">
         <v>2687559.38992443</v>
@@ -75466,7 +75466,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>18094017.76785364</v>
+        <v>18086826.81614764</v>
       </c>
       <c r="C65" t="n">
         <v>2682946.38992443</v>
@@ -75477,7 +75477,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>18090861.19785364</v>
+        <v>18083670.24614764</v>
       </c>
       <c r="C66" t="n">
         <v>2678333.38992443</v>
@@ -75488,7 +75488,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>18077257.21785364</v>
+        <v>18070066.26614764</v>
       </c>
       <c r="C67" t="n">
         <v>2673720.38992443</v>
@@ -75499,7 +75499,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>18063653.23785364</v>
+        <v>18056462.28614764</v>
       </c>
       <c r="C68" t="n">
         <v>2669107.38992443</v>
@@ -75510,7 +75510,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>18050049.25785364</v>
+        <v>18042858.30614764</v>
       </c>
       <c r="C69" t="n">
         <v>2664494.38992443</v>
@@ -75521,7 +75521,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>18036445.27785364</v>
+        <v>18029254.32614764</v>
       </c>
       <c r="C70" t="n">
         <v>2659881.38992443</v>
@@ -75532,7 +75532,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>18022841.29785364</v>
+        <v>18015650.34614764</v>
       </c>
       <c r="C71" t="n">
         <v>2655268.38992443</v>
@@ -75543,7 +75543,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>18009237.31785364</v>
+        <v>18002046.36614764</v>
       </c>
       <c r="C72" t="n">
         <v>2650655.38992443</v>
@@ -75554,7 +75554,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>17995633.33785364</v>
+        <v>17988442.38614764</v>
       </c>
       <c r="C73" t="n">
         <v>2646042.38992443</v>
@@ -75565,7 +75565,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>17985455.61711305</v>
+        <v>17978264.66540705</v>
       </c>
       <c r="C74" t="n">
         <v>2641429.38992443</v>
@@ -75576,7 +75576,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>17976463.87876848</v>
+        <v>17969272.92706248</v>
       </c>
       <c r="C75" t="n">
         <v>2636816.38992443</v>
@@ -75587,7 +75587,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>17969523.19811327</v>
+        <v>17962332.24640727</v>
       </c>
       <c r="C76" t="n">
         <v>2632203.38992443</v>
@@ -75598,7 +75598,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>17963146.17266766</v>
+        <v>17955955.22096166</v>
       </c>
       <c r="C77" t="n">
         <v>2627590.38992443</v>
@@ -75609,7 +75609,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>17956361.34001537</v>
+        <v>17949170.38830937</v>
       </c>
       <c r="C78" t="n">
         <v>2622977.38992443</v>
@@ -75620,7 +75620,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>17945977.78106239</v>
+        <v>17938786.82935639</v>
       </c>
       <c r="C79" t="n">
         <v>2618364.38992443</v>
@@ -75631,7 +75631,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>17932373.80106239</v>
+        <v>17925182.84935639</v>
       </c>
       <c r="C80" t="n">
         <v>2613751.38992443</v>
@@ -75642,7 +75642,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>17918769.82106239</v>
+        <v>17911578.86935639</v>
       </c>
       <c r="C81" t="n">
         <v>2609138.38992443</v>
@@ -75653,7 +75653,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>17905165.84106239</v>
+        <v>17897974.88935639</v>
       </c>
       <c r="C82" t="n">
         <v>2604525.38992443</v>
@@ -75664,7 +75664,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>17896550.28369762</v>
+        <v>17889359.33199162</v>
       </c>
       <c r="C83" t="n">
         <v>2599912.38992443</v>
@@ -75675,7 +75675,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>17893393.71369762</v>
+        <v>17886202.76199162</v>
       </c>
       <c r="C84" t="n">
         <v>2595299.38992443</v>
@@ -75686,7 +75686,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>17893393.71369762</v>
+        <v>17886202.76199162</v>
       </c>
       <c r="C85" t="n">
         <v>2590686.38992443</v>
@@ -75697,7 +75697,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>17890642.86531454</v>
+        <v>17883451.91360854</v>
       </c>
       <c r="C86" t="n">
         <v>2586073.38992443</v>
@@ -75708,7 +75708,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>17890642.86531454</v>
+        <v>17883451.91360854</v>
       </c>
       <c r="C87" t="n">
         <v>2581460.38992443</v>
@@ -75719,7 +75719,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>17890642.86531454</v>
+        <v>17883451.91360854</v>
       </c>
       <c r="C88" t="n">
         <v>2576847.38992443</v>
@@ -75730,7 +75730,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>17890642.86531454</v>
+        <v>17883451.91360854</v>
       </c>
       <c r="C89" t="n">
         <v>2572234.38992443</v>
@@ -75741,7 +75741,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>17890642.86531454</v>
+        <v>17883451.91360854</v>
       </c>
       <c r="C90" t="n">
         <v>2567621.38992443</v>
@@ -75752,7 +75752,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>17887486.29531454</v>
+        <v>17880295.34360854</v>
       </c>
       <c r="C91" t="n">
         <v>2563008.38992443</v>
@@ -75763,7 +75763,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>17884329.72531454</v>
+        <v>17877138.77360854</v>
       </c>
       <c r="C92" t="n">
         <v>2558395.38992443</v>
@@ -75774,7 +75774,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>17881173.15531454</v>
+        <v>17873982.20360854</v>
       </c>
       <c r="C93" t="n">
         <v>2553782.38992443</v>
@@ -75785,7 +75785,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>17877995.91124761</v>
+        <v>17870804.95954161</v>
       </c>
       <c r="C94" t="n">
         <v>2549169.38992443</v>
@@ -75796,7 +75796,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>17873832.46879983</v>
+        <v>17866641.51709383</v>
       </c>
       <c r="C95" t="n">
         <v>2544556.38992443</v>
@@ -75807,7 +75807,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>17870675.89879983</v>
+        <v>17863484.94709383</v>
       </c>
       <c r="C96" t="n">
         <v>2539943.38992443</v>
@@ -75818,7 +75818,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>17870675.89879983</v>
+        <v>17863484.94709383</v>
       </c>
       <c r="C97" t="n">
         <v>2535330.38992443</v>
@@ -75829,7 +75829,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>17870675.89879983</v>
+        <v>17863484.94709383</v>
       </c>
       <c r="C98" t="n">
         <v>2530717.38992443</v>
@@ -75840,7 +75840,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>17870675.89879983</v>
+        <v>17863484.94709383</v>
       </c>
       <c r="C99" t="n">
         <v>2526104.38992443</v>
@@ -75851,7 +75851,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>17870675.89879983</v>
+        <v>17863484.94709383</v>
       </c>
       <c r="C100" t="n">
         <v>2521491.38992443</v>
@@ -75862,7 +75862,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>17870675.89879983</v>
+        <v>17863484.94709383</v>
       </c>
       <c r="C101" t="n">
         <v>2516878.38992443</v>
@@ -75873,7 +75873,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>17870675.89879983</v>
+        <v>17863484.94709383</v>
       </c>
       <c r="C102" t="n">
         <v>2512265.38992443</v>
@@ -75884,7 +75884,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>17870675.89879983</v>
+        <v>17863484.94709383</v>
       </c>
       <c r="C103" t="n">
         <v>2507652.38992443</v>
@@ -75895,7 +75895,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>17870675.89879983</v>
+        <v>17863484.94709383</v>
       </c>
       <c r="C104" t="n">
         <v>2503039.38992443</v>
@@ -75906,7 +75906,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>17870675.89879983</v>
+        <v>17863484.94709383</v>
       </c>
       <c r="C105" t="n">
         <v>2498426.38992443</v>
@@ -75917,7 +75917,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>17870675.89879983</v>
+        <v>17863484.94709383</v>
       </c>
       <c r="C106" t="n">
         <v>2493813.38992443</v>
@@ -75928,7 +75928,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>17871681.1785499</v>
+        <v>17864490.2268439</v>
       </c>
       <c r="C107" t="n">
         <v>2491116.57572865</v>
@@ -75939,7 +75939,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>17885001.9285499</v>
+        <v>17877810.9768439</v>
       </c>
       <c r="C108" t="n">
         <v>2491116.57572865</v>
@@ -75950,7 +75950,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>17898322.6785499</v>
+        <v>17891131.7268439</v>
       </c>
       <c r="C109" t="n">
         <v>2491116.57572865</v>
@@ -75961,7 +75961,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>17911643.4285499</v>
+        <v>17904452.4768439</v>
       </c>
       <c r="C110" t="n">
         <v>2491116.57572865</v>
@@ -75972,7 +75972,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>17924964.1785499</v>
+        <v>17917773.2268439</v>
       </c>
       <c r="C111" t="n">
         <v>2491430.281993693</v>
@@ -75983,7 +75983,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>17938284.9285499</v>
+        <v>17931093.9768439</v>
       </c>
       <c r="C112" t="n">
         <v>2491724.373280013</v>
@@ -75994,7 +75994,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>17951605.6785499</v>
+        <v>17944414.7268439</v>
       </c>
       <c r="C113" t="n">
         <v>2491724.373280013</v>
@@ -76005,7 +76005,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>17964926.4285499</v>
+        <v>17957735.4768439</v>
       </c>
       <c r="C114" t="n">
         <v>2491724.373280013</v>
@@ -76016,7 +76016,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>17964926.4285499</v>
+        <v>17957735.4768439</v>
       </c>
       <c r="C115" t="n">
         <v>2487111.373280013</v>
@@ -76027,7 +76027,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>17964926.4285499</v>
+        <v>17957735.4768439</v>
       </c>
       <c r="C116" t="n">
         <v>2482498.373280013</v>
@@ -76038,7 +76038,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>17957597.62150288</v>
+        <v>17950406.66979688</v>
       </c>
       <c r="C117" t="n">
         <v>2477885.373280013</v>
@@ -76049,7 +76049,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>17951880.21621902</v>
+        <v>17944689.26451302</v>
       </c>
       <c r="C118" t="n">
         <v>2473272.373280013</v>
@@ -76060,7 +76060,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>17951880.21621902</v>
+        <v>17944689.26451302</v>
       </c>
       <c r="C119" t="n">
         <v>2468659.373280013</v>
@@ -76071,7 +76071,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>17947384.99367891</v>
+        <v>17940194.04197291</v>
       </c>
       <c r="C120" t="n">
         <v>2464046.373280013</v>
@@ -76082,7 +76082,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>17942649.33806644</v>
+        <v>17935458.38636044</v>
       </c>
       <c r="C121" t="n">
         <v>2459433.373280013</v>
@@ -76093,7 +76093,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>17943115.01699836</v>
+        <v>17933341.06529236</v>
       </c>
       <c r="C122" t="n">
         <v>2454820.373280013</v>
@@ -76104,7 +76104,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>17945271.71542943</v>
+        <v>17933341.06529236</v>
       </c>
       <c r="C123" t="n">
         <v>2450207.373280013</v>
@@ -76115,7 +76115,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>17947736.04155459</v>
+        <v>17935805.39141752</v>
       </c>
       <c r="C124" t="n">
         <v>2445594.373280013</v>
@@ -76126,7 +76126,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>17949678.98402704</v>
+        <v>17937748.33388997</v>
       </c>
       <c r="C125" t="n">
         <v>2440981.373280013</v>
@@ -76137,7 +76137,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>17951805.70875048</v>
+        <v>17939875.0586134</v>
       </c>
       <c r="C126" t="n">
         <v>2436368.373280013</v>
@@ -76148,7 +76148,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>17954549.89697255</v>
+        <v>17942619.24683548</v>
       </c>
       <c r="C127" t="n">
         <v>2431755.373280013</v>
@@ -76159,7 +76159,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>17954689.87016824</v>
+        <v>17942759.22003116</v>
       </c>
       <c r="C128" t="n">
         <v>2427142.373280013</v>
@@ -76170,7 +76170,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>17951956.13217064</v>
+        <v>17940025.48203357</v>
       </c>
       <c r="C129" t="n">
         <v>2422529.373280013</v>
@@ -76181,7 +76181,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>17941508.72217064</v>
+        <v>17929578.07203357</v>
       </c>
       <c r="C130" t="n">
         <v>2417916.373280013</v>
@@ -76192,7 +76192,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>17947072.41591895</v>
+        <v>17934427.02264979</v>
       </c>
       <c r="C131" t="n">
         <v>2413303.373280013</v>
@@ -76203,7 +76203,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>17960393.16591895</v>
+        <v>17947747.77264979</v>
       </c>
       <c r="C132" t="n">
         <v>2412371.373488523</v>
@@ -76214,7 +76214,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>17973713.91591895</v>
+        <v>17961068.52264979</v>
       </c>
       <c r="C133" t="n">
         <v>2407758.373488523</v>
@@ -76225,7 +76225,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>17987034.66591895</v>
+        <v>17974389.27264979</v>
       </c>
       <c r="C134" t="n">
         <v>2404973.265486393</v>
@@ -76236,7 +76236,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>18000355.41591895</v>
+        <v>17987710.02264979</v>
       </c>
       <c r="C135" t="n">
         <v>2404973.265486393</v>
@@ -76247,7 +76247,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>18013676.16591895</v>
+        <v>18001030.77264979</v>
       </c>
       <c r="C136" t="n">
         <v>2404973.265486393</v>
@@ -76258,7 +76258,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>18026996.91591895</v>
+        <v>18014351.52264979</v>
       </c>
       <c r="C137" t="n">
         <v>2404973.265486393</v>
@@ -76269,7 +76269,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>18040317.66591895</v>
+        <v>18027672.27264979</v>
       </c>
       <c r="C138" t="n">
         <v>2404973.265486393</v>
@@ -76280,7 +76280,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>18032419.2598551</v>
+        <v>18019773.86658594</v>
       </c>
       <c r="C139" t="n">
         <v>2400360.265486393</v>
@@ -76291,7 +76291,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>18035316.6598551</v>
+        <v>18009326.45658594</v>
       </c>
       <c r="C140" t="n">
         <v>2395747.265486393</v>
@@ -76302,7 +76302,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>18024869.2498551</v>
+        <v>17998879.04658594</v>
       </c>
       <c r="C141" t="n">
         <v>2391134.265486393</v>
@@ -76313,7 +76313,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>18014421.8398551</v>
+        <v>17988431.63658594</v>
       </c>
       <c r="C142" t="n">
         <v>2386521.265486393</v>
@@ -76324,7 +76324,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>18003974.4298551</v>
+        <v>17977984.22658594</v>
       </c>
       <c r="C143" t="n">
         <v>2383062.868056603</v>
@@ -76335,7 +76335,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>17998968.62775818</v>
+        <v>17976334.90109166</v>
       </c>
       <c r="C144" t="n">
         <v>2378449.868056603</v>
@@ -76346,10 +76346,10 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>17998501.14112968</v>
+        <v>17979232.30109166</v>
       </c>
       <c r="C145" t="n">
-        <v>2374628.680019453</v>
+        <v>2375884.123113135</v>
       </c>
     </row>
     <row r="146">
@@ -76357,10 +76357,10 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>18001398.54112967</v>
+        <v>17982129.70109166</v>
       </c>
       <c r="C146" t="n">
-        <v>2374628.680019453</v>
+        <v>2375884.123113135</v>
       </c>
     </row>
     <row r="147">
@@ -76368,10 +76368,10 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>18014719.29112967</v>
+        <v>17995450.45109166</v>
       </c>
       <c r="C147" t="n">
-        <v>2375424.623409058</v>
+        <v>2375884.123113135</v>
       </c>
     </row>
     <row r="148">
@@ -76379,10 +76379,10 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>18025508.07501809</v>
+        <v>18008771.20109166</v>
       </c>
       <c r="C148" t="n">
-        <v>2375424.623409058</v>
+        <v>2378354.716105715</v>
       </c>
     </row>
     <row r="149">
@@ -76390,10 +76390,10 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>18038828.82501809</v>
+        <v>18022091.95109166</v>
       </c>
       <c r="C149" t="n">
-        <v>2377710.942797505</v>
+        <v>2378354.716105715</v>
       </c>
     </row>
     <row r="150">
@@ -76401,10 +76401,10 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>18052149.57501809</v>
+        <v>18035412.70109166</v>
       </c>
       <c r="C150" t="n">
-        <v>2380554.095645403</v>
+        <v>2381197.868953614</v>
       </c>
     </row>
     <row r="151">
@@ -76412,10 +76412,10 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>18065470.32501809</v>
+        <v>18048733.45109166</v>
       </c>
       <c r="C151" t="n">
-        <v>2382912.673957255</v>
+        <v>2381197.868953614</v>
       </c>
     </row>
     <row r="152">
@@ -76423,10 +76423,10 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>18078791.07501809</v>
+        <v>18062054.20109166</v>
       </c>
       <c r="C152" t="n">
-        <v>2385157.470460596</v>
+        <v>2382688.061463762</v>
       </c>
     </row>
     <row r="153">
@@ -76434,7 +76434,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>18092111.82501809</v>
+        <v>18075374.95109166</v>
       </c>
       <c r="C153" t="n">
         <v>2385157.470460596</v>
@@ -76445,7 +76445,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>18095009.22501809</v>
+        <v>18078272.35109166</v>
       </c>
       <c r="C154" t="n">
         <v>2385157.470460596</v>
@@ -76456,7 +76456,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>18097906.62501809</v>
+        <v>18081169.75109166</v>
       </c>
       <c r="C155" t="n">
         <v>2385157.470460596</v>
@@ -76467,7 +76467,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>18111227.37501809</v>
+        <v>18094490.50109166</v>
       </c>
       <c r="C156" t="n">
         <v>2385157.470460596</v>
@@ -76478,7 +76478,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>18124548.12501809</v>
+        <v>18107811.25109166</v>
       </c>
       <c r="C157" t="n">
         <v>2385157.470460596</v>
@@ -76489,7 +76489,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>18137868.87501809</v>
+        <v>18121132.00109166</v>
       </c>
       <c r="C158" t="n">
         <v>2385157.470460596</v>
@@ -76500,7 +76500,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>18151189.62501809</v>
+        <v>18134452.75109166</v>
       </c>
       <c r="C159" t="n">
         <v>2385157.470460596</v>
@@ -76511,7 +76511,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>18164510.37501809</v>
+        <v>18147773.50109166</v>
       </c>
       <c r="C160" t="n">
         <v>2385157.470460596</v>
@@ -76522,7 +76522,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>18177831.12501809</v>
+        <v>18161094.25109166</v>
       </c>
       <c r="C161" t="n">
         <v>2385157.470460596</v>
@@ -76533,7 +76533,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>18191151.87501809</v>
+        <v>18174415.00109166</v>
       </c>
       <c r="C162" t="n">
         <v>2385157.470460596</v>
@@ -76544,7 +76544,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>18194049.27501809</v>
+        <v>18177312.40109165</v>
       </c>
       <c r="C163" t="n">
         <v>2385157.470460596</v>
@@ -76555,7 +76555,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>18196946.67501809</v>
+        <v>18180209.80109165</v>
       </c>
       <c r="C164" t="n">
         <v>2383092.500304766</v>
@@ -76566,7 +76566,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>18210267.42501809</v>
+        <v>18193530.55109165</v>
       </c>
       <c r="C165" t="n">
         <v>2378479.500304766</v>
@@ -76577,7 +76577,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>18223588.17501809</v>
+        <v>18206851.30109165</v>
       </c>
       <c r="C166" t="n">
         <v>2374479.584709026</v>
@@ -76588,7 +76588,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>18236908.92501809</v>
+        <v>18220172.05109165</v>
       </c>
       <c r="C167" t="n">
         <v>2372019.380679236</v>
@@ -76599,7 +76599,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>18250229.67501809</v>
+        <v>18233492.80109165</v>
       </c>
       <c r="C168" t="n">
         <v>2367406.380679236</v>
@@ -76610,7 +76610,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>18263550.42501809</v>
+        <v>18246813.55109165</v>
       </c>
       <c r="C169" t="n">
         <v>2366018.108326046</v>
@@ -76658,7 +76658,7 @@
         <v>2583</v>
       </c>
       <c r="D2" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -76680,13 +76680,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2831.128857310512</v>
       </c>
       <c r="C4" t="n">
         <v>2583</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1238.99706261653</v>
       </c>
     </row>
     <row r="5">
@@ -76700,7 +76700,7 @@
         <v>2583</v>
       </c>
       <c r="D5" t="n">
-        <v>138.5922563735921</v>
+        <v>909.4297509402186</v>
       </c>
     </row>
     <row r="6">
@@ -76714,7 +76714,7 @@
         <v>2583</v>
       </c>
       <c r="D6" t="n">
-        <v>837.051557482518</v>
+        <v>1827.217000299361</v>
       </c>
     </row>
     <row r="7">
@@ -76750,7 +76750,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7584.875425402002</v>
+        <v>5141.295927790364</v>
       </c>
       <c r="C9" t="n">
         <v>2583</v>
@@ -76764,7 +76764,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>12765.6919006769</v>
+        <v>14582.37093477142</v>
       </c>
       <c r="C10" t="n">
         <v>2583</v>
@@ -76778,7 +76778,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2204.228393793393</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>2583</v>
@@ -76792,10 +76792,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-2298.191051888389</v>
+        <v>-2952.21128094609</v>
       </c>
       <c r="C12" t="n">
-        <v>2583</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>-855.5462565324092</v>
@@ -76806,10 +76806,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-11318.1968748879</v>
+        <v>-2413.003459576957</v>
       </c>
       <c r="C13" t="n">
-        <v>2435.774892253643</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>-1246.256912036459</v>
@@ -76820,10 +76820,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-7282.687464226188</v>
+        <v>-6748.902854721528</v>
       </c>
       <c r="C14" t="n">
-        <v>533.7846095046607</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>-3000</v>
@@ -76840,7 +76840,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-2996.169758663049</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="16">
@@ -76848,10 +76848,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-18045.50764256506</v>
+        <v>-17787.98958030242</v>
       </c>
       <c r="C16" t="n">
-        <v>257.5180622626422</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>-3000</v>
@@ -76862,13 +76862,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-2835.617062528594</v>
+        <v>-11878.09292054914</v>
       </c>
       <c r="C17" t="n">
-        <v>1380.874141979453</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-1945.505333637647</v>
+        <v>-1941.675092300697</v>
       </c>
     </row>
     <row r="18">
@@ -76890,13 +76890,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2349.727501894497</v>
       </c>
       <c r="C19" t="n">
         <v>2583</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1861.10526699495</v>
       </c>
     </row>
     <row r="20">
@@ -76904,13 +76904,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5496.468864160198</v>
+        <v>6668.904022634484</v>
       </c>
       <c r="C20" t="n">
         <v>2583</v>
       </c>
       <c r="D20" t="n">
-        <v>1172.435158474286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -76918,13 +76918,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>9122.687836438015</v>
+        <v>6195.718705613275</v>
       </c>
       <c r="C21" t="n">
         <v>2583</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2926.969130824741</v>
       </c>
     </row>
     <row r="22">
@@ -76932,7 +76932,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>3475.962545707418</v>
       </c>
       <c r="C22" t="n">
         <v>2583</v>
@@ -76946,13 +76946,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>3200.087201622599</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>2583</v>
       </c>
       <c r="D23" t="n">
-        <v>2110.786828697081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -76960,13 +76960,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1244.575809898751</v>
+        <v>2081.586595456361</v>
       </c>
       <c r="C24" t="n">
         <v>2583</v>
       </c>
       <c r="D24" t="n">
-        <v>2022.36642869708</v>
+        <v>1185.35564313947</v>
       </c>
     </row>
     <row r="25">
@@ -76974,13 +76974,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1112.107330278804</v>
+        <v>2555.770218550354</v>
       </c>
       <c r="C25" t="n">
         <v>2583</v>
       </c>
       <c r="D25" t="n">
-        <v>1443.662888271549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -76988,13 +76988,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>856.8839563684287</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>2583</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>856.8839563684287</v>
       </c>
     </row>
     <row r="27">
@@ -77008,7 +77008,7 @@
         <v>2583</v>
       </c>
       <c r="D27" t="n">
-        <v>23.8054476937541</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -77044,13 +77044,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>2461.13625569749</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>2583</v>
       </c>
       <c r="D30" t="n">
-        <v>5.452215931119099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -77058,13 +77058,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>5430.985287373902</v>
       </c>
       <c r="C31" t="n">
         <v>2583</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>198.6588929524005</v>
       </c>
     </row>
     <row r="32">
@@ -77072,7 +77072,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>10766.25109444523</v>
+        <v>11637.03999451407</v>
       </c>
       <c r="C32" t="n">
         <v>2583</v>
@@ -77086,13 +77086,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>8613.742469962741</v>
+        <v>2478.245947127904</v>
       </c>
       <c r="C33" t="n">
         <v>2583</v>
       </c>
       <c r="D33" t="n">
-        <v>1257.53972316516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -77120,7 +77120,7 @@
         <v>2583</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1007.075800650039</v>
       </c>
     </row>
     <row r="36">
@@ -77134,7 +77134,7 @@
         <v>2583</v>
       </c>
       <c r="D36" t="n">
-        <v>-2144.656833556458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -77142,13 +77142,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>-2388.388337507891</v>
+        <v>-10261.38833750789</v>
       </c>
       <c r="C37" t="n">
         <v>2583</v>
       </c>
       <c r="D37" t="n">
-        <v>-1066.404243766458</v>
+        <v>-2186.224652974469</v>
       </c>
     </row>
     <row r="38">
@@ -77170,7 +77170,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>-15654.61531544976</v>
+        <v>-7781.615315449763</v>
       </c>
       <c r="C39" t="n">
         <v>1264.899916353793</v>
@@ -77184,7 +77184,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>-12351.81993969722</v>
+        <v>-19946.07318270552</v>
       </c>
       <c r="C40" t="n">
         <v>1099.597678494734</v>
@@ -77198,13 +77198,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>-10930.96319742345</v>
+        <v>-3336.709954415153</v>
       </c>
       <c r="C41" t="n">
         <v>2425.467609738741</v>
       </c>
       <c r="D41" t="n">
-        <v>-1975.163575651554</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="42">
@@ -77226,7 +77226,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>6597.267824466933</v>
+        <v>918.5733261997996</v>
       </c>
       <c r="C43" t="n">
         <v>2583</v>
@@ -77240,7 +77240,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>10739.39615927011</v>
+        <v>3346.359913270112</v>
       </c>
       <c r="C44" t="n">
         <v>2583</v>
@@ -77254,13 +77254,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>5847.350451411139</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>2583</v>
       </c>
       <c r="D45" t="n">
-        <v>2521.079530824741</v>
+        <v>975.3937362358806</v>
       </c>
     </row>
     <row r="46">
@@ -77268,13 +77268,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>2185.593597778683</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>2583</v>
       </c>
       <c r="D46" t="n">
-        <v>499.0534596797685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -77296,13 +77296,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>4018.652031945508</v>
       </c>
       <c r="C48" t="n">
         <v>2583</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>903.7201772384951</v>
       </c>
     </row>
     <row r="49">
@@ -77310,13 +77310,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>129.3620925866821</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
         <v>2583</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>129.3620925866821</v>
       </c>
     </row>
     <row r="50">
@@ -77366,7 +77366,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>387.6601500911988</v>
       </c>
       <c r="C53" t="n">
         <v>2583</v>
@@ -77380,7 +77380,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>2319.547015732088</v>
       </c>
       <c r="C54" t="n">
         <v>2583</v>
@@ -77408,7 +77408,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>3009.297076312449</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
         <v>2583</v>
@@ -77422,7 +77422,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>10027.52713364935</v>
+        <v>17420.56337964935</v>
       </c>
       <c r="C57" t="n">
         <v>2583</v>
@@ -77436,7 +77436,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>3272.723379664419</v>
+        <v>10665.75962566442</v>
       </c>
       <c r="C58" t="n">
         <v>2583</v>
@@ -77450,13 +77450,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>2731.402272587279</v>
       </c>
       <c r="C59" t="n">
         <v>2583</v>
       </c>
       <c r="D59" t="n">
-        <v>1026.737581274909</v>
+        <v>2038.394565718361</v>
       </c>
     </row>
     <row r="60">
@@ -77464,7 +77464,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>-2866.927846235348</v>
       </c>
       <c r="C60" t="n">
         <v>2583</v>
@@ -77478,13 +77478,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>-6622.835051629611</v>
+        <v>-7437.565951006747</v>
       </c>
       <c r="C61" t="n">
         <v>2583</v>
       </c>
       <c r="D61" t="n">
-        <v>-3000</v>
+        <v>-2185.269100622864</v>
       </c>
     </row>
     <row r="62">
@@ -77492,7 +77492,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>-15920.65969276754</v>
+        <v>-13053.73184653219</v>
       </c>
       <c r="C62" t="n">
         <v>2583</v>
@@ -77506,13 +77506,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>-14511.36131298078</v>
+        <v>-14773.90647208796</v>
       </c>
       <c r="C63" t="n">
         <v>2581.473028340376</v>
       </c>
       <c r="D63" t="n">
-        <v>-2120.754319353885</v>
+        <v>-1858.2091602467</v>
       </c>
     </row>
     <row r="64">
@@ -77520,13 +77520,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>-15314.90267309157</v>
+        <v>-14237.62661460725</v>
       </c>
       <c r="C64" t="n">
         <v>2555.531179588875</v>
       </c>
       <c r="D64" t="n">
-        <v>-1922.72394151568</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="65">
@@ -77562,13 +77562,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>6386.360726014229</v>
+        <v>7795.106099081026</v>
       </c>
       <c r="C67" t="n">
         <v>2583</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>125.091266933202</v>
       </c>
     </row>
     <row r="68">
@@ -77576,13 +77576,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>12006.22324575544</v>
+        <v>13472.38660575544</v>
       </c>
       <c r="C68" t="n">
         <v>2583</v>
       </c>
       <c r="D68" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -77596,7 +77596,7 @@
         <v>2583</v>
       </c>
       <c r="D69" t="n">
-        <v>2980.116056364537</v>
+        <v>2588.412090824741</v>
       </c>
     </row>
     <row r="70">
@@ -77604,13 +77604,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>8672.206234147827</v>
+        <v>7206.042874147826</v>
       </c>
       <c r="C70" t="n">
         <v>2583</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="71">
@@ -77632,13 +77632,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>1408.745373066796</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
         <v>2583</v>
       </c>
       <c r="D72" t="n">
-        <v>864.6446101904351</v>
+        <v>739.553343257232</v>
       </c>
     </row>
     <row r="73">
@@ -77764,7 +77764,7 @@
         <v>2583</v>
       </c>
       <c r="D81" t="n">
-        <v>960.8238031651608</v>
+        <v>2494.66044316516</v>
       </c>
     </row>
     <row r="82">
@@ -77792,7 +77792,7 @@
         <v>2583</v>
       </c>
       <c r="D83" t="n">
-        <v>1322.604941582788</v>
+        <v>180.4722671225865</v>
       </c>
     </row>
     <row r="84">
@@ -77898,7 +77898,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>3327.500881666889</v>
+        <v>8403.681838990458</v>
       </c>
       <c r="C91" t="n">
         <v>2583</v>
@@ -77912,13 +77912,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>15999.3055399834</v>
+        <v>10923.12458265983</v>
       </c>
       <c r="C92" t="n">
         <v>2583</v>
       </c>
       <c r="D92" t="n">
-        <v>1737.276290133243</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="93">
@@ -77960,7 +77960,7 @@
         <v>2583</v>
       </c>
       <c r="D95" t="n">
-        <v>1314.54411614121</v>
+        <v>51.82040627445367</v>
       </c>
     </row>
     <row r="96">
@@ -78240,7 +78240,7 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>2397.893040930913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -78254,7 +78254,7 @@
         <v>2583</v>
       </c>
       <c r="D116" t="n">
-        <v>321.2281010374991</v>
+        <v>2912.228101037499</v>
       </c>
     </row>
     <row r="117">
@@ -78268,7 +78268,7 @@
         <v>2583</v>
       </c>
       <c r="D117" t="n">
-        <v>3000</v>
+        <v>2924.332530930027</v>
       </c>
     </row>
     <row r="118">
@@ -78290,13 +78290,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>11605.21158238571</v>
+        <v>6212.635589752518</v>
       </c>
       <c r="C119" t="n">
         <v>2583</v>
       </c>
       <c r="D119" t="n">
-        <v>163.116656482747</v>
+        <v>2592.473186143892</v>
       </c>
     </row>
     <row r="120">
@@ -78310,7 +78310,7 @@
         <v>2583</v>
       </c>
       <c r="D120" t="n">
-        <v>2546.796019660261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -78318,7 +78318,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>1884.185223481814</v>
+        <v>7276.761216115001</v>
       </c>
       <c r="C121" t="n">
         <v>2583</v>
@@ -78335,10 +78335,10 @@
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>2583</v>
+        <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>-458.1131586600786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -78349,10 +78349,10 @@
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>2583</v>
+        <v>426.3015689291715</v>
       </c>
       <c r="D123" t="n">
-        <v>-758.2103586600683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -78394,7 +78394,7 @@
         <v>2583</v>
       </c>
       <c r="D126" t="n">
-        <v>-1113.988447898671</v>
+        <v>-245.1044478986705</v>
       </c>
     </row>
     <row r="127">
@@ -78422,7 +78422,7 @@
         <v>2583</v>
       </c>
       <c r="D128" t="n">
-        <v>-511.5391831615724</v>
+        <v>-986.0683585369597</v>
       </c>
     </row>
     <row r="129">
@@ -78450,7 +78450,7 @@
         <v>755.5023416130725</v>
       </c>
       <c r="D130" t="n">
-        <v>-478.1725246175192</v>
+        <v>-1423.335524617517</v>
       </c>
     </row>
     <row r="131">
@@ -78461,10 +78461,10 @@
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>714.7431320923042</v>
+        <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>-908.1617586600682</v>
       </c>
     </row>
     <row r="132">
@@ -78486,13 +78486,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>-3220.534395423005</v>
+        <v>-9213.651754122111</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>-1056.740907813188</v>
+        <v>-406.5676772394306</v>
       </c>
     </row>
     <row r="134">
@@ -78500,13 +78500,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>-17557.74616980211</v>
+        <v>-8946.687106303363</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>-407.5268138584515</v>
       </c>
     </row>
     <row r="135">
@@ -78528,7 +78528,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>-11517.97241427975</v>
+        <v>-12558.74817773614</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -78542,7 +78542,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>-8097.931040953503</v>
+        <v>-8669.134011625125</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -78556,7 +78556,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>-1577.907013909101</v>
+        <v>-2583.869984580723</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -78584,7 +78584,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>25959.01650894526</v>
+        <v>12614.20650894526</v>
       </c>
       <c r="C140" t="n">
         <v>2583</v>
@@ -78612,10 +78612,10 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>4393.999283839035</v>
+        <v>6976.999283839035</v>
       </c>
       <c r="C142" t="n">
-        <v>2583</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -78640,10 +78640,10 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>5939.476602636797</v>
       </c>
       <c r="C144" t="n">
-        <v>2583</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
         <v>-1797.27122662207</v>
@@ -78654,13 +78654,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>831.1906911137412</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>2533.695937394116</v>
       </c>
       <c r="D145" t="n">
-        <v>-1255.44309368241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -78682,13 +78682,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>4295.226573915235</v>
+        <v>5754.403168582432</v>
       </c>
       <c r="C147" t="n">
-        <v>1459.176594667197</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>-391.4551690550767</v>
+        <v>-1187.398558660068</v>
       </c>
     </row>
     <row r="148">
@@ -78696,13 +78696,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>2144.150037472908</v>
+        <v>4676.116149055175</v>
       </c>
       <c r="C148" t="n">
         <v>1162.193724847197</v>
       </c>
       <c r="D148" t="n">
-        <v>-2470.59299257951</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -78716,7 +78716,7 @@
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>-2286.319388447299</v>
       </c>
     </row>
     <row r="150">
@@ -78738,13 +78738,13 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>-9001.270347538863</v>
+        <v>-7002.04597157519</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>-2358.578311851559</v>
       </c>
     </row>
     <row r="152">
@@ -78758,7 +78758,7 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>-754.6039931929104</v>
       </c>
     </row>
     <row r="153">
@@ -78766,13 +78766,13 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>-1999.224375963672</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>-2469.408996834839</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -78878,7 +78878,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>-8172.124299626876</v>
+        <v>-11795.39657081299</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -78906,7 +78906,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>-8794.826899303473</v>
+        <v>-5171.554628117359</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -79041,7 +79041,7 @@
         <v>2583</v>
       </c>
       <c r="D2" t="n">
-        <v>3000</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -79063,13 +79063,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>2831.128857310512</v>
       </c>
       <c r="C4" t="n">
         <v>2583</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>1238.99706261653</v>
       </c>
     </row>
     <row r="5">
@@ -79083,7 +79083,7 @@
         <v>2583</v>
       </c>
       <c r="D5" t="n">
-        <v>138.5922563735921</v>
+        <v>909.4297509402186</v>
       </c>
     </row>
     <row r="6">
@@ -79097,7 +79097,7 @@
         <v>2583</v>
       </c>
       <c r="D6" t="n">
-        <v>837.051557482518</v>
+        <v>1827.217000299361</v>
       </c>
     </row>
     <row r="7">
@@ -79133,7 +79133,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7584.875425402002</v>
+        <v>5141.295927790364</v>
       </c>
       <c r="C9" t="n">
         <v>2583</v>
@@ -79147,7 +79147,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>12765.6919006769</v>
+        <v>14582.37093477142</v>
       </c>
       <c r="C10" t="n">
         <v>2583</v>
@@ -79161,7 +79161,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2204.228393793393</v>
+        <v>-0</v>
       </c>
       <c r="C11" t="n">
         <v>2583</v>
@@ -79178,7 +79178,7 @@
         <v>-0</v>
       </c>
       <c r="C12" t="n">
-        <v>2583</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>-0</v>
@@ -79192,7 +79192,7 @@
         <v>-0</v>
       </c>
       <c r="C13" t="n">
-        <v>2435.774892253643</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>-0</v>
@@ -79206,7 +79206,7 @@
         <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>533.7846095046607</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
         <v>-0</v>
@@ -79234,7 +79234,7 @@
         <v>-0</v>
       </c>
       <c r="C16" t="n">
-        <v>257.5180622626422</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
         <v>-0</v>
@@ -79248,7 +79248,7 @@
         <v>-0</v>
       </c>
       <c r="C17" t="n">
-        <v>1380.874141979453</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
         <v>-0</v>
@@ -79273,13 +79273,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-0</v>
+        <v>2349.727501894497</v>
       </c>
       <c r="C19" t="n">
         <v>2583</v>
       </c>
       <c r="D19" t="n">
-        <v>-0</v>
+        <v>1861.10526699495</v>
       </c>
     </row>
     <row r="20">
@@ -79287,13 +79287,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5496.468864160198</v>
+        <v>6668.904022634484</v>
       </c>
       <c r="C20" t="n">
         <v>2583</v>
       </c>
       <c r="D20" t="n">
-        <v>1172.435158474286</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
@@ -79301,13 +79301,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>9122.687836438015</v>
+        <v>6195.718705613275</v>
       </c>
       <c r="C21" t="n">
         <v>2583</v>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>2926.969130824741</v>
       </c>
     </row>
     <row r="22">
@@ -79315,7 +79315,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-0</v>
+        <v>3475.962545707418</v>
       </c>
       <c r="C22" t="n">
         <v>2583</v>
@@ -79329,13 +79329,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>3200.087201622599</v>
+        <v>-0</v>
       </c>
       <c r="C23" t="n">
         <v>2583</v>
       </c>
       <c r="D23" t="n">
-        <v>2110.786828697081</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
@@ -79343,13 +79343,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1244.575809898751</v>
+        <v>2081.586595456361</v>
       </c>
       <c r="C24" t="n">
         <v>2583</v>
       </c>
       <c r="D24" t="n">
-        <v>2022.36642869708</v>
+        <v>1185.35564313947</v>
       </c>
     </row>
     <row r="25">
@@ -79357,13 +79357,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1112.107330278804</v>
+        <v>2555.770218550354</v>
       </c>
       <c r="C25" t="n">
         <v>2583</v>
       </c>
       <c r="D25" t="n">
-        <v>1443.662888271549</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -79371,13 +79371,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>856.8839563684287</v>
+        <v>-0</v>
       </c>
       <c r="C26" t="n">
         <v>2583</v>
       </c>
       <c r="D26" t="n">
-        <v>-0</v>
+        <v>856.8839563684287</v>
       </c>
     </row>
     <row r="27">
@@ -79391,7 +79391,7 @@
         <v>2583</v>
       </c>
       <c r="D27" t="n">
-        <v>23.8054476937541</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -79427,13 +79427,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>2461.13625569749</v>
+        <v>-0</v>
       </c>
       <c r="C30" t="n">
         <v>2583</v>
       </c>
       <c r="D30" t="n">
-        <v>5.452215931119099</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="31">
@@ -79441,13 +79441,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>-0</v>
+        <v>5430.985287373902</v>
       </c>
       <c r="C31" t="n">
         <v>2583</v>
       </c>
       <c r="D31" t="n">
-        <v>-0</v>
+        <v>198.6588929524005</v>
       </c>
     </row>
     <row r="32">
@@ -79455,7 +79455,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>10766.25109444523</v>
+        <v>11637.03999451407</v>
       </c>
       <c r="C32" t="n">
         <v>2583</v>
@@ -79469,13 +79469,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>8613.742469962741</v>
+        <v>2478.245947127904</v>
       </c>
       <c r="C33" t="n">
         <v>2583</v>
       </c>
       <c r="D33" t="n">
-        <v>1257.53972316516</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="34">
@@ -79503,7 +79503,7 @@
         <v>2583</v>
       </c>
       <c r="D35" t="n">
-        <v>-0</v>
+        <v>1007.075800650039</v>
       </c>
     </row>
     <row r="36">
@@ -79609,7 +79609,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>6597.267824466933</v>
+        <v>918.5733261997996</v>
       </c>
       <c r="C43" t="n">
         <v>2583</v>
@@ -79623,7 +79623,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>10739.39615927011</v>
+        <v>3346.359913270112</v>
       </c>
       <c r="C44" t="n">
         <v>2583</v>
@@ -79637,13 +79637,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>5847.350451411139</v>
+        <v>-0</v>
       </c>
       <c r="C45" t="n">
         <v>2583</v>
       </c>
       <c r="D45" t="n">
-        <v>2521.079530824741</v>
+        <v>975.3937362358806</v>
       </c>
     </row>
     <row r="46">
@@ -79651,13 +79651,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>2185.593597778683</v>
+        <v>-0</v>
       </c>
       <c r="C46" t="n">
         <v>2583</v>
       </c>
       <c r="D46" t="n">
-        <v>499.0534596797685</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="47">
@@ -79679,13 +79679,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>-0</v>
+        <v>4018.652031945508</v>
       </c>
       <c r="C48" t="n">
         <v>2583</v>
       </c>
       <c r="D48" t="n">
-        <v>-0</v>
+        <v>903.7201772384951</v>
       </c>
     </row>
     <row r="49">
@@ -79693,13 +79693,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>129.3620925866821</v>
+        <v>-0</v>
       </c>
       <c r="C49" t="n">
         <v>2583</v>
       </c>
       <c r="D49" t="n">
-        <v>-0</v>
+        <v>129.3620925866821</v>
       </c>
     </row>
     <row r="50">
@@ -79749,7 +79749,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>-0</v>
+        <v>387.6601500911988</v>
       </c>
       <c r="C53" t="n">
         <v>2583</v>
@@ -79763,7 +79763,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>-0</v>
+        <v>2319.547015732088</v>
       </c>
       <c r="C54" t="n">
         <v>2583</v>
@@ -79791,7 +79791,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>3009.297076312449</v>
+        <v>-0</v>
       </c>
       <c r="C56" t="n">
         <v>2583</v>
@@ -79805,7 +79805,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>10027.52713364935</v>
+        <v>17420.56337964935</v>
       </c>
       <c r="C57" t="n">
         <v>2583</v>
@@ -79819,7 +79819,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>3272.723379664419</v>
+        <v>10665.75962566442</v>
       </c>
       <c r="C58" t="n">
         <v>2583</v>
@@ -79833,13 +79833,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>-0</v>
+        <v>2731.402272587279</v>
       </c>
       <c r="C59" t="n">
         <v>2583</v>
       </c>
       <c r="D59" t="n">
-        <v>1026.737581274909</v>
+        <v>2038.394565718361</v>
       </c>
     </row>
     <row r="60">
@@ -79945,13 +79945,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>6386.360726014229</v>
+        <v>7795.106099081026</v>
       </c>
       <c r="C67" t="n">
         <v>2583</v>
       </c>
       <c r="D67" t="n">
-        <v>-0</v>
+        <v>125.091266933202</v>
       </c>
     </row>
     <row r="68">
@@ -79959,13 +79959,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>12006.22324575544</v>
+        <v>13472.38660575544</v>
       </c>
       <c r="C68" t="n">
         <v>2583</v>
       </c>
       <c r="D68" t="n">
-        <v>3000</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="69">
@@ -79979,7 +79979,7 @@
         <v>2583</v>
       </c>
       <c r="D69" t="n">
-        <v>2980.116056364537</v>
+        <v>2588.412090824741</v>
       </c>
     </row>
     <row r="70">
@@ -79987,13 +79987,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>8672.206234147827</v>
+        <v>7206.042874147826</v>
       </c>
       <c r="C70" t="n">
         <v>2583</v>
       </c>
       <c r="D70" t="n">
-        <v>-0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="71">
@@ -80015,13 +80015,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>1408.745373066796</v>
+        <v>-0</v>
       </c>
       <c r="C72" t="n">
         <v>2583</v>
       </c>
       <c r="D72" t="n">
-        <v>864.6446101904351</v>
+        <v>739.553343257232</v>
       </c>
     </row>
     <row r="73">
@@ -80147,7 +80147,7 @@
         <v>2583</v>
       </c>
       <c r="D81" t="n">
-        <v>960.8238031651608</v>
+        <v>2494.66044316516</v>
       </c>
     </row>
     <row r="82">
@@ -80175,7 +80175,7 @@
         <v>2583</v>
       </c>
       <c r="D83" t="n">
-        <v>1322.604941582788</v>
+        <v>180.4722671225865</v>
       </c>
     </row>
     <row r="84">
@@ -80281,7 +80281,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>3327.500881666889</v>
+        <v>8403.681838990458</v>
       </c>
       <c r="C91" t="n">
         <v>2583</v>
@@ -80295,13 +80295,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>15999.3055399834</v>
+        <v>10923.12458265983</v>
       </c>
       <c r="C92" t="n">
         <v>2583</v>
       </c>
       <c r="D92" t="n">
-        <v>1737.276290133243</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="93">
@@ -80343,7 +80343,7 @@
         <v>2583</v>
       </c>
       <c r="D95" t="n">
-        <v>1314.54411614121</v>
+        <v>51.82040627445367</v>
       </c>
     </row>
     <row r="96">
@@ -80623,7 +80623,7 @@
         <v>-0</v>
       </c>
       <c r="D115" t="n">
-        <v>2397.893040930913</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="116">
@@ -80637,7 +80637,7 @@
         <v>2583</v>
       </c>
       <c r="D116" t="n">
-        <v>321.2281010374991</v>
+        <v>2912.228101037499</v>
       </c>
     </row>
     <row r="117">
@@ -80651,7 +80651,7 @@
         <v>2583</v>
       </c>
       <c r="D117" t="n">
-        <v>3000</v>
+        <v>2924.332530930027</v>
       </c>
     </row>
     <row r="118">
@@ -80673,13 +80673,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>11605.21158238571</v>
+        <v>6212.635589752518</v>
       </c>
       <c r="C119" t="n">
         <v>2583</v>
       </c>
       <c r="D119" t="n">
-        <v>163.116656482747</v>
+        <v>2592.473186143892</v>
       </c>
     </row>
     <row r="120">
@@ -80693,7 +80693,7 @@
         <v>2583</v>
       </c>
       <c r="D120" t="n">
-        <v>2546.796019660261</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="121">
@@ -80701,7 +80701,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>1884.185223481814</v>
+        <v>7276.761216115001</v>
       </c>
       <c r="C121" t="n">
         <v>2583</v>
@@ -80718,7 +80718,7 @@
         <v>-0</v>
       </c>
       <c r="C122" t="n">
-        <v>2583</v>
+        <v>-0</v>
       </c>
       <c r="D122" t="n">
         <v>-0</v>
@@ -80732,7 +80732,7 @@
         <v>-0</v>
       </c>
       <c r="C123" t="n">
-        <v>2583</v>
+        <v>426.3015689291715</v>
       </c>
       <c r="D123" t="n">
         <v>-0</v>
@@ -80844,7 +80844,7 @@
         <v>-0</v>
       </c>
       <c r="C131" t="n">
-        <v>714.7431320923042</v>
+        <v>-0</v>
       </c>
       <c r="D131" t="n">
         <v>-0</v>
@@ -80967,7 +80967,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>25959.01650894526</v>
+        <v>12614.20650894526</v>
       </c>
       <c r="C140" t="n">
         <v>2583</v>
@@ -80995,10 +80995,10 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>4393.999283839035</v>
+        <v>6976.999283839035</v>
       </c>
       <c r="C142" t="n">
-        <v>2583</v>
+        <v>-0</v>
       </c>
       <c r="D142" t="n">
         <v>-0</v>
@@ -81023,10 +81023,10 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>-0</v>
+        <v>5939.476602636797</v>
       </c>
       <c r="C144" t="n">
-        <v>2583</v>
+        <v>-0</v>
       </c>
       <c r="D144" t="n">
         <v>-0</v>
@@ -81037,10 +81037,10 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>-0</v>
+        <v>831.1906911137412</v>
       </c>
       <c r="C145" t="n">
-        <v>-0</v>
+        <v>2533.695937394116</v>
       </c>
       <c r="D145" t="n">
         <v>-0</v>
@@ -81065,10 +81065,10 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>4295.226573915235</v>
+        <v>5754.403168582432</v>
       </c>
       <c r="C147" t="n">
-        <v>1459.176594667197</v>
+        <v>-0</v>
       </c>
       <c r="D147" t="n">
         <v>-0</v>
@@ -81079,7 +81079,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>2144.150037472908</v>
+        <v>4676.116149055175</v>
       </c>
       <c r="C148" t="n">
         <v>1162.193724847197</v>
@@ -81523,7 +81523,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2298.191051888389</v>
+        <v>2952.21128094609</v>
       </c>
       <c r="C12" t="n">
         <v>855.5462565324092</v>
@@ -81534,7 +81534,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11318.1968748879</v>
+        <v>2413.003459576957</v>
       </c>
       <c r="C13" t="n">
         <v>1246.256912036459</v>
@@ -81545,7 +81545,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7282.687464226188</v>
+        <v>6748.902854721528</v>
       </c>
       <c r="C14" t="n">
         <v>3000</v>
@@ -81559,7 +81559,7 @@
         <v>17774.86151347345</v>
       </c>
       <c r="C15" t="n">
-        <v>2996.169758663049</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="16">
@@ -81567,7 +81567,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>18045.50764256506</v>
+        <v>17787.98958030242</v>
       </c>
       <c r="C16" t="n">
         <v>3000</v>
@@ -81578,10 +81578,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2835.617062528594</v>
+        <v>11878.09292054914</v>
       </c>
       <c r="C17" t="n">
-        <v>1945.505333637647</v>
+        <v>1941.675092300697</v>
       </c>
     </row>
     <row r="18">
@@ -81790,7 +81790,7 @@
         <v>-0</v>
       </c>
       <c r="C36" t="n">
-        <v>2144.656833556458</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="37">
@@ -81798,10 +81798,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>2388.388337507891</v>
+        <v>10261.38833750789</v>
       </c>
       <c r="C37" t="n">
-        <v>1066.404243766458</v>
+        <v>2186.224652974469</v>
       </c>
     </row>
     <row r="38">
@@ -81820,7 +81820,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>15654.61531544976</v>
+        <v>7781.615315449763</v>
       </c>
       <c r="C39" t="n">
         <v>2976.87206504305</v>
@@ -81831,7 +81831,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>12351.81993969722</v>
+        <v>19946.07318270552</v>
       </c>
       <c r="C40" t="n">
         <v>2770.07018631964</v>
@@ -81842,10 +81842,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>10930.96319742345</v>
+        <v>3336.709954415153</v>
       </c>
       <c r="C41" t="n">
-        <v>1975.163575651554</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="42">
@@ -82051,7 +82051,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>-0</v>
+        <v>2866.927846235348</v>
       </c>
       <c r="C60" t="n">
         <v>-0</v>
@@ -82062,10 +82062,10 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>6622.835051629611</v>
+        <v>7437.565951006747</v>
       </c>
       <c r="C61" t="n">
-        <v>3000</v>
+        <v>2185.269100622864</v>
       </c>
     </row>
     <row r="62">
@@ -82073,7 +82073,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>15920.65969276754</v>
+        <v>13053.73184653219</v>
       </c>
       <c r="C62" t="n">
         <v>3000</v>
@@ -82084,10 +82084,10 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>14511.36131298078</v>
+        <v>14773.90647208796</v>
       </c>
       <c r="C63" t="n">
-        <v>2120.754319353885</v>
+        <v>1858.2091602467</v>
       </c>
     </row>
     <row r="64">
@@ -82095,10 +82095,10 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>15314.90267309157</v>
+        <v>14237.62661460725</v>
       </c>
       <c r="C64" t="n">
-        <v>1922.72394151568</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="65">
@@ -82736,7 +82736,7 @@
         <v>-0</v>
       </c>
       <c r="C122" t="n">
-        <v>458.1131586600786</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="123">
@@ -82747,7 +82747,7 @@
         <v>-0</v>
       </c>
       <c r="C123" t="n">
-        <v>758.2103586600683</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="124">
@@ -82780,7 +82780,7 @@
         <v>-0</v>
       </c>
       <c r="C126" t="n">
-        <v>1113.988447898671</v>
+        <v>245.1044478986705</v>
       </c>
     </row>
     <row r="127">
@@ -82802,7 +82802,7 @@
         <v>-0</v>
       </c>
       <c r="C128" t="n">
-        <v>511.5391831615724</v>
+        <v>986.0683585369597</v>
       </c>
     </row>
     <row r="129">
@@ -82824,7 +82824,7 @@
         <v>-0</v>
       </c>
       <c r="C130" t="n">
-        <v>478.1725246175192</v>
+        <v>1423.335524617517</v>
       </c>
     </row>
     <row r="131">
@@ -82835,7 +82835,7 @@
         <v>-0</v>
       </c>
       <c r="C131" t="n">
-        <v>-0</v>
+        <v>908.1617586600682</v>
       </c>
     </row>
     <row r="132">
@@ -82854,10 +82854,10 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>3220.534395423005</v>
+        <v>9213.651754122111</v>
       </c>
       <c r="C133" t="n">
-        <v>1056.740907813188</v>
+        <v>406.5676772394306</v>
       </c>
     </row>
     <row r="134">
@@ -82865,10 +82865,10 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>17557.74616980211</v>
+        <v>8946.687106303363</v>
       </c>
       <c r="C134" t="n">
-        <v>-0</v>
+        <v>407.5268138584515</v>
       </c>
     </row>
     <row r="135">
@@ -82887,7 +82887,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>11517.97241427975</v>
+        <v>12558.74817773614</v>
       </c>
       <c r="C136" t="n">
         <v>-0</v>
@@ -82898,7 +82898,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>8097.931040953503</v>
+        <v>8669.134011625125</v>
       </c>
       <c r="C137" t="n">
         <v>-0</v>
@@ -82909,7 +82909,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>1577.907013909101</v>
+        <v>2583.869984580723</v>
       </c>
       <c r="C138" t="n">
         <v>-0</v>
@@ -82989,7 +82989,7 @@
         <v>-0</v>
       </c>
       <c r="C145" t="n">
-        <v>1255.44309368241</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="146">
@@ -83011,7 +83011,7 @@
         <v>-0</v>
       </c>
       <c r="C147" t="n">
-        <v>391.4551690550767</v>
+        <v>1187.398558660068</v>
       </c>
     </row>
     <row r="148">
@@ -83022,7 +83022,7 @@
         <v>-0</v>
       </c>
       <c r="C148" t="n">
-        <v>2470.59299257951</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="149">
@@ -83033,7 +83033,7 @@
         <v>-0</v>
       </c>
       <c r="C149" t="n">
-        <v>-0</v>
+        <v>2286.319388447299</v>
       </c>
     </row>
     <row r="150">
@@ -83052,10 +83052,10 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>9001.270347538863</v>
+        <v>7002.04597157519</v>
       </c>
       <c r="C151" t="n">
-        <v>-0</v>
+        <v>2358.578311851559</v>
       </c>
     </row>
     <row r="152">
@@ -83066,7 +83066,7 @@
         <v>-0</v>
       </c>
       <c r="C152" t="n">
-        <v>-0</v>
+        <v>754.6039931929104</v>
       </c>
     </row>
     <row r="153">
@@ -83074,10 +83074,10 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>-0</v>
+        <v>1999.224375963672</v>
       </c>
       <c r="C153" t="n">
-        <v>2469.408996834839</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="154">
@@ -83162,7 +83162,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>8172.124299626876</v>
+        <v>11795.39657081299</v>
       </c>
       <c r="C161" t="n">
         <v>1042.772323254218</v>
@@ -83184,7 +83184,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>8794.826899303473</v>
+        <v>5171.554628117359</v>
       </c>
       <c r="C163" t="n">
         <v>-0</v>
@@ -83298,7 +83298,7 @@
         <v>643167</v>
       </c>
       <c r="D2" t="n">
-        <v>2739.130434782609</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="3">
@@ -83312,7 +83312,7 @@
         <v>640584</v>
       </c>
       <c r="D3" t="n">
-        <v>1060.482406365337</v>
+        <v>4321.351971582728</v>
       </c>
     </row>
     <row r="4">
@@ -83320,13 +83320,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22385.66970902696</v>
+        <v>19227.9789920864</v>
       </c>
       <c r="C4" t="n">
         <v>638001</v>
       </c>
       <c r="D4" t="n">
-        <v>1060.482406365337</v>
+        <v>2974.616033956065</v>
       </c>
     </row>
     <row r="5">
@@ -83334,13 +83334,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22385.66970902696</v>
+        <v>19227.9789920864</v>
       </c>
       <c r="C5" t="n">
         <v>635418</v>
       </c>
       <c r="D5" t="n">
-        <v>909.8386494375195</v>
+        <v>1986.105435108001</v>
       </c>
     </row>
     <row r="6">
@@ -83348,7 +83348,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22385.66970902696</v>
+        <v>19227.9789920864</v>
       </c>
       <c r="C6" t="n">
         <v>632835</v>
@@ -83362,7 +83362,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23367.24994019105</v>
+        <v>20209.5592232505</v>
       </c>
       <c r="C7" t="n">
         <v>630252</v>
@@ -83376,7 +83376,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25156.42086838435</v>
+        <v>21998.7301514438</v>
       </c>
       <c r="C8" t="n">
         <v>627669</v>
@@ -83390,7 +83390,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16696.65378357039</v>
+        <v>16264.40181725052</v>
       </c>
       <c r="C9" t="n">
         <v>625086</v>
@@ -83404,7 +83404,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2458.479245522663</v>
+        <v>-0</v>
       </c>
       <c r="C10" t="n">
         <v>622503</v>
@@ -83432,10 +83432,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2060.516874470231</v>
+        <v>2646.899680682518</v>
       </c>
       <c r="C12" t="n">
-        <v>617337</v>
+        <v>619920</v>
       </c>
       <c r="D12" t="n">
         <v>787.1025560098165</v>
@@ -83446,10 +83446,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12208.20917799738</v>
+        <v>4810.355300496162</v>
       </c>
       <c r="C13" t="n">
-        <v>614901.2251077463</v>
+        <v>619920</v>
       </c>
       <c r="D13" t="n">
         <v>1933.658915083359</v>
@@ -83460,10 +83460,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>18737.73612885753</v>
+        <v>10861.30054496898</v>
       </c>
       <c r="C14" t="n">
-        <v>614367.4404982417</v>
+        <v>619920</v>
       </c>
       <c r="D14" t="n">
         <v>4693.658915083359</v>
@@ -83474,13 +83474,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>34674.35813414686</v>
+        <v>26797.92255025831</v>
       </c>
       <c r="C15" t="n">
-        <v>614367.4404982417</v>
+        <v>619920</v>
       </c>
       <c r="D15" t="n">
-        <v>7450.135093053364</v>
+        <v>7453.658915083359</v>
       </c>
     </row>
     <row r="16">
@@ -83488,13 +83488,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>50853.63660420011</v>
+        <v>42746.31494478836</v>
       </c>
       <c r="C16" t="n">
-        <v>614109.922435979</v>
+        <v>619920</v>
       </c>
       <c r="D16" t="n">
-        <v>10210.13509305336</v>
+        <v>10213.65891508336</v>
       </c>
     </row>
     <row r="17">
@@ -83505,7 +83505,7 @@
         <v>53396</v>
       </c>
       <c r="C17" t="n">
-        <v>612729.0482939995</v>
+        <v>619920</v>
       </c>
       <c r="D17" t="n">
         <v>12000</v>
@@ -83519,7 +83519,7 @@
         <v>53396</v>
       </c>
       <c r="C18" t="n">
-        <v>610146.0482939995</v>
+        <v>617337</v>
       </c>
       <c r="D18" t="n">
         <v>12000</v>
@@ -83530,13 +83530,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>53396</v>
+        <v>50775.23877929008</v>
       </c>
       <c r="C19" t="n">
-        <v>607563.0482939995</v>
+        <v>614754</v>
       </c>
       <c r="D19" t="n">
-        <v>12000</v>
+        <v>9977.059492396793</v>
       </c>
     </row>
     <row r="20">
@@ -83544,13 +83544,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>47265.53064199301</v>
+        <v>43337.09753394768</v>
       </c>
       <c r="C20" t="n">
-        <v>604980.0482939995</v>
+        <v>612171</v>
       </c>
       <c r="D20" t="n">
-        <v>10725.61395818012</v>
+        <v>9977.059492396793</v>
       </c>
     </row>
     <row r="21">
@@ -83558,13 +83558,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>37090.56929387822</v>
+        <v>36426.72205210706</v>
       </c>
       <c r="C21" t="n">
-        <v>602397.0482939995</v>
+        <v>609588</v>
       </c>
       <c r="D21" t="n">
-        <v>10725.61395818012</v>
+        <v>6795.571306717727</v>
       </c>
     </row>
     <row r="22">
@@ -83572,13 +83572,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>37090.56929387822</v>
+        <v>32549.81809746324</v>
       </c>
       <c r="C22" t="n">
-        <v>599814.0482939995</v>
+        <v>607005</v>
       </c>
       <c r="D22" t="n">
-        <v>10725.61395818012</v>
+        <v>6795.571306717727</v>
       </c>
     </row>
     <row r="23">
@@ -83586,13 +83586,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>33521.36204148798</v>
+        <v>32549.81809746324</v>
       </c>
       <c r="C23" t="n">
-        <v>597231.0482939995</v>
+        <v>604422</v>
       </c>
       <c r="D23" t="n">
-        <v>8431.280448726775</v>
+        <v>6795.571306717727</v>
       </c>
     </row>
     <row r="24">
@@ -83600,13 +83600,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>32133.22830419867</v>
+        <v>30228.12699816633</v>
       </c>
       <c r="C24" t="n">
-        <v>594648.0482939995</v>
+        <v>601839</v>
       </c>
       <c r="D24" t="n">
-        <v>6233.056069708211</v>
+        <v>5507.141259826998</v>
       </c>
     </row>
     <row r="25">
@@ -83614,13 +83614,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>30892.84287137209</v>
+        <v>27377.55667781144</v>
       </c>
       <c r="C25" t="n">
-        <v>592065.0482939995</v>
+        <v>599256</v>
       </c>
       <c r="D25" t="n">
-        <v>4663.8572781087</v>
+        <v>5507.141259826998</v>
       </c>
     </row>
     <row r="26">
@@ -83628,13 +83628,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>29937.12003045192</v>
+        <v>27377.55667781144</v>
       </c>
       <c r="C26" t="n">
-        <v>589482.0482939995</v>
+        <v>596673</v>
       </c>
       <c r="D26" t="n">
-        <v>4663.8572781087</v>
+        <v>4575.745655078706</v>
       </c>
     </row>
     <row r="27">
@@ -83642,13 +83642,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>29937.12003045192</v>
+        <v>27377.55667781144</v>
       </c>
       <c r="C27" t="n">
-        <v>586899.0482939995</v>
+        <v>594090</v>
       </c>
       <c r="D27" t="n">
-        <v>4637.981791485055</v>
+        <v>4575.745655078706</v>
       </c>
     </row>
     <row r="28">
@@ -83656,13 +83656,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>29743.35021308667</v>
+        <v>27183.7868604462</v>
       </c>
       <c r="C28" t="n">
-        <v>584316.0482939995</v>
+        <v>591507</v>
       </c>
       <c r="D28" t="n">
-        <v>4273.10852254974</v>
+        <v>4210.872386143392</v>
       </c>
     </row>
     <row r="29">
@@ -83670,13 +83670,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>29743.35021308667</v>
+        <v>27183.7868604462</v>
       </c>
       <c r="C29" t="n">
-        <v>581733.0482939995</v>
+        <v>588924</v>
       </c>
       <c r="D29" t="n">
-        <v>4273.10852254974</v>
+        <v>4210.872386143392</v>
       </c>
     </row>
     <row r="30">
@@ -83684,13 +83684,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>26998.32958724186</v>
+        <v>27183.7868604462</v>
       </c>
       <c r="C30" t="n">
-        <v>579150.0482939995</v>
+        <v>586341</v>
       </c>
       <c r="D30" t="n">
-        <v>4267.18220088548</v>
+        <v>4210.872386143392</v>
       </c>
     </row>
     <row r="31">
@@ -83698,13 +83698,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>26998.32958724186</v>
+        <v>21126.35440501473</v>
       </c>
       <c r="C31" t="n">
-        <v>576567.0482939995</v>
+        <v>583758</v>
       </c>
       <c r="D31" t="n">
-        <v>4267.18220088548</v>
+        <v>3994.938806847304</v>
       </c>
     </row>
     <row r="32">
@@ -83712,13 +83712,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>14990.22509938169</v>
+        <v>8147.018240764405</v>
       </c>
       <c r="C32" t="n">
-        <v>573984.0482939995</v>
+        <v>581175</v>
       </c>
       <c r="D32" t="n">
-        <v>3612.600503643045</v>
+        <v>3340.357109604869</v>
       </c>
     </row>
     <row r="33">
@@ -83729,10 +83729,10 @@
         <v>5382.914374091461</v>
       </c>
       <c r="C33" t="n">
-        <v>571401.0482939995</v>
+        <v>578592</v>
       </c>
       <c r="D33" t="n">
-        <v>2245.709500202653</v>
+        <v>3340.357109604869</v>
       </c>
     </row>
     <row r="34">
@@ -83743,10 +83743,10 @@
         <v>-0</v>
       </c>
       <c r="C34" t="n">
-        <v>568818.0482939995</v>
+        <v>576009</v>
       </c>
       <c r="D34" t="n">
-        <v>-0</v>
+        <v>1094.647609402216</v>
       </c>
     </row>
     <row r="35">
@@ -83757,7 +83757,7 @@
         <v>-0</v>
       </c>
       <c r="C35" t="n">
-        <v>566235.0482939995</v>
+        <v>573426</v>
       </c>
       <c r="D35" t="n">
         <v>-0</v>
@@ -83771,10 +83771,10 @@
         <v>-0</v>
       </c>
       <c r="C36" t="n">
-        <v>563652.0482939995</v>
+        <v>570843</v>
       </c>
       <c r="D36" t="n">
-        <v>1973.084286871942</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="37">
@@ -83782,13 +83782,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>2141.386142887965</v>
+        <v>9200.176724886966</v>
       </c>
       <c r="C37" t="n">
-        <v>561069.0482939995</v>
+        <v>568260</v>
       </c>
       <c r="D37" t="n">
-        <v>2954.176191137084</v>
+        <v>2011.326680736512</v>
       </c>
     </row>
     <row r="38">
@@ -83796,13 +83796,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>18485.42696754139</v>
+        <v>25544.21754954039</v>
       </c>
       <c r="C38" t="n">
-        <v>558654.9939349805</v>
+        <v>565845.945640981</v>
       </c>
       <c r="D38" t="n">
-        <v>4895.662639146897</v>
+        <v>3952.813128746325</v>
       </c>
     </row>
     <row r="39">
@@ -83813,10 +83813,10 @@
         <v>32521.07426253874</v>
       </c>
       <c r="C39" t="n">
-        <v>557390.0940186267</v>
+        <v>564581.0457246272</v>
       </c>
       <c r="D39" t="n">
-        <v>7634.384938986503</v>
+        <v>6691.535428585931</v>
       </c>
     </row>
     <row r="40">
@@ -83824,13 +83824,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>43595.49446587701</v>
+        <v>50404.36570543783</v>
       </c>
       <c r="C40" t="n">
-        <v>556290.496340132</v>
+        <v>563481.4480461325</v>
       </c>
       <c r="D40" t="n">
-        <v>10182.84951040057</v>
+        <v>9240</v>
       </c>
     </row>
     <row r="41">
@@ -83841,7 +83841,7 @@
         <v>53396</v>
       </c>
       <c r="C41" t="n">
-        <v>553865.0287303933</v>
+        <v>561055.9804363938</v>
       </c>
       <c r="D41" t="n">
         <v>12000</v>
@@ -83855,7 +83855,7 @@
         <v>53396</v>
       </c>
       <c r="C42" t="n">
-        <v>551282.0287303933</v>
+        <v>558472.9804363938</v>
       </c>
       <c r="D42" t="n">
         <v>12000</v>
@@ -83866,10 +83866,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>46037.75796424902</v>
+        <v>52371.47211336549</v>
       </c>
       <c r="C43" t="n">
-        <v>548699.0287303933</v>
+        <v>555889.9804363938</v>
       </c>
       <c r="D43" t="n">
         <v>8819.961883701142</v>
@@ -83880,10 +83880,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>34059.6060443504</v>
+        <v>48639.12004949187</v>
       </c>
       <c r="C44" t="n">
-        <v>546116.0287303933</v>
+        <v>553306.9804363938</v>
       </c>
       <c r="D44" t="n">
         <v>5559.092318483751</v>
@@ -83894,13 +83894,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>27537.78200534869</v>
+        <v>48639.12004949187</v>
       </c>
       <c r="C45" t="n">
-        <v>543533.0287303933</v>
+        <v>550723.9804363938</v>
       </c>
       <c r="D45" t="n">
-        <v>2818.788480630772</v>
+        <v>4498.881735618664</v>
       </c>
     </row>
     <row r="46">
@@ -83908,13 +83908,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>25100.08702128265</v>
+        <v>48639.12004949187</v>
       </c>
       <c r="C46" t="n">
-        <v>540950.0287303933</v>
+        <v>548140.9804363938</v>
       </c>
       <c r="D46" t="n">
-        <v>2276.339067935372</v>
+        <v>4498.881735618664</v>
       </c>
     </row>
     <row r="47">
@@ -83922,13 +83922,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>21659.22352630767</v>
+        <v>45198.25655451689</v>
       </c>
       <c r="C47" t="n">
-        <v>538367.0287303933</v>
+        <v>545557.9804363938</v>
       </c>
       <c r="D47" t="n">
-        <v>378.8088193515883</v>
+        <v>2601.351487034881</v>
       </c>
     </row>
     <row r="48">
@@ -83936,13 +83936,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>21659.22352630767</v>
+        <v>40716.06557860228</v>
       </c>
       <c r="C48" t="n">
-        <v>535784.0287303933</v>
+        <v>542974.9804363938</v>
       </c>
       <c r="D48" t="n">
-        <v>378.8088193515883</v>
+        <v>1619.046946558256</v>
       </c>
     </row>
     <row r="49">
@@ -83950,13 +83950,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>21514.93992090759</v>
+        <v>40716.06557860228</v>
       </c>
       <c r="C49" t="n">
-        <v>533201.0287303933</v>
+        <v>540391.9804363938</v>
       </c>
       <c r="D49" t="n">
-        <v>378.8088193515883</v>
+        <v>1478.43597635534</v>
       </c>
     </row>
     <row r="50">
@@ -83964,13 +83964,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>18190.80289767766</v>
+        <v>37391.92855537235</v>
       </c>
       <c r="C50" t="n">
-        <v>530618.0287303933</v>
+        <v>537808.9804363938</v>
       </c>
       <c r="D50" t="n">
-        <v>-0</v>
+        <v>1099.627157003752</v>
       </c>
     </row>
     <row r="51">
@@ -83978,13 +83978,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>18190.80289767766</v>
+        <v>37391.92855537235</v>
       </c>
       <c r="C51" t="n">
-        <v>528035.0287303933</v>
+        <v>535225.9804363938</v>
       </c>
       <c r="D51" t="n">
-        <v>39.84306413329778</v>
+        <v>1139.47022113705</v>
       </c>
     </row>
     <row r="52">
@@ -83992,13 +83992,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>18190.80289767766</v>
+        <v>37391.92855537235</v>
       </c>
       <c r="C52" t="n">
-        <v>525452.0287303933</v>
+        <v>532642.9804363938</v>
       </c>
       <c r="D52" t="n">
-        <v>834.4768403265778</v>
+        <v>1934.10399733033</v>
       </c>
     </row>
     <row r="53">
@@ -84006,13 +84006,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>18190.80289767766</v>
+        <v>36959.55301933488</v>
       </c>
       <c r="C53" t="n">
-        <v>522869.0287303933</v>
+        <v>530059.9804363938</v>
       </c>
       <c r="D53" t="n">
-        <v>1573.255574095475</v>
+        <v>2672.882731099228</v>
       </c>
     </row>
     <row r="54">
@@ -84020,13 +84020,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>18190.80289767766</v>
+        <v>34372.45350947988</v>
       </c>
       <c r="C54" t="n">
-        <v>520286.0287303933</v>
+        <v>527476.9804363938</v>
       </c>
       <c r="D54" t="n">
-        <v>2274.382039438845</v>
+        <v>3374.009196442597</v>
       </c>
     </row>
     <row r="55">
@@ -84034,13 +84034,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>18190.80289767766</v>
+        <v>34372.45350947988</v>
       </c>
       <c r="C55" t="n">
-        <v>517703.0287303933</v>
+        <v>524893.9804363938</v>
       </c>
       <c r="D55" t="n">
-        <v>2895.057929922637</v>
+        <v>3994.685086926389</v>
       </c>
     </row>
     <row r="56">
@@ -84048,13 +84048,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>14834.39281487585</v>
+        <v>34372.45350947988</v>
       </c>
       <c r="C56" t="n">
-        <v>515120.0287303933</v>
+        <v>522310.9804363938</v>
       </c>
       <c r="D56" t="n">
-        <v>3147.895309376641</v>
+        <v>4247.522466380393</v>
       </c>
     </row>
     <row r="57">
@@ -84062,13 +84062,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>3650.221786407095</v>
+        <v>14942.48262498611</v>
       </c>
       <c r="C57" t="n">
-        <v>512537.0287303933</v>
+        <v>519727.9804363938</v>
       </c>
       <c r="D57" t="n">
-        <v>2717.574175501468</v>
+        <v>3817.20133250522</v>
       </c>
     </row>
     <row r="58">
@@ -84076,13 +84076,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>-0</v>
+        <v>3046.460982554008</v>
       </c>
       <c r="C58" t="n">
-        <v>509954.0287303933</v>
+        <v>517144.9804363938</v>
       </c>
       <c r="D58" t="n">
-        <v>1116.019110081422</v>
+        <v>2215.646267085175</v>
       </c>
     </row>
     <row r="59">
@@ -84093,7 +84093,7 @@
         <v>-0</v>
       </c>
       <c r="C59" t="n">
-        <v>507371.0287303933</v>
+        <v>514561.9804363938</v>
       </c>
       <c r="D59" t="n">
         <v>-0</v>
@@ -84104,10 +84104,10 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>-0</v>
+        <v>2570.436082849835</v>
       </c>
       <c r="C60" t="n">
-        <v>504788.0287303933</v>
+        <v>511978.9804363938</v>
       </c>
       <c r="D60" t="n">
         <v>-0</v>
@@ -84118,13 +84118,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>5937.915113498789</v>
+        <v>9238.824306902021</v>
       </c>
       <c r="C61" t="n">
-        <v>502205.0287303933</v>
+        <v>509395.9804363938</v>
       </c>
       <c r="D61" t="n">
-        <v>2760</v>
+        <v>2010.447572573035</v>
       </c>
     </row>
     <row r="62">
@@ -84132,13 +84132,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>20212.09302516125</v>
+        <v>20942.56613571465</v>
       </c>
       <c r="C62" t="n">
-        <v>499622.0287303933</v>
+        <v>506812.9804363938</v>
       </c>
       <c r="D62" t="n">
-        <v>5520</v>
+        <v>4770.447572573035</v>
       </c>
     </row>
     <row r="63">
@@ -84146,13 +84146,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>33222.71928809195</v>
+        <v>34188.58567902833</v>
       </c>
       <c r="C63" t="n">
-        <v>497040.5557020529</v>
+        <v>504231.5074080534</v>
       </c>
       <c r="D63" t="n">
-        <v>7471.093973805574</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="64">
@@ -84163,7 +84163,7 @@
         <v>46953.7863213766</v>
       </c>
       <c r="C64" t="n">
-        <v>494485.024522464</v>
+        <v>501675.9762284645</v>
       </c>
       <c r="D64" t="n">
         <v>9240</v>
@@ -84177,7 +84177,7 @@
         <v>53396</v>
       </c>
       <c r="C65" t="n">
-        <v>491902.024522464</v>
+        <v>499092.9762284645</v>
       </c>
       <c r="D65" t="n">
         <v>12000</v>
@@ -84191,7 +84191,7 @@
         <v>53396</v>
       </c>
       <c r="C66" t="n">
-        <v>489319.024522464</v>
+        <v>496509.9762284645</v>
       </c>
       <c r="D66" t="n">
         <v>12000</v>
@@ -84202,13 +84202,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>46272.99253691825</v>
+        <v>44701.75279077268</v>
       </c>
       <c r="C67" t="n">
-        <v>486736.024522464</v>
+        <v>493926.9762284645</v>
       </c>
       <c r="D67" t="n">
-        <v>12000</v>
+        <v>11864.03123159435</v>
       </c>
     </row>
     <row r="68">
@@ -84216,13 +84216,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>32881.88898797804</v>
+        <v>29675.36852352972</v>
       </c>
       <c r="C68" t="n">
-        <v>484153.024522464</v>
+        <v>491343.9762284645</v>
       </c>
       <c r="D68" t="n">
-        <v>8739.130434782608</v>
+        <v>11864.03123159435</v>
       </c>
     </row>
     <row r="69">
@@ -84230,13 +84230,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>24561.98075750281</v>
+        <v>21355.46029305449</v>
       </c>
       <c r="C69" t="n">
-        <v>481570.024522464</v>
+        <v>488760.9762284645</v>
       </c>
       <c r="D69" t="n">
-        <v>5499.873851777676</v>
+        <v>9050.539828523975</v>
       </c>
     </row>
     <row r="70">
@@ -84244,13 +84244,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>14889.46265566808</v>
+        <v>13318.2229095225</v>
       </c>
       <c r="C70" t="n">
-        <v>478987.024522464</v>
+        <v>486177.9762284645</v>
       </c>
       <c r="D70" t="n">
-        <v>5499.873851777676</v>
+        <v>5789.670263306584</v>
       </c>
     </row>
     <row r="71">
@@ -84258,13 +84258,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>12477.40067111347</v>
+        <v>10906.16092496789</v>
       </c>
       <c r="C71" t="n">
-        <v>476404.024522464</v>
+        <v>483594.9762284645</v>
       </c>
       <c r="D71" t="n">
-        <v>3421.818864063461</v>
+        <v>3711.615275592368</v>
       </c>
     </row>
     <row r="72">
@@ -84275,10 +84275,10 @@
         <v>10906.16092496789</v>
       </c>
       <c r="C72" t="n">
-        <v>473821.024522464</v>
+        <v>481011.9762284645</v>
       </c>
       <c r="D72" t="n">
-        <v>2481.987766030379</v>
+        <v>2907.752945964942</v>
       </c>
     </row>
     <row r="73">
@@ -84289,10 +84289,10 @@
         <v>10906.16092496789</v>
       </c>
       <c r="C73" t="n">
-        <v>471238.024522464</v>
+        <v>478428.9762284645</v>
       </c>
       <c r="D73" t="n">
-        <v>2481.987766030379</v>
+        <v>2907.752945964942</v>
       </c>
     </row>
     <row r="74">
@@ -84303,10 +84303,10 @@
         <v>10906.16092496789</v>
       </c>
       <c r="C74" t="n">
-        <v>468655.024522464</v>
+        <v>475845.9762284645</v>
       </c>
       <c r="D74" t="n">
-        <v>2481.987766030379</v>
+        <v>2907.752945964942</v>
       </c>
     </row>
     <row r="75">
@@ -84317,10 +84317,10 @@
         <v>10906.16092496789</v>
       </c>
       <c r="C75" t="n">
-        <v>466072.024522464</v>
+        <v>473262.9762284645</v>
       </c>
       <c r="D75" t="n">
-        <v>2481.987766030379</v>
+        <v>2907.752945964942</v>
       </c>
     </row>
     <row r="76">
@@ -84331,10 +84331,10 @@
         <v>10906.16092496789</v>
       </c>
       <c r="C76" t="n">
-        <v>463489.024522464</v>
+        <v>470679.9762284645</v>
       </c>
       <c r="D76" t="n">
-        <v>2481.987766030379</v>
+        <v>2907.752945964942</v>
       </c>
     </row>
     <row r="77">
@@ -84345,10 +84345,10 @@
         <v>10906.16092496789</v>
       </c>
       <c r="C77" t="n">
-        <v>460906.024522464</v>
+        <v>468096.9762284645</v>
       </c>
       <c r="D77" t="n">
-        <v>2481.987766030379</v>
+        <v>2907.752945964942</v>
       </c>
     </row>
     <row r="78">
@@ -84359,10 +84359,10 @@
         <v>10906.16092496789</v>
       </c>
       <c r="C78" t="n">
-        <v>458323.024522464</v>
+        <v>465513.9762284645</v>
       </c>
       <c r="D78" t="n">
-        <v>2481.987766030379</v>
+        <v>2907.752945964942</v>
       </c>
     </row>
     <row r="79">
@@ -84373,10 +84373,10 @@
         <v>10906.16092496789</v>
       </c>
       <c r="C79" t="n">
-        <v>455740.024522464</v>
+        <v>462930.9762284645</v>
       </c>
       <c r="D79" t="n">
-        <v>2481.987766030379</v>
+        <v>2907.752945964942</v>
       </c>
     </row>
     <row r="80">
@@ -84387,10 +84387,10 @@
         <v>10906.16092496789</v>
       </c>
       <c r="C80" t="n">
-        <v>453157.024522464</v>
+        <v>460347.9762284645</v>
       </c>
       <c r="D80" t="n">
-        <v>2481.987766030379</v>
+        <v>2907.752945964942</v>
       </c>
     </row>
     <row r="81">
@@ -84401,10 +84401,10 @@
         <v>8395.201091258743</v>
       </c>
       <c r="C81" t="n">
-        <v>450574.024522464</v>
+        <v>457764.9762284645</v>
       </c>
       <c r="D81" t="n">
-        <v>1437.614066937813</v>
+        <v>196.1655077419418</v>
       </c>
     </row>
     <row r="82">
@@ -84415,10 +84415,10 @@
         <v>-0</v>
       </c>
       <c r="C82" t="n">
-        <v>447991.024522464</v>
+        <v>455181.9762284645</v>
       </c>
       <c r="D82" t="n">
-        <v>1437.614066937813</v>
+        <v>196.1655077419418</v>
       </c>
     </row>
     <row r="83">
@@ -84429,7 +84429,7 @@
         <v>-0</v>
       </c>
       <c r="C83" t="n">
-        <v>445408.024522464</v>
+        <v>452598.9762284645</v>
       </c>
       <c r="D83" t="n">
         <v>-0</v>
@@ -84443,7 +84443,7 @@
         <v>-0</v>
       </c>
       <c r="C84" t="n">
-        <v>442825.024522464</v>
+        <v>450015.9762284645</v>
       </c>
       <c r="D84" t="n">
         <v>-0</v>
@@ -84457,7 +84457,7 @@
         <v>-0</v>
       </c>
       <c r="C85" t="n">
-        <v>440242.024522464</v>
+        <v>447432.9762284645</v>
       </c>
       <c r="D85" t="n">
         <v>514.6480022998676</v>
@@ -84471,7 +84471,7 @@
         <v>6268.363524628467</v>
       </c>
       <c r="C86" t="n">
-        <v>437659.024522464</v>
+        <v>444849.9762284645</v>
       </c>
       <c r="D86" t="n">
         <v>3274.648002299868</v>
@@ -84485,7 +84485,7 @@
         <v>13492.57795355989</v>
       </c>
       <c r="C87" t="n">
-        <v>435193.6832270098</v>
+        <v>442384.6349330103</v>
       </c>
       <c r="D87" t="n">
         <v>6034.648002299868</v>
@@ -84499,7 +84499,7 @@
         <v>23955.60342074071</v>
       </c>
       <c r="C88" t="n">
-        <v>433155.7409904924</v>
+        <v>440346.6926964929</v>
       </c>
       <c r="D88" t="n">
         <v>8794.648002299868</v>
@@ -84513,7 +84513,7 @@
         <v>36344.49089492738</v>
       </c>
       <c r="C89" t="n">
-        <v>430572.7409904924</v>
+        <v>437763.6926964929</v>
       </c>
       <c r="D89" t="n">
         <v>11554.64800229987</v>
@@ -84527,7 +84527,7 @@
         <v>36344.49089492738</v>
       </c>
       <c r="C90" t="n">
-        <v>427989.7409904924</v>
+        <v>435180.6926964929</v>
       </c>
       <c r="D90" t="n">
         <v>11943.11464485805</v>
@@ -84538,10 +84538,10 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>32633.17319297276</v>
+        <v>26971.47063744933</v>
       </c>
       <c r="C91" t="n">
-        <v>425406.7409904924</v>
+        <v>432597.6926964929</v>
       </c>
       <c r="D91" t="n">
         <v>9838.935224211362</v>
@@ -84555,10 +84555,10 @@
         <v>14788.39779511451</v>
       </c>
       <c r="C92" t="n">
-        <v>422823.7409904924</v>
+        <v>430014.6926964929</v>
       </c>
       <c r="D92" t="n">
-        <v>7950.591430588272</v>
+        <v>6578.065658993971</v>
       </c>
     </row>
     <row r="93">
@@ -84569,10 +84569,10 @@
         <v>5974.563982504359</v>
       </c>
       <c r="C93" t="n">
-        <v>420240.7409904924</v>
+        <v>427431.6926964929</v>
       </c>
       <c r="D93" t="n">
-        <v>4689.721865370881</v>
+        <v>3317.19609377658</v>
       </c>
     </row>
     <row r="94">
@@ -84583,10 +84583,10 @@
         <v>-0</v>
       </c>
       <c r="C94" t="n">
-        <v>417657.7409904924</v>
+        <v>424848.6926964929</v>
       </c>
       <c r="D94" t="n">
-        <v>1428.852300153489</v>
+        <v>56.32652855918877</v>
       </c>
     </row>
     <row r="95">
@@ -84597,7 +84597,7 @@
         <v>-0</v>
       </c>
       <c r="C95" t="n">
-        <v>415074.7409904924</v>
+        <v>422265.6926964929</v>
       </c>
       <c r="D95" t="n">
         <v>-0</v>
@@ -84611,7 +84611,7 @@
         <v>-0</v>
       </c>
       <c r="C96" t="n">
-        <v>412491.7409904924</v>
+        <v>419682.6926964929</v>
       </c>
       <c r="D96" t="n">
         <v>-0</v>
@@ -84625,7 +84625,7 @@
         <v>-0</v>
       </c>
       <c r="C97" t="n">
-        <v>409908.7409904924</v>
+        <v>417099.6926964929</v>
       </c>
       <c r="D97" t="n">
         <v>-0</v>
@@ -84639,7 +84639,7 @@
         <v>-0</v>
       </c>
       <c r="C98" t="n">
-        <v>407325.7409904924</v>
+        <v>414516.6926964929</v>
       </c>
       <c r="D98" t="n">
         <v>425.5706602396636</v>
@@ -84653,7 +84653,7 @@
         <v>716.7567832423572</v>
       </c>
       <c r="C99" t="n">
-        <v>404742.7409904924</v>
+        <v>411933.6926964929</v>
       </c>
       <c r="D99" t="n">
         <v>425.5706602396636</v>
@@ -84667,7 +84667,7 @@
         <v>-0</v>
       </c>
       <c r="C100" t="n">
-        <v>402159.7409904924</v>
+        <v>409350.6926964929</v>
       </c>
       <c r="D100" t="n">
         <v>-0</v>
@@ -84681,7 +84681,7 @@
         <v>-0</v>
       </c>
       <c r="C101" t="n">
-        <v>399576.7409904924</v>
+        <v>406767.6926964929</v>
       </c>
       <c r="D101" t="n">
         <v>-0</v>
@@ -84695,7 +84695,7 @@
         <v>-0</v>
       </c>
       <c r="C102" t="n">
-        <v>396993.7409904924</v>
+        <v>404184.6926964929</v>
       </c>
       <c r="D102" t="n">
         <v>-0</v>
@@ -84709,7 +84709,7 @@
         <v>-0</v>
       </c>
       <c r="C103" t="n">
-        <v>394410.7409904924</v>
+        <v>401601.6926964929</v>
       </c>
       <c r="D103" t="n">
         <v>-0</v>
@@ -84723,7 +84723,7 @@
         <v>-0</v>
       </c>
       <c r="C104" t="n">
-        <v>392047.9205076756</v>
+        <v>399238.872213676</v>
       </c>
       <c r="D104" t="n">
         <v>-0</v>
@@ -84737,7 +84737,7 @@
         <v>-0</v>
       </c>
       <c r="C105" t="n">
-        <v>389894.859035911</v>
+        <v>397085.8107419115</v>
       </c>
       <c r="D105" t="n">
         <v>-0</v>
@@ -84751,7 +84751,7 @@
         <v>-0</v>
       </c>
       <c r="C106" t="n">
-        <v>388246.7761646067</v>
+        <v>395437.7278706072</v>
       </c>
       <c r="D106" t="n">
         <v>-0</v>
@@ -84765,7 +84765,7 @@
         <v>-0</v>
       </c>
       <c r="C107" t="n">
-        <v>388246.7761646067</v>
+        <v>395437.7278706072</v>
       </c>
       <c r="D107" t="n">
         <v>-0</v>
@@ -84779,7 +84779,7 @@
         <v>-0</v>
       </c>
       <c r="C108" t="n">
-        <v>388246.7761646067</v>
+        <v>395437.7278706072</v>
       </c>
       <c r="D108" t="n">
         <v>-0</v>
@@ -84793,7 +84793,7 @@
         <v>-0</v>
       </c>
       <c r="C109" t="n">
-        <v>388246.7761646067</v>
+        <v>395437.7278706072</v>
       </c>
       <c r="D109" t="n">
         <v>1090.905680265141</v>
@@ -84807,7 +84807,7 @@
         <v>-0</v>
       </c>
       <c r="C110" t="n">
-        <v>388246.7761646067</v>
+        <v>395437.7278706072</v>
       </c>
       <c r="D110" t="n">
         <v>3774.692104274956</v>
@@ -84821,7 +84821,7 @@
         <v>17563.41575760708</v>
       </c>
       <c r="C111" t="n">
-        <v>388246.7761646067</v>
+        <v>395437.7278706072</v>
       </c>
       <c r="D111" t="n">
         <v>6534.692104274956</v>
@@ -84835,7 +84835,7 @@
         <v>38097.96413947697</v>
       </c>
       <c r="C112" t="n">
-        <v>388246.7761646067</v>
+        <v>395437.7278706072</v>
       </c>
       <c r="D112" t="n">
         <v>9294.692104274956</v>
@@ -84849,7 +84849,7 @@
         <v>53396</v>
       </c>
       <c r="C113" t="n">
-        <v>388246.7761646067</v>
+        <v>395437.7278706072</v>
       </c>
       <c r="D113" t="n">
         <v>12000</v>
@@ -84863,7 +84863,7 @@
         <v>53396</v>
       </c>
       <c r="C114" t="n">
-        <v>388246.7761646067</v>
+        <v>395437.7278706072</v>
       </c>
       <c r="D114" t="n">
         <v>12000</v>
@@ -84877,10 +84877,10 @@
         <v>45721.07536618317</v>
       </c>
       <c r="C115" t="n">
-        <v>388246.7761646067</v>
+        <v>395437.7278706072</v>
       </c>
       <c r="D115" t="n">
-        <v>9393.594520727269</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="116">
@@ -84891,10 +84891,10 @@
         <v>28649.55966512779</v>
       </c>
       <c r="C116" t="n">
-        <v>385663.7761646067</v>
+        <v>392854.7278706072</v>
       </c>
       <c r="D116" t="n">
-        <v>9044.433541338683</v>
+        <v>8834.534672785327</v>
       </c>
     </row>
     <row r="117">
@@ -84905,10 +84905,10 @@
         <v>19202.75763450051</v>
       </c>
       <c r="C117" t="n">
-        <v>383080.7761646067</v>
+        <v>390271.7278706072</v>
       </c>
       <c r="D117" t="n">
-        <v>5783.563976121292</v>
+        <v>5655.912356557037</v>
       </c>
     </row>
     <row r="118">
@@ -84919,10 +84919,10 @@
         <v>13555.12061293168</v>
       </c>
       <c r="C118" t="n">
-        <v>380497.7761646067</v>
+        <v>387688.7278706072</v>
       </c>
       <c r="D118" t="n">
-        <v>2945.557256677182</v>
+        <v>2817.905637112926</v>
       </c>
     </row>
     <row r="119">
@@ -84930,13 +84930,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>611.284168608674</v>
+        <v>6625.876937272157</v>
       </c>
       <c r="C119" t="n">
-        <v>377914.7761646067</v>
+        <v>385105.7278706072</v>
       </c>
       <c r="D119" t="n">
-        <v>2768.256543108979</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="120">
@@ -84944,10 +84944,10 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>2101.520096417336</v>
+        <v>8116.11286508082</v>
       </c>
       <c r="C120" t="n">
-        <v>375331.7761646067</v>
+        <v>382522.7278706072</v>
       </c>
       <c r="D120" t="n">
         <v>-0</v>
@@ -84961,7 +84961,7 @@
         <v>-0</v>
       </c>
       <c r="C121" t="n">
-        <v>372748.7761646067</v>
+        <v>379939.7278706072</v>
       </c>
       <c r="D121" t="n">
         <v>-0</v>
@@ -84975,10 +84975,10 @@
         <v>-0</v>
       </c>
       <c r="C122" t="n">
-        <v>370165.7761646067</v>
+        <v>379939.7278706072</v>
       </c>
       <c r="D122" t="n">
-        <v>421.4641059672724</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="123">
@@ -84989,10 +84989,10 @@
         <v>-0</v>
       </c>
       <c r="C123" t="n">
-        <v>367582.7761646067</v>
+        <v>379513.4263016781</v>
       </c>
       <c r="D123" t="n">
-        <v>1119.017635934535</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="124">
@@ -85003,10 +85003,10 @@
         <v>-0</v>
       </c>
       <c r="C124" t="n">
-        <v>364999.7761646067</v>
+        <v>376930.4263016781</v>
       </c>
       <c r="D124" t="n">
-        <v>2131.679477107685</v>
+        <v>1012.661841173149</v>
       </c>
     </row>
     <row r="125">
@@ -85017,10 +85017,10 @@
         <v>-0</v>
       </c>
       <c r="C125" t="n">
-        <v>362416.7761646067</v>
+        <v>374347.4263016781</v>
       </c>
       <c r="D125" t="n">
-        <v>2966.937958197043</v>
+        <v>1847.920322262508</v>
       </c>
     </row>
     <row r="126">
@@ -85031,10 +85031,10 @@
         <v>-0</v>
       </c>
       <c r="C126" t="n">
-        <v>359833.7761646067</v>
+        <v>371764.4263016781</v>
       </c>
       <c r="D126" t="n">
-        <v>3991.80733026382</v>
+        <v>2073.416414329285</v>
       </c>
     </row>
     <row r="127">
@@ -85045,10 +85045,10 @@
         <v>-0</v>
       </c>
       <c r="C127" t="n">
-        <v>357250.7761646067</v>
+        <v>369181.4263016781</v>
       </c>
       <c r="D127" t="n">
-        <v>5181.590675947613</v>
+        <v>3263.199760013077</v>
       </c>
     </row>
     <row r="128">
@@ -85059,10 +85059,10 @@
         <v>-0</v>
       </c>
       <c r="C128" t="n">
-        <v>354667.7761646067</v>
+        <v>366598.4263016781</v>
       </c>
       <c r="D128" t="n">
-        <v>5652.20672445626</v>
+        <v>4170.382649867081</v>
       </c>
     </row>
     <row r="129">
@@ -85073,10 +85073,10 @@
         <v>-0</v>
       </c>
       <c r="C129" t="n">
-        <v>352084.7761646067</v>
+        <v>364015.4263016781</v>
       </c>
       <c r="D129" t="n">
-        <v>6561.015054763954</v>
+        <v>5079.190980174775</v>
       </c>
     </row>
     <row r="130">
@@ -85087,10 +85087,10 @@
         <v>-0</v>
       </c>
       <c r="C130" t="n">
-        <v>351329.2738229937</v>
+        <v>363259.923960065</v>
       </c>
       <c r="D130" t="n">
-        <v>7000.933777412072</v>
+        <v>6388.659662822891</v>
       </c>
     </row>
     <row r="131">
@@ -85101,10 +85101,10 @@
         <v>-0</v>
       </c>
       <c r="C131" t="n">
-        <v>350614.5306909014</v>
+        <v>363259.923960065</v>
       </c>
       <c r="D131" t="n">
-        <v>7000.933777412072</v>
+        <v>7224.168480790154</v>
       </c>
     </row>
     <row r="132">
@@ -85115,10 +85115,10 @@
         <v>-0</v>
       </c>
       <c r="C132" t="n">
-        <v>350614.5306909014</v>
+        <v>363259.923960065</v>
       </c>
       <c r="D132" t="n">
-        <v>4183.028140299845</v>
+        <v>4406.262843677927</v>
       </c>
     </row>
     <row r="133">
@@ -85126,13 +85126,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>2887.473372210815</v>
+        <v>8260.79489747437</v>
       </c>
       <c r="C133" t="n">
-        <v>350614.5306909014</v>
+        <v>363259.923960065</v>
       </c>
       <c r="D133" t="n">
-        <v>5155.229775487978</v>
+        <v>4780.305106738203</v>
       </c>
     </row>
     <row r="134">
@@ -85140,10 +85140,10 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>18629.43365476234</v>
+        <v>16282.23408025934</v>
       </c>
       <c r="C134" t="n">
-        <v>350614.5306909014</v>
+        <v>363259.923960065</v>
       </c>
       <c r="D134" t="n">
         <v>5155.229775487978</v>
@@ -85154,10 +85154,10 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>34394.00968674535</v>
+        <v>32046.81011224235</v>
       </c>
       <c r="C135" t="n">
-        <v>350614.5306909014</v>
+        <v>363259.923960065</v>
       </c>
       <c r="D135" t="n">
         <v>2782.689520099988</v>
@@ -85168,10 +85168,10 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>44720.81715551738</v>
+        <v>43306.75846213452</v>
       </c>
       <c r="C136" t="n">
-        <v>350614.5306909014</v>
+        <v>363259.923960065</v>
       </c>
       <c r="D136" t="n">
         <v>2486.139502917355</v>
@@ -85182,10 +85182,10 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>51981.27687424721</v>
+        <v>51079.34851870083</v>
       </c>
       <c r="C137" t="n">
-        <v>350614.5306909014</v>
+        <v>363259.923960065</v>
       </c>
       <c r="D137" t="n">
         <v>1474.296210855312</v>
@@ -85199,7 +85199,7 @@
         <v>53396</v>
       </c>
       <c r="C138" t="n">
-        <v>350614.5306909014</v>
+        <v>363259.923960065</v>
       </c>
       <c r="D138" t="n">
         <v>1034.485476610106</v>
@@ -85213,7 +85213,7 @@
         <v>48836.69785724101</v>
       </c>
       <c r="C139" t="n">
-        <v>348031.5306909014</v>
+        <v>360676.923960065</v>
       </c>
       <c r="D139" t="n">
         <v>1869.99429457737</v>
@@ -85224,10 +85224,10 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>19883.38997811019</v>
+        <v>34767.48207710638</v>
       </c>
       <c r="C140" t="n">
-        <v>345448.5306909014</v>
+        <v>358093.923960065</v>
       </c>
       <c r="D140" t="n">
         <v>1099.425489101826</v>
@@ -85238,10 +85238,10 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>10942.54208944314</v>
+        <v>25826.63418843933</v>
       </c>
       <c r="C141" t="n">
-        <v>342865.5306909014</v>
+        <v>355510.923960065</v>
       </c>
       <c r="D141" t="n">
         <v>-0</v>
@@ -85252,10 +85252,10 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>6041.70872998853</v>
+        <v>18044.85985704828</v>
       </c>
       <c r="C142" t="n">
-        <v>340282.5306909014</v>
+        <v>355510.923960065</v>
       </c>
       <c r="D142" t="n">
         <v>-0</v>
@@ -85266,10 +85266,10 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>6041.70872998853</v>
+        <v>18044.85985704828</v>
       </c>
       <c r="C143" t="n">
-        <v>338960.5097388951</v>
+        <v>354188.9030080587</v>
       </c>
       <c r="D143" t="n">
         <v>-0</v>
@@ -85280,10 +85280,10 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>6041.70872998853</v>
+        <v>11420.28320339198</v>
       </c>
       <c r="C144" t="n">
-        <v>336377.5097388951</v>
+        <v>354188.9030080587</v>
       </c>
       <c r="D144" t="n">
         <v>1653.489528492304</v>
@@ -85294,13 +85294,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>6041.70872998853</v>
+        <v>10493.21726552061</v>
       </c>
       <c r="C145" t="n">
-        <v>336377.5097388951</v>
+        <v>351655.2070706646</v>
       </c>
       <c r="D145" t="n">
-        <v>2808.497174680121</v>
+        <v>1653.489528492304</v>
       </c>
     </row>
     <row r="146">
@@ -85308,13 +85308,13 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>7182.138565031882</v>
+        <v>11633.64710056397</v>
       </c>
       <c r="C146" t="n">
-        <v>336377.5097388951</v>
+        <v>351655.2070706646</v>
       </c>
       <c r="D146" t="n">
-        <v>2211.195492238806</v>
+        <v>1056.187846050989</v>
       </c>
     </row>
     <row r="147">
@@ -85322,13 +85322,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>2391.471038689415</v>
+        <v>5215.49152278231</v>
       </c>
       <c r="C147" t="n">
-        <v>334918.3331442279</v>
+        <v>351655.2070706646</v>
       </c>
       <c r="D147" t="n">
-        <v>2571.334247769477</v>
+        <v>2148.594520018252</v>
       </c>
     </row>
     <row r="148">
@@ -85339,10 +85339,10 @@
         <v>-0</v>
       </c>
       <c r="C148" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D148" t="n">
-        <v>4844.279800942626</v>
+        <v>2148.594520018252</v>
       </c>
     </row>
     <row r="149">
@@ -85353,10 +85353,10 @@
         <v>-0</v>
       </c>
       <c r="C149" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D149" t="n">
-        <v>4844.279800942626</v>
+        <v>4252.008357389767</v>
       </c>
     </row>
     <row r="150">
@@ -85367,10 +85367,10 @@
         <v>-0</v>
       </c>
       <c r="C150" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D150" t="n">
-        <v>4844.279800942626</v>
+        <v>4252.008357389767</v>
       </c>
     </row>
     <row r="151">
@@ -85378,13 +85378,13 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>8070.37753781712</v>
+        <v>6277.908822415723</v>
       </c>
       <c r="C151" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D151" t="n">
-        <v>4844.279800942626</v>
+        <v>6421.900404293201</v>
       </c>
     </row>
     <row r="152">
@@ -85392,13 +85392,13 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>6269.584492857457</v>
+        <v>4477.11577745606</v>
       </c>
       <c r="C152" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D152" t="n">
-        <v>4844.279800942626</v>
+        <v>7116.136078030679</v>
       </c>
     </row>
     <row r="153">
@@ -85409,7 +85409,7 @@
         <v>6269.584492857457</v>
       </c>
       <c r="C153" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D153" t="n">
         <v>7116.136078030679</v>
@@ -85423,7 +85423,7 @@
         <v>3495.398747552198</v>
       </c>
       <c r="C154" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D154" t="n">
         <v>7634.285712678796</v>
@@ -85437,7 +85437,7 @@
         <v>1656.313134728513</v>
       </c>
       <c r="C155" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D155" t="n">
         <v>7972.004593870283</v>
@@ -85451,7 +85451,7 @@
         <v>-0</v>
       </c>
       <c r="C156" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D156" t="n">
         <v>8364.675334447693</v>
@@ -85465,7 +85465,7 @@
         <v>-0</v>
       </c>
       <c r="C157" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D157" t="n">
         <v>8085.409059036899</v>
@@ -85479,7 +85479,7 @@
         <v>-0</v>
       </c>
       <c r="C158" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D158" t="n">
         <v>7694.884911285681</v>
@@ -85493,7 +85493,7 @@
         <v>3900.426320254093</v>
       </c>
       <c r="C159" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D159" t="n">
         <v>8563.226074614642</v>
@@ -85507,7 +85507,7 @@
         <v>11952.97300133897</v>
       </c>
       <c r="C160" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D160" t="n">
         <v>10343.25867085162</v>
@@ -85518,10 +85518,10 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>19279.95306499087</v>
+        <v>22528.51399270161</v>
       </c>
       <c r="C161" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D161" t="n">
         <v>11302.6092082455</v>
@@ -85532,10 +85532,10 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>26172.254200492</v>
+        <v>29420.81512820274</v>
       </c>
       <c r="C162" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D162" t="n">
         <v>12000</v>
@@ -85549,7 +85549,7 @@
         <v>34057.5382455974</v>
       </c>
       <c r="C163" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D163" t="n">
         <v>10845.86247587936</v>
@@ -85563,7 +85563,7 @@
         <v>32795.52694830789</v>
       </c>
       <c r="C164" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D164" t="n">
         <v>8027.956838770762</v>
@@ -85577,7 +85577,7 @@
         <v>22410.35199658581</v>
       </c>
       <c r="C165" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D165" t="n">
         <v>7635.56700184285</v>
@@ -85591,7 +85591,7 @@
         <v>12371.33424616991</v>
       </c>
       <c r="C166" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D166" t="n">
         <v>5728.134130816087</v>
@@ -85605,7 +85605,7 @@
         <v>14039.10849273815</v>
       </c>
       <c r="C167" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D167" t="n">
         <v>3820.011102401826</v>
@@ -85619,7 +85619,7 @@
         <v>9328.14251452289</v>
       </c>
       <c r="C168" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D168" t="n">
         <v>3979.732755523425</v>
@@ -85633,7 +85633,7 @@
         <v>10679.2</v>
       </c>
       <c r="C169" t="n">
-        <v>333756.1394193806</v>
+        <v>350493.0133458173</v>
       </c>
       <c r="D169" t="n">
         <v>2400</v>
